--- a/wwwroot/template/TemPlateApproverQuote.xlsx
+++ b/wwwroot/template/TemPlateApproverQuote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanhmf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F52DDB-2193-46B9-A6BE-7ECAB381E402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D4F6B1-A19A-4BFB-835F-B6141B4F9EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
@@ -666,7 +666,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="501">
   <si>
     <t>No</t>
   </si>
@@ -2100,6 +2100,342 @@
   <si>
     <t>Số đơn yêu cầu báo giá</t>
   </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao/xơ </t>
+  </si>
+  <si>
+    <t>Ao/xơ (gồm bao bì)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao/xơ (gồm cont.) </t>
+  </si>
+  <si>
+    <t>Ao/xơ (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Ao/xơ (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Ao/xơ đong</t>
+  </si>
+  <si>
+    <t>Bản</t>
+  </si>
+  <si>
+    <t>Bảng</t>
+  </si>
+  <si>
+    <t>Barrel</t>
+  </si>
+  <si>
+    <t>Bịch</t>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <t>Cái/Chiếc</t>
+  </si>
+  <si>
+    <t>Cành</t>
+  </si>
+  <si>
+    <t>Cara</t>
+  </si>
+  <si>
+    <t>Cây</t>
+  </si>
+  <si>
+    <t>Cen ti mét</t>
+  </si>
+  <si>
+    <t>Chai/ Lọ/ Tuýp</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>cm2</t>
+  </si>
+  <si>
+    <t>cm3</t>
+  </si>
+  <si>
+    <t>Con</t>
+  </si>
+  <si>
+    <t>CONTAINER</t>
+  </si>
+  <si>
+    <t>Củ</t>
+  </si>
+  <si>
+    <t>Cục</t>
+  </si>
+  <si>
+    <t>Cụm</t>
+  </si>
+  <si>
+    <t>Cuốn</t>
+  </si>
+  <si>
+    <t>Cuộn</t>
+  </si>
+  <si>
+    <t>dm</t>
+  </si>
+  <si>
+    <t>dm2</t>
+  </si>
+  <si>
+    <t>Đôi/Cặp</t>
+  </si>
+  <si>
+    <t>Galông ruợu</t>
+  </si>
+  <si>
+    <t>Gam</t>
+  </si>
+  <si>
+    <t>Gam (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Gam (gồm container)</t>
+  </si>
+  <si>
+    <t>Gam (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Gam (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Gói</t>
+  </si>
+  <si>
+    <t>Hàm luợng lactoza</t>
+  </si>
+  <si>
+    <t>Hectolit</t>
+  </si>
+  <si>
+    <t>I/át</t>
+  </si>
+  <si>
+    <t>I/át khối</t>
+  </si>
+  <si>
+    <t>I/át vuông</t>
+  </si>
+  <si>
+    <t>Inch</t>
+  </si>
+  <si>
+    <t>Kiện/Hộp/Bao/Gói</t>
+  </si>
+  <si>
+    <t>Kilo lít</t>
+  </si>
+  <si>
+    <t>Kilo mét (1000 mét)</t>
+  </si>
+  <si>
+    <t>Kilô/oắt giờ</t>
+  </si>
+  <si>
+    <t>Kilogam</t>
+  </si>
+  <si>
+    <t>Kilogam (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Kilogam (gồm cont.)</t>
+  </si>
+  <si>
+    <t>Kilogam (hàm lg KL)</t>
+  </si>
+  <si>
+    <t>Kilogam (tr.lg khô)</t>
+  </si>
+  <si>
+    <t>KIT</t>
+  </si>
+  <si>
+    <t>KVA</t>
+  </si>
+  <si>
+    <t>Liều</t>
+  </si>
+  <si>
+    <t>Lít</t>
+  </si>
+  <si>
+    <t>Lít Anh</t>
+  </si>
+  <si>
+    <t>Lô (nhiều cái)</t>
+  </si>
+  <si>
+    <t>Lon/Can</t>
+  </si>
+  <si>
+    <t>Mét</t>
+  </si>
+  <si>
+    <t>Mét khối</t>
+  </si>
+  <si>
+    <t>Mét vuông</t>
+  </si>
+  <si>
+    <t>Mili gram</t>
+  </si>
+  <si>
+    <t>Mili lít</t>
+  </si>
+  <si>
+    <t>Mili mét</t>
+  </si>
+  <si>
+    <t>mm2</t>
+  </si>
+  <si>
+    <t>mm3</t>
+  </si>
+  <si>
+    <t>Nghìn</t>
+  </si>
+  <si>
+    <t>Ống</t>
+  </si>
+  <si>
+    <t>Panh</t>
+  </si>
+  <si>
+    <t>Pao</t>
+  </si>
+  <si>
+    <t>Pao (gồm bao bì)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pao (gồm container) </t>
+  </si>
+  <si>
+    <t>Pao (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Pao (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Phút</t>
+  </si>
+  <si>
+    <t>Phút khối</t>
+  </si>
+  <si>
+    <t>Phút vuông</t>
+  </si>
+  <si>
+    <t>Quả</t>
+  </si>
+  <si>
+    <t>Quyển/Tập</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Sợi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ster </t>
+  </si>
+  <si>
+    <t>Tá</t>
+  </si>
+  <si>
+    <t>Tạ (100kg)</t>
+  </si>
+  <si>
+    <t>Tấm</t>
+  </si>
+  <si>
+    <t>Tấn</t>
+  </si>
+  <si>
+    <t>Tấn (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Tấn (gồm container)</t>
+  </si>
+  <si>
+    <t>Tấn (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Tấn (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Tấn dài</t>
+  </si>
+  <si>
+    <t>Tấn ngắn</t>
+  </si>
+  <si>
+    <t>Thanh/Mảnh/Miếng</t>
+  </si>
+  <si>
+    <t>Tờ</t>
+  </si>
+  <si>
+    <t>Tổng trọng lượng</t>
+  </si>
+  <si>
+    <t>Tổng trọng tải</t>
+  </si>
+  <si>
+    <t>Troi ao/xơ</t>
+  </si>
+  <si>
+    <t>Trọng tải</t>
+  </si>
+  <si>
+    <t>Túi</t>
+  </si>
+  <si>
+    <t>Tút</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Viên/Hạt</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>LBS</t>
+  </si>
+  <si>
+    <t>Vỉ</t>
+  </si>
+  <si>
+    <t>Inch2</t>
+  </si>
+  <si>
+    <t>Air Dry Met Ton</t>
+  </si>
+  <si>
+    <t>Sản phẩm</t>
+  </si>
+  <si>
+    <t>Thùng</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
 </sst>
 </file>
 
@@ -2108,7 +2444,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2190,6 +2526,23 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2317,7 +2670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2407,13 +2760,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2435,15 +2800,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2455,20 +2820,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2810,35 +3170,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17565F5E-2F90-4D1C-BF41-7BF32BF5014E}">
   <dimension ref="A1:AG567"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.54296875" style="10" customWidth="1"/>
-    <col min="2" max="5" width="9.1796875" style="10"/>
-    <col min="6" max="6" width="11.1796875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="13.81640625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="20.81640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="18.26953125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="15.54296875" style="10" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" style="10" customWidth="1"/>
-    <col min="13" max="14" width="13.81640625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="18.26953125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="11.140625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" style="10" customWidth="1"/>
+    <col min="13" max="14" width="13.85546875" style="10" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" style="10" customWidth="1"/>
     <col min="16" max="16" width="19" style="10" customWidth="1"/>
-    <col min="17" max="17" width="23.26953125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" style="10" customWidth="1"/>
     <col min="18" max="18" width="23" style="10" customWidth="1"/>
-    <col min="19" max="23" width="15.54296875" style="10" customWidth="1"/>
-    <col min="24" max="24" width="9.1796875" style="10"/>
-    <col min="25" max="25" width="11.54296875" style="10" customWidth="1"/>
-    <col min="26" max="26" width="14.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.1796875" style="10" customWidth="1"/>
-    <col min="28" max="28" width="13.453125" style="10" customWidth="1"/>
-    <col min="29" max="29" width="19.81640625" style="10" customWidth="1"/>
-    <col min="30" max="30" width="18.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.7265625" style="10" customWidth="1"/>
-    <col min="32" max="16384" width="9.1796875" style="10"/>
+    <col min="19" max="23" width="15.5703125" style="10" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="10"/>
+    <col min="25" max="25" width="11.5703125" style="10" customWidth="1"/>
+    <col min="26" max="26" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.140625" style="10" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="10" customWidth="1"/>
+    <col min="29" max="29" width="19.85546875" style="10" customWidth="1"/>
+    <col min="30" max="30" width="18.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.7109375" style="10" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>330</v>
       </c>
@@ -2873,7 +3233,7 @@
       <c r="AD1" s="9"/>
       <c r="AE1" s="9"/>
     </row>
-    <row r="2" spans="1:33" ht="14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>332</v>
       </c>
@@ -2908,7 +3268,7 @@
       <c r="AD2" s="9"/>
       <c r="AE2" s="9"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2941,19 +3301,19 @@
       <c r="AD3" s="9"/>
       <c r="AE3" s="9"/>
     </row>
-    <row r="4" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -2976,7 +3336,7 @@
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
     </row>
-    <row r="5" spans="1:33" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>1</v>
       </c>
@@ -3016,15 +3376,15 @@
       <c r="M5" s="25">
         <v>12</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="40">
         <f>M5+1</f>
         <v>13</v>
       </c>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="38"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="42"/>
       <c r="T5" s="24">
         <v>14</v>
       </c>
@@ -3081,111 +3441,111 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="7" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+    <row r="6" spans="1:33" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="L6" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="N6" s="39" t="s">
+      <c r="N6" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="34" t="s">
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="U6" s="34" t="s">
+      <c r="U6" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="V6" s="34" t="s">
+      <c r="V6" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="W6" s="34" t="s">
+      <c r="W6" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="X6" s="34" t="s">
+      <c r="X6" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="Y6" s="34" t="s">
+      <c r="Y6" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="Z6" s="34" t="s">
+      <c r="Z6" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="AA6" s="34" t="s">
+      <c r="AA6" s="35" t="s">
         <v>358</v>
       </c>
-      <c r="AB6" s="34" t="s">
+      <c r="AB6" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="AC6" s="34" t="s">
+      <c r="AC6" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="AD6" s="34" t="s">
+      <c r="AD6" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="AE6" s="34" t="s">
+      <c r="AE6" s="35" t="s">
         <v>362</v>
       </c>
-      <c r="AF6" s="33" t="s">
+      <c r="AF6" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="AG6" s="33" t="s">
+      <c r="AG6" s="39" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" ht="57.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="43"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+    <row r="7" spans="1:33" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
       <c r="N7" s="19" t="s">
         <v>344</v>
       </c>
@@ -3204,22 +3564,22 @@
       <c r="S7" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="35"/>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="35"/>
-      <c r="AE7" s="35"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="33"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1</v>
       </c>
@@ -3264,7 +3624,7 @@
       <c r="AF8" s="13"/>
       <c r="AG8" s="13"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -3309,7 +3669,7 @@
       <c r="AF9" s="13"/>
       <c r="AG9" s="13"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>3</v>
       </c>
@@ -3354,7 +3714,7 @@
       <c r="AF10" s="13"/>
       <c r="AG10" s="13"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>4</v>
       </c>
@@ -3399,7 +3759,7 @@
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>5</v>
       </c>
@@ -3444,7 +3804,7 @@
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>6</v>
       </c>
@@ -3489,7 +3849,7 @@
       <c r="AF13" s="13"/>
       <c r="AG13" s="13"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>7</v>
       </c>
@@ -3534,7 +3894,7 @@
       <c r="AF14" s="13"/>
       <c r="AG14" s="13"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>8</v>
       </c>
@@ -3579,7 +3939,7 @@
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>9</v>
       </c>
@@ -3624,7 +3984,7 @@
       <c r="AF16" s="13"/>
       <c r="AG16" s="13"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>10</v>
       </c>
@@ -3669,7 +4029,7 @@
       <c r="AF17" s="13"/>
       <c r="AG17" s="13"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>11</v>
       </c>
@@ -3714,7 +4074,7 @@
       <c r="AF18" s="13"/>
       <c r="AG18" s="13"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>12</v>
       </c>
@@ -3759,7 +4119,7 @@
       <c r="AF19" s="13"/>
       <c r="AG19" s="13"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>13</v>
       </c>
@@ -3804,7 +4164,7 @@
       <c r="AF20" s="13"/>
       <c r="AG20" s="13"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>14</v>
       </c>
@@ -3849,7 +4209,7 @@
       <c r="AF21" s="13"/>
       <c r="AG21" s="13"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>15</v>
       </c>
@@ -3894,7 +4254,7 @@
       <c r="AF22" s="13"/>
       <c r="AG22" s="13"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>16</v>
       </c>
@@ -3939,7 +4299,7 @@
       <c r="AF23" s="13"/>
       <c r="AG23" s="13"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>17</v>
       </c>
@@ -3984,7 +4344,7 @@
       <c r="AF24" s="13"/>
       <c r="AG24" s="13"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>18</v>
       </c>
@@ -4029,7 +4389,7 @@
       <c r="AF25" s="13"/>
       <c r="AG25" s="13"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>19</v>
       </c>
@@ -4074,7 +4434,7 @@
       <c r="AF26" s="13"/>
       <c r="AG26" s="13"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>20</v>
       </c>
@@ -4119,7 +4479,7 @@
       <c r="AF27" s="13"/>
       <c r="AG27" s="13"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>21</v>
       </c>
@@ -4164,7 +4524,7 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>22</v>
       </c>
@@ -4209,7 +4569,7 @@
       <c r="AF29" s="13"/>
       <c r="AG29" s="13"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>23</v>
       </c>
@@ -4254,7 +4614,7 @@
       <c r="AF30" s="13"/>
       <c r="AG30" s="13"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>24</v>
       </c>
@@ -4299,7 +4659,7 @@
       <c r="AF31" s="13"/>
       <c r="AG31" s="13"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>25</v>
       </c>
@@ -4344,7 +4704,7 @@
       <c r="AF32" s="13"/>
       <c r="AG32" s="13"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>26</v>
       </c>
@@ -4389,7 +4749,7 @@
       <c r="AF33" s="13"/>
       <c r="AG33" s="13"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>27</v>
       </c>
@@ -4434,7 +4794,7 @@
       <c r="AF34" s="13"/>
       <c r="AG34" s="13"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>28</v>
       </c>
@@ -4479,7 +4839,7 @@
       <c r="AF35" s="13"/>
       <c r="AG35" s="13"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>29</v>
       </c>
@@ -4524,7 +4884,7 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>30</v>
       </c>
@@ -4569,7 +4929,7 @@
       <c r="AF37" s="13"/>
       <c r="AG37" s="13"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>31</v>
       </c>
@@ -4614,7 +4974,7 @@
       <c r="AF38" s="13"/>
       <c r="AG38" s="13"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>32</v>
       </c>
@@ -4659,7 +5019,7 @@
       <c r="AF39" s="13"/>
       <c r="AG39" s="13"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>33</v>
       </c>
@@ -4704,7 +5064,7 @@
       <c r="AF40" s="13"/>
       <c r="AG40" s="13"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>34</v>
       </c>
@@ -4749,7 +5109,7 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>35</v>
       </c>
@@ -4794,7 +5154,7 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>36</v>
       </c>
@@ -4839,7 +5199,7 @@
       <c r="AF43" s="13"/>
       <c r="AG43" s="13"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>37</v>
       </c>
@@ -4884,7 +5244,7 @@
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>38</v>
       </c>
@@ -4929,7 +5289,7 @@
       <c r="AF45" s="13"/>
       <c r="AG45" s="13"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>39</v>
       </c>
@@ -4974,7 +5334,7 @@
       <c r="AF46" s="13"/>
       <c r="AG46" s="13"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>40</v>
       </c>
@@ -5019,7 +5379,7 @@
       <c r="AF47" s="13"/>
       <c r="AG47" s="13"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>41</v>
       </c>
@@ -5064,7 +5424,7 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>42</v>
       </c>
@@ -5109,7 +5469,7 @@
       <c r="AF49" s="13"/>
       <c r="AG49" s="13"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>43</v>
       </c>
@@ -5154,7 +5514,7 @@
       <c r="AF50" s="13"/>
       <c r="AG50" s="13"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>44</v>
       </c>
@@ -5199,7 +5559,7 @@
       <c r="AF51" s="13"/>
       <c r="AG51" s="13"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>45</v>
       </c>
@@ -5244,7 +5604,7 @@
       <c r="AF52" s="13"/>
       <c r="AG52" s="13"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>46</v>
       </c>
@@ -5289,7 +5649,7 @@
       <c r="AF53" s="13"/>
       <c r="AG53" s="13"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>47</v>
       </c>
@@ -5334,7 +5694,7 @@
       <c r="AF54" s="13"/>
       <c r="AG54" s="13"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>48</v>
       </c>
@@ -5379,7 +5739,7 @@
       <c r="AF55" s="13"/>
       <c r="AG55" s="13"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>49</v>
       </c>
@@ -5424,7 +5784,7 @@
       <c r="AF56" s="13"/>
       <c r="AG56" s="13"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>50</v>
       </c>
@@ -5469,7 +5829,7 @@
       <c r="AF57" s="13"/>
       <c r="AG57" s="13"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>51</v>
       </c>
@@ -5514,7 +5874,7 @@
       <c r="AF58" s="13"/>
       <c r="AG58" s="13"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>52</v>
       </c>
@@ -5559,7 +5919,7 @@
       <c r="AF59" s="13"/>
       <c r="AG59" s="13"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>53</v>
       </c>
@@ -5604,7 +5964,7 @@
       <c r="AF60" s="13"/>
       <c r="AG60" s="13"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>54</v>
       </c>
@@ -5649,7 +6009,7 @@
       <c r="AF61" s="13"/>
       <c r="AG61" s="13"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>55</v>
       </c>
@@ -5694,7 +6054,7 @@
       <c r="AF62" s="13"/>
       <c r="AG62" s="13"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>56</v>
       </c>
@@ -5739,7 +6099,7 @@
       <c r="AF63" s="13"/>
       <c r="AG63" s="13"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>57</v>
       </c>
@@ -5784,7 +6144,7 @@
       <c r="AF64" s="13"/>
       <c r="AG64" s="13"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>58</v>
       </c>
@@ -5829,7 +6189,7 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>59</v>
       </c>
@@ -5874,7 +6234,7 @@
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>60</v>
       </c>
@@ -5919,7 +6279,7 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>61</v>
       </c>
@@ -5964,7 +6324,7 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>62</v>
       </c>
@@ -6009,7 +6369,7 @@
       <c r="AF69" s="13"/>
       <c r="AG69" s="13"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>63</v>
       </c>
@@ -6054,7 +6414,7 @@
       <c r="AF70" s="13"/>
       <c r="AG70" s="13"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>64</v>
       </c>
@@ -6099,7 +6459,7 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>65</v>
       </c>
@@ -6144,7 +6504,7 @@
       <c r="AF72" s="13"/>
       <c r="AG72" s="13"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>66</v>
       </c>
@@ -6189,7 +6549,7 @@
       <c r="AF73" s="13"/>
       <c r="AG73" s="13"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>67</v>
       </c>
@@ -6234,7 +6594,7 @@
       <c r="AF74" s="13"/>
       <c r="AG74" s="13"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>68</v>
       </c>
@@ -6279,7 +6639,7 @@
       <c r="AF75" s="13"/>
       <c r="AG75" s="13"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>69</v>
       </c>
@@ -6324,7 +6684,7 @@
       <c r="AF76" s="13"/>
       <c r="AG76" s="13"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>70</v>
       </c>
@@ -6369,7 +6729,7 @@
       <c r="AF77" s="13"/>
       <c r="AG77" s="13"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>71</v>
       </c>
@@ -6414,7 +6774,7 @@
       <c r="AF78" s="13"/>
       <c r="AG78" s="13"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>72</v>
       </c>
@@ -6459,7 +6819,7 @@
       <c r="AF79" s="13"/>
       <c r="AG79" s="13"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>73</v>
       </c>
@@ -6504,7 +6864,7 @@
       <c r="AF80" s="13"/>
       <c r="AG80" s="13"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
         <v>74</v>
       </c>
@@ -6549,7 +6909,7 @@
       <c r="AF81" s="13"/>
       <c r="AG81" s="13"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>75</v>
       </c>
@@ -6594,7 +6954,7 @@
       <c r="AF82" s="13"/>
       <c r="AG82" s="13"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="11">
         <v>76</v>
       </c>
@@ -6639,7 +6999,7 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
         <v>77</v>
       </c>
@@ -6684,7 +7044,7 @@
       <c r="AF84" s="13"/>
       <c r="AG84" s="13"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
         <v>78</v>
       </c>
@@ -6729,7 +7089,7 @@
       <c r="AF85" s="13"/>
       <c r="AG85" s="13"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>79</v>
       </c>
@@ -6774,7 +7134,7 @@
       <c r="AF86" s="13"/>
       <c r="AG86" s="13"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>80</v>
       </c>
@@ -6819,7 +7179,7 @@
       <c r="AF87" s="13"/>
       <c r="AG87" s="13"/>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="11">
         <v>81</v>
       </c>
@@ -6864,7 +7224,7 @@
       <c r="AF88" s="13"/>
       <c r="AG88" s="13"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>82</v>
       </c>
@@ -6909,7 +7269,7 @@
       <c r="AF89" s="13"/>
       <c r="AG89" s="13"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>83</v>
       </c>
@@ -6954,7 +7314,7 @@
       <c r="AF90" s="13"/>
       <c r="AG90" s="13"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
         <v>84</v>
       </c>
@@ -6999,7 +7359,7 @@
       <c r="AF91" s="13"/>
       <c r="AG91" s="13"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>85</v>
       </c>
@@ -7044,7 +7404,7 @@
       <c r="AF92" s="13"/>
       <c r="AG92" s="13"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" s="11">
         <v>86</v>
       </c>
@@ -7089,7 +7449,7 @@
       <c r="AF93" s="13"/>
       <c r="AG93" s="13"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" s="11">
         <v>87</v>
       </c>
@@ -7134,7 +7494,7 @@
       <c r="AF94" s="13"/>
       <c r="AG94" s="13"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" s="11">
         <v>88</v>
       </c>
@@ -7179,7 +7539,7 @@
       <c r="AF95" s="13"/>
       <c r="AG95" s="13"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" s="11">
         <v>89</v>
       </c>
@@ -7224,7 +7584,7 @@
       <c r="AF96" s="13"/>
       <c r="AG96" s="13"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" s="11">
         <v>90</v>
       </c>
@@ -7269,7 +7629,7 @@
       <c r="AF97" s="13"/>
       <c r="AG97" s="13"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" s="11">
         <v>91</v>
       </c>
@@ -7314,7 +7674,7 @@
       <c r="AF98" s="13"/>
       <c r="AG98" s="13"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" s="11">
         <v>92</v>
       </c>
@@ -7359,7 +7719,7 @@
       <c r="AF99" s="13"/>
       <c r="AG99" s="13"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" s="11">
         <v>93</v>
       </c>
@@ -7404,7 +7764,7 @@
       <c r="AF100" s="13"/>
       <c r="AG100" s="13"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" s="11">
         <v>94</v>
       </c>
@@ -7449,7 +7809,7 @@
       <c r="AF101" s="13"/>
       <c r="AG101" s="13"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" s="11">
         <v>95</v>
       </c>
@@ -7494,7 +7854,7 @@
       <c r="AF102" s="13"/>
       <c r="AG102" s="13"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" s="11">
         <v>96</v>
       </c>
@@ -7539,7 +7899,7 @@
       <c r="AF103" s="13"/>
       <c r="AG103" s="13"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" s="11">
         <v>97</v>
       </c>
@@ -7584,7 +7944,7 @@
       <c r="AF104" s="13"/>
       <c r="AG104" s="13"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" s="11">
         <v>98</v>
       </c>
@@ -7629,7 +7989,7 @@
       <c r="AF105" s="13"/>
       <c r="AG105" s="13"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" s="11">
         <v>99</v>
       </c>
@@ -7674,7 +8034,7 @@
       <c r="AF106" s="13"/>
       <c r="AG106" s="13"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" s="11">
         <v>100</v>
       </c>
@@ -7719,7 +8079,7 @@
       <c r="AF107" s="13"/>
       <c r="AG107" s="13"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" s="11">
         <v>101</v>
       </c>
@@ -7764,7 +8124,7 @@
       <c r="AF108" s="13"/>
       <c r="AG108" s="13"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" s="11">
         <v>102</v>
       </c>
@@ -7809,7 +8169,7 @@
       <c r="AF109" s="13"/>
       <c r="AG109" s="13"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" s="11">
         <v>103</v>
       </c>
@@ -7854,7 +8214,7 @@
       <c r="AF110" s="13"/>
       <c r="AG110" s="13"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" s="11">
         <v>104</v>
       </c>
@@ -7899,7 +8259,7 @@
       <c r="AF111" s="13"/>
       <c r="AG111" s="13"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" s="11">
         <v>105</v>
       </c>
@@ -7944,7 +8304,7 @@
       <c r="AF112" s="13"/>
       <c r="AG112" s="13"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" s="11">
         <v>106</v>
       </c>
@@ -7989,7 +8349,7 @@
       <c r="AF113" s="13"/>
       <c r="AG113" s="13"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" s="11">
         <v>107</v>
       </c>
@@ -8034,7 +8394,7 @@
       <c r="AF114" s="13"/>
       <c r="AG114" s="13"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" s="11">
         <v>108</v>
       </c>
@@ -8079,7 +8439,7 @@
       <c r="AF115" s="13"/>
       <c r="AG115" s="13"/>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" s="11">
         <v>109</v>
       </c>
@@ -8124,7 +8484,7 @@
       <c r="AF116" s="13"/>
       <c r="AG116" s="13"/>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" s="11">
         <v>110</v>
       </c>
@@ -8169,7 +8529,7 @@
       <c r="AF117" s="13"/>
       <c r="AG117" s="13"/>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" s="11">
         <v>111</v>
       </c>
@@ -8214,7 +8574,7 @@
       <c r="AF118" s="13"/>
       <c r="AG118" s="13"/>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" s="11">
         <v>112</v>
       </c>
@@ -8259,7 +8619,7 @@
       <c r="AF119" s="13"/>
       <c r="AG119" s="13"/>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" s="11">
         <v>113</v>
       </c>
@@ -8304,7 +8664,7 @@
       <c r="AF120" s="13"/>
       <c r="AG120" s="13"/>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" s="11">
         <v>114</v>
       </c>
@@ -8349,7 +8709,7 @@
       <c r="AF121" s="13"/>
       <c r="AG121" s="13"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" s="11">
         <v>115</v>
       </c>
@@ -8394,7 +8754,7 @@
       <c r="AF122" s="13"/>
       <c r="AG122" s="13"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" s="11">
         <v>116</v>
       </c>
@@ -8439,7 +8799,7 @@
       <c r="AF123" s="13"/>
       <c r="AG123" s="13"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" s="11">
         <v>117</v>
       </c>
@@ -8484,7 +8844,7 @@
       <c r="AF124" s="13"/>
       <c r="AG124" s="13"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" s="11">
         <v>118</v>
       </c>
@@ -8529,7 +8889,7 @@
       <c r="AF125" s="13"/>
       <c r="AG125" s="13"/>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" s="11">
         <v>119</v>
       </c>
@@ -8574,7 +8934,7 @@
       <c r="AF126" s="13"/>
       <c r="AG126" s="13"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" s="11">
         <v>120</v>
       </c>
@@ -8619,7 +8979,7 @@
       <c r="AF127" s="13"/>
       <c r="AG127" s="13"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" s="11">
         <v>121</v>
       </c>
@@ -8664,7 +9024,7 @@
       <c r="AF128" s="13"/>
       <c r="AG128" s="13"/>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" s="11">
         <v>122</v>
       </c>
@@ -8709,7 +9069,7 @@
       <c r="AF129" s="13"/>
       <c r="AG129" s="13"/>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" s="11">
         <v>123</v>
       </c>
@@ -8754,7 +9114,7 @@
       <c r="AF130" s="13"/>
       <c r="AG130" s="13"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" s="11">
         <v>124</v>
       </c>
@@ -8799,7 +9159,7 @@
       <c r="AF131" s="13"/>
       <c r="AG131" s="13"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" s="11">
         <v>125</v>
       </c>
@@ -8844,7 +9204,7 @@
       <c r="AF132" s="13"/>
       <c r="AG132" s="13"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" s="11">
         <v>126</v>
       </c>
@@ -8889,7 +9249,7 @@
       <c r="AF133" s="13"/>
       <c r="AG133" s="13"/>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" s="11">
         <v>127</v>
       </c>
@@ -8934,7 +9294,7 @@
       <c r="AF134" s="13"/>
       <c r="AG134" s="13"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" s="11">
         <v>128</v>
       </c>
@@ -8979,7 +9339,7 @@
       <c r="AF135" s="13"/>
       <c r="AG135" s="13"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" s="11">
         <v>129</v>
       </c>
@@ -9024,7 +9384,7 @@
       <c r="AF136" s="13"/>
       <c r="AG136" s="13"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" s="11">
         <v>130</v>
       </c>
@@ -9069,7 +9429,7 @@
       <c r="AF137" s="13"/>
       <c r="AG137" s="13"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" s="11">
         <v>131</v>
       </c>
@@ -9114,7 +9474,7 @@
       <c r="AF138" s="13"/>
       <c r="AG138" s="13"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" s="11">
         <v>132</v>
       </c>
@@ -9159,7 +9519,7 @@
       <c r="AF139" s="13"/>
       <c r="AG139" s="13"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" s="11">
         <v>133</v>
       </c>
@@ -9204,7 +9564,7 @@
       <c r="AF140" s="13"/>
       <c r="AG140" s="13"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" s="11">
         <v>134</v>
       </c>
@@ -9249,7 +9609,7 @@
       <c r="AF141" s="13"/>
       <c r="AG141" s="13"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" s="11">
         <v>135</v>
       </c>
@@ -9294,7 +9654,7 @@
       <c r="AF142" s="13"/>
       <c r="AG142" s="13"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" s="11">
         <v>136</v>
       </c>
@@ -9339,7 +9699,7 @@
       <c r="AF143" s="13"/>
       <c r="AG143" s="13"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" s="11">
         <v>137</v>
       </c>
@@ -9384,7 +9744,7 @@
       <c r="AF144" s="13"/>
       <c r="AG144" s="13"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" s="11">
         <v>138</v>
       </c>
@@ -9429,7 +9789,7 @@
       <c r="AF145" s="13"/>
       <c r="AG145" s="13"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" s="11">
         <v>139</v>
       </c>
@@ -9474,7 +9834,7 @@
       <c r="AF146" s="13"/>
       <c r="AG146" s="13"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" s="11">
         <v>140</v>
       </c>
@@ -9519,7 +9879,7 @@
       <c r="AF147" s="13"/>
       <c r="AG147" s="13"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" s="11">
         <v>141</v>
       </c>
@@ -9564,7 +9924,7 @@
       <c r="AF148" s="13"/>
       <c r="AG148" s="13"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" s="11">
         <v>142</v>
       </c>
@@ -9609,7 +9969,7 @@
       <c r="AF149" s="13"/>
       <c r="AG149" s="13"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" s="11">
         <v>143</v>
       </c>
@@ -9654,7 +10014,7 @@
       <c r="AF150" s="13"/>
       <c r="AG150" s="13"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" s="11">
         <v>144</v>
       </c>
@@ -9699,7 +10059,7 @@
       <c r="AF151" s="13"/>
       <c r="AG151" s="13"/>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
         <v>145</v>
       </c>
@@ -9744,7 +10104,7 @@
       <c r="AF152" s="13"/>
       <c r="AG152" s="13"/>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
         <v>146</v>
       </c>
@@ -9789,7 +10149,7 @@
       <c r="AF153" s="13"/>
       <c r="AG153" s="13"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" s="11">
         <v>147</v>
       </c>
@@ -9834,7 +10194,7 @@
       <c r="AF154" s="13"/>
       <c r="AG154" s="13"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" s="11">
         <v>148</v>
       </c>
@@ -9879,7 +10239,7 @@
       <c r="AF155" s="13"/>
       <c r="AG155" s="13"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" s="11">
         <v>149</v>
       </c>
@@ -9924,7 +10284,7 @@
       <c r="AF156" s="13"/>
       <c r="AG156" s="13"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" s="11">
         <v>150</v>
       </c>
@@ -9969,7 +10329,7 @@
       <c r="AF157" s="13"/>
       <c r="AG157" s="13"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" s="11">
         <v>151</v>
       </c>
@@ -10014,7 +10374,7 @@
       <c r="AF158" s="13"/>
       <c r="AG158" s="13"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" s="11">
         <v>152</v>
       </c>
@@ -10059,7 +10419,7 @@
       <c r="AF159" s="13"/>
       <c r="AG159" s="13"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" s="11">
         <v>153</v>
       </c>
@@ -10104,7 +10464,7 @@
       <c r="AF160" s="13"/>
       <c r="AG160" s="13"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" s="11">
         <v>154</v>
       </c>
@@ -10149,7 +10509,7 @@
       <c r="AF161" s="13"/>
       <c r="AG161" s="13"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" s="11">
         <v>155</v>
       </c>
@@ -10194,7 +10554,7 @@
       <c r="AF162" s="13"/>
       <c r="AG162" s="13"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" s="11">
         <v>156</v>
       </c>
@@ -10239,7 +10599,7 @@
       <c r="AF163" s="13"/>
       <c r="AG163" s="13"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" s="11">
         <v>157</v>
       </c>
@@ -10284,7 +10644,7 @@
       <c r="AF164" s="13"/>
       <c r="AG164" s="13"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" s="11">
         <v>158</v>
       </c>
@@ -10329,7 +10689,7 @@
       <c r="AF165" s="13"/>
       <c r="AG165" s="13"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" s="11">
         <v>159</v>
       </c>
@@ -10374,7 +10734,7 @@
       <c r="AF166" s="13"/>
       <c r="AG166" s="13"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" s="11">
         <v>160</v>
       </c>
@@ -10419,7 +10779,7 @@
       <c r="AF167" s="13"/>
       <c r="AG167" s="13"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" s="11">
         <v>161</v>
       </c>
@@ -10464,7 +10824,7 @@
       <c r="AF168" s="13"/>
       <c r="AG168" s="13"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" s="11">
         <v>162</v>
       </c>
@@ -10509,7 +10869,7 @@
       <c r="AF169" s="13"/>
       <c r="AG169" s="13"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" s="11">
         <v>163</v>
       </c>
@@ -10554,7 +10914,7 @@
       <c r="AF170" s="13"/>
       <c r="AG170" s="13"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" s="11">
         <v>164</v>
       </c>
@@ -10599,7 +10959,7 @@
       <c r="AF171" s="13"/>
       <c r="AG171" s="13"/>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172" s="11">
         <v>165</v>
       </c>
@@ -10644,7 +11004,7 @@
       <c r="AF172" s="13"/>
       <c r="AG172" s="13"/>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173" s="11">
         <v>166</v>
       </c>
@@ -10689,7 +11049,7 @@
       <c r="AF173" s="13"/>
       <c r="AG173" s="13"/>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174" s="11">
         <v>167</v>
       </c>
@@ -10734,7 +11094,7 @@
       <c r="AF174" s="13"/>
       <c r="AG174" s="13"/>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175" s="11">
         <v>168</v>
       </c>
@@ -10779,7 +11139,7 @@
       <c r="AF175" s="13"/>
       <c r="AG175" s="13"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176" s="11">
         <v>169</v>
       </c>
@@ -10824,7 +11184,7 @@
       <c r="AF176" s="13"/>
       <c r="AG176" s="13"/>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A177" s="11">
         <v>170</v>
       </c>
@@ -10869,7 +11229,7 @@
       <c r="AF177" s="13"/>
       <c r="AG177" s="13"/>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A178" s="11">
         <v>171</v>
       </c>
@@ -10914,7 +11274,7 @@
       <c r="AF178" s="13"/>
       <c r="AG178" s="13"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A179" s="11">
         <v>172</v>
       </c>
@@ -10959,7 +11319,7 @@
       <c r="AF179" s="13"/>
       <c r="AG179" s="13"/>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A180" s="11">
         <v>173</v>
       </c>
@@ -11004,7 +11364,7 @@
       <c r="AF180" s="13"/>
       <c r="AG180" s="13"/>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A181" s="11">
         <v>174</v>
       </c>
@@ -11049,7 +11409,7 @@
       <c r="AF181" s="13"/>
       <c r="AG181" s="13"/>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A182" s="11">
         <v>175</v>
       </c>
@@ -11094,7 +11454,7 @@
       <c r="AF182" s="13"/>
       <c r="AG182" s="13"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A183" s="11">
         <v>176</v>
       </c>
@@ -11139,7 +11499,7 @@
       <c r="AF183" s="13"/>
       <c r="AG183" s="13"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A184" s="11">
         <v>177</v>
       </c>
@@ -11184,7 +11544,7 @@
       <c r="AF184" s="13"/>
       <c r="AG184" s="13"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A185" s="11">
         <v>178</v>
       </c>
@@ -11229,7 +11589,7 @@
       <c r="AF185" s="13"/>
       <c r="AG185" s="13"/>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A186" s="11">
         <v>179</v>
       </c>
@@ -11274,7 +11634,7 @@
       <c r="AF186" s="13"/>
       <c r="AG186" s="13"/>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A187" s="11">
         <v>180</v>
       </c>
@@ -11319,7 +11679,7 @@
       <c r="AF187" s="13"/>
       <c r="AG187" s="13"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A188" s="11">
         <v>181</v>
       </c>
@@ -11364,7 +11724,7 @@
       <c r="AF188" s="13"/>
       <c r="AG188" s="13"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A189" s="11">
         <v>182</v>
       </c>
@@ -11409,7 +11769,7 @@
       <c r="AF189" s="13"/>
       <c r="AG189" s="13"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A190" s="11">
         <v>183</v>
       </c>
@@ -11454,7 +11814,7 @@
       <c r="AF190" s="13"/>
       <c r="AG190" s="13"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
         <v>184</v>
       </c>
@@ -11499,7 +11859,7 @@
       <c r="AF191" s="13"/>
       <c r="AG191" s="13"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
         <v>185</v>
       </c>
@@ -11544,7 +11904,7 @@
       <c r="AF192" s="13"/>
       <c r="AG192" s="13"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A193" s="11">
         <v>186</v>
       </c>
@@ -11589,7 +11949,7 @@
       <c r="AF193" s="13"/>
       <c r="AG193" s="13"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A194" s="11">
         <v>187</v>
       </c>
@@ -11634,7 +11994,7 @@
       <c r="AF194" s="13"/>
       <c r="AG194" s="13"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
         <v>188</v>
       </c>
@@ -11679,7 +12039,7 @@
       <c r="AF195" s="13"/>
       <c r="AG195" s="13"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
         <v>189</v>
       </c>
@@ -11724,7 +12084,7 @@
       <c r="AF196" s="13"/>
       <c r="AG196" s="13"/>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A197" s="11">
         <v>190</v>
       </c>
@@ -11769,7 +12129,7 @@
       <c r="AF197" s="13"/>
       <c r="AG197" s="13"/>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A198" s="11">
         <v>191</v>
       </c>
@@ -11814,7 +12174,7 @@
       <c r="AF198" s="13"/>
       <c r="AG198" s="13"/>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A199" s="11">
         <v>192</v>
       </c>
@@ -11859,7 +12219,7 @@
       <c r="AF199" s="13"/>
       <c r="AG199" s="13"/>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A200" s="11">
         <v>193</v>
       </c>
@@ -11904,7 +12264,7 @@
       <c r="AF200" s="13"/>
       <c r="AG200" s="13"/>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A201" s="11">
         <v>194</v>
       </c>
@@ -11949,7 +12309,7 @@
       <c r="AF201" s="13"/>
       <c r="AG201" s="13"/>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A202" s="11">
         <v>195</v>
       </c>
@@ -11994,7 +12354,7 @@
       <c r="AF202" s="13"/>
       <c r="AG202" s="13"/>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A203" s="11">
         <v>196</v>
       </c>
@@ -12039,7 +12399,7 @@
       <c r="AF203" s="13"/>
       <c r="AG203" s="13"/>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A204" s="11">
         <v>197</v>
       </c>
@@ -12084,7 +12444,7 @@
       <c r="AF204" s="13"/>
       <c r="AG204" s="13"/>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A205" s="11">
         <v>198</v>
       </c>
@@ -12129,7 +12489,7 @@
       <c r="AF205" s="13"/>
       <c r="AG205" s="13"/>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A206" s="11">
         <v>199</v>
       </c>
@@ -12174,7 +12534,7 @@
       <c r="AF206" s="13"/>
       <c r="AG206" s="13"/>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A207" s="11">
         <v>200</v>
       </c>
@@ -12219,7 +12579,7 @@
       <c r="AF207" s="13"/>
       <c r="AG207" s="13"/>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A208" s="11">
         <v>201</v>
       </c>
@@ -12264,7 +12624,7 @@
       <c r="AF208" s="13"/>
       <c r="AG208" s="13"/>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A209" s="11">
         <v>202</v>
       </c>
@@ -12309,7 +12669,7 @@
       <c r="AF209" s="13"/>
       <c r="AG209" s="13"/>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A210" s="11">
         <v>203</v>
       </c>
@@ -12354,7 +12714,7 @@
       <c r="AF210" s="13"/>
       <c r="AG210" s="13"/>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A211" s="11">
         <v>204</v>
       </c>
@@ -12399,7 +12759,7 @@
       <c r="AF211" s="13"/>
       <c r="AG211" s="13"/>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A212" s="11">
         <v>205</v>
       </c>
@@ -12444,7 +12804,7 @@
       <c r="AF212" s="13"/>
       <c r="AG212" s="13"/>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A213" s="11">
         <v>206</v>
       </c>
@@ -12489,7 +12849,7 @@
       <c r="AF213" s="13"/>
       <c r="AG213" s="13"/>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A214" s="11">
         <v>207</v>
       </c>
@@ -12534,7 +12894,7 @@
       <c r="AF214" s="13"/>
       <c r="AG214" s="13"/>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A215" s="11">
         <v>208</v>
       </c>
@@ -12579,7 +12939,7 @@
       <c r="AF215" s="13"/>
       <c r="AG215" s="13"/>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A216" s="11">
         <v>209</v>
       </c>
@@ -12624,7 +12984,7 @@
       <c r="AF216" s="13"/>
       <c r="AG216" s="13"/>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A217" s="11">
         <v>210</v>
       </c>
@@ -12669,7 +13029,7 @@
       <c r="AF217" s="13"/>
       <c r="AG217" s="13"/>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A218" s="11">
         <v>211</v>
       </c>
@@ -12714,7 +13074,7 @@
       <c r="AF218" s="13"/>
       <c r="AG218" s="13"/>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A219" s="11">
         <v>212</v>
       </c>
@@ -12759,7 +13119,7 @@
       <c r="AF219" s="13"/>
       <c r="AG219" s="13"/>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A220" s="11">
         <v>213</v>
       </c>
@@ -12804,7 +13164,7 @@
       <c r="AF220" s="13"/>
       <c r="AG220" s="13"/>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A221" s="11">
         <v>214</v>
       </c>
@@ -12849,7 +13209,7 @@
       <c r="AF221" s="13"/>
       <c r="AG221" s="13"/>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A222" s="11">
         <v>215</v>
       </c>
@@ -12894,7 +13254,7 @@
       <c r="AF222" s="13"/>
       <c r="AG222" s="13"/>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A223" s="11">
         <v>216</v>
       </c>
@@ -12939,7 +13299,7 @@
       <c r="AF223" s="13"/>
       <c r="AG223" s="13"/>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A224" s="11">
         <v>217</v>
       </c>
@@ -12984,7 +13344,7 @@
       <c r="AF224" s="13"/>
       <c r="AG224" s="13"/>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A225" s="11">
         <v>218</v>
       </c>
@@ -13029,7 +13389,7 @@
       <c r="AF225" s="13"/>
       <c r="AG225" s="13"/>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A226" s="11">
         <v>219</v>
       </c>
@@ -13074,7 +13434,7 @@
       <c r="AF226" s="13"/>
       <c r="AG226" s="13"/>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A227" s="11">
         <v>220</v>
       </c>
@@ -13119,7 +13479,7 @@
       <c r="AF227" s="13"/>
       <c r="AG227" s="13"/>
     </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A228" s="11">
         <v>221</v>
       </c>
@@ -13164,7 +13524,7 @@
       <c r="AF228" s="13"/>
       <c r="AG228" s="13"/>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A229" s="11">
         <v>222</v>
       </c>
@@ -13209,7 +13569,7 @@
       <c r="AF229" s="13"/>
       <c r="AG229" s="13"/>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A230" s="11">
         <v>223</v>
       </c>
@@ -13254,7 +13614,7 @@
       <c r="AF230" s="13"/>
       <c r="AG230" s="13"/>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A231" s="11">
         <v>224</v>
       </c>
@@ -13299,7 +13659,7 @@
       <c r="AF231" s="13"/>
       <c r="AG231" s="13"/>
     </row>
-    <row r="232" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A232" s="11">
         <v>225</v>
       </c>
@@ -13344,7 +13704,7 @@
       <c r="AF232" s="13"/>
       <c r="AG232" s="13"/>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A233" s="11">
         <v>226</v>
       </c>
@@ -13389,7 +13749,7 @@
       <c r="AF233" s="13"/>
       <c r="AG233" s="13"/>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A234" s="11">
         <v>227</v>
       </c>
@@ -13434,7 +13794,7 @@
       <c r="AF234" s="13"/>
       <c r="AG234" s="13"/>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A235" s="11">
         <v>228</v>
       </c>
@@ -13479,7 +13839,7 @@
       <c r="AF235" s="13"/>
       <c r="AG235" s="13"/>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A236" s="11">
         <v>229</v>
       </c>
@@ -13524,7 +13884,7 @@
       <c r="AF236" s="13"/>
       <c r="AG236" s="13"/>
     </row>
-    <row r="237" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A237" s="11">
         <v>230</v>
       </c>
@@ -13569,7 +13929,7 @@
       <c r="AF237" s="13"/>
       <c r="AG237" s="13"/>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A238" s="11">
         <v>231</v>
       </c>
@@ -13614,7 +13974,7 @@
       <c r="AF238" s="13"/>
       <c r="AG238" s="13"/>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A239" s="11">
         <v>232</v>
       </c>
@@ -13659,7 +14019,7 @@
       <c r="AF239" s="13"/>
       <c r="AG239" s="13"/>
     </row>
-    <row r="240" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A240" s="11">
         <v>233</v>
       </c>
@@ -13704,7 +14064,7 @@
       <c r="AF240" s="13"/>
       <c r="AG240" s="13"/>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A241" s="11">
         <v>234</v>
       </c>
@@ -13749,7 +14109,7 @@
       <c r="AF241" s="13"/>
       <c r="AG241" s="13"/>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A242" s="11">
         <v>235</v>
       </c>
@@ -13794,7 +14154,7 @@
       <c r="AF242" s="13"/>
       <c r="AG242" s="13"/>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A243" s="11">
         <v>236</v>
       </c>
@@ -13839,7 +14199,7 @@
       <c r="AF243" s="13"/>
       <c r="AG243" s="13"/>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A244" s="11">
         <v>237</v>
       </c>
@@ -13884,7 +14244,7 @@
       <c r="AF244" s="13"/>
       <c r="AG244" s="13"/>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A245" s="11">
         <v>238</v>
       </c>
@@ -13929,7 +14289,7 @@
       <c r="AF245" s="13"/>
       <c r="AG245" s="13"/>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A246" s="11">
         <v>239</v>
       </c>
@@ -13974,7 +14334,7 @@
       <c r="AF246" s="13"/>
       <c r="AG246" s="13"/>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A247" s="11">
         <v>240</v>
       </c>
@@ -14019,7 +14379,7 @@
       <c r="AF247" s="13"/>
       <c r="AG247" s="13"/>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A248" s="11">
         <v>241</v>
       </c>
@@ -14064,7 +14424,7 @@
       <c r="AF248" s="13"/>
       <c r="AG248" s="13"/>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A249" s="11">
         <v>242</v>
       </c>
@@ -14109,7 +14469,7 @@
       <c r="AF249" s="13"/>
       <c r="AG249" s="13"/>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A250" s="11">
         <v>243</v>
       </c>
@@ -14154,7 +14514,7 @@
       <c r="AF250" s="13"/>
       <c r="AG250" s="13"/>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A251" s="11">
         <v>244</v>
       </c>
@@ -14199,7 +14559,7 @@
       <c r="AF251" s="13"/>
       <c r="AG251" s="13"/>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A252" s="11">
         <v>245</v>
       </c>
@@ -14244,7 +14604,7 @@
       <c r="AF252" s="13"/>
       <c r="AG252" s="13"/>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A253" s="11">
         <v>246</v>
       </c>
@@ -14289,7 +14649,7 @@
       <c r="AF253" s="13"/>
       <c r="AG253" s="13"/>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A254" s="11">
         <v>247</v>
       </c>
@@ -14334,7 +14694,7 @@
       <c r="AF254" s="13"/>
       <c r="AG254" s="13"/>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A255" s="11">
         <v>248</v>
       </c>
@@ -14379,7 +14739,7 @@
       <c r="AF255" s="13"/>
       <c r="AG255" s="13"/>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A256" s="11">
         <v>249</v>
       </c>
@@ -14424,7 +14784,7 @@
       <c r="AF256" s="13"/>
       <c r="AG256" s="13"/>
     </row>
-    <row r="257" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A257" s="11">
         <v>250</v>
       </c>
@@ -14469,7 +14829,7 @@
       <c r="AF257" s="13"/>
       <c r="AG257" s="13"/>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A258" s="11">
         <v>251</v>
       </c>
@@ -14514,7 +14874,7 @@
       <c r="AF258" s="13"/>
       <c r="AG258" s="13"/>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A259" s="11">
         <v>252</v>
       </c>
@@ -14559,7 +14919,7 @@
       <c r="AF259" s="13"/>
       <c r="AG259" s="13"/>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A260" s="11">
         <v>253</v>
       </c>
@@ -14604,7 +14964,7 @@
       <c r="AF260" s="13"/>
       <c r="AG260" s="13"/>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A261" s="11">
         <v>254</v>
       </c>
@@ -14649,7 +15009,7 @@
       <c r="AF261" s="13"/>
       <c r="AG261" s="13"/>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A262" s="11">
         <v>255</v>
       </c>
@@ -14694,7 +15054,7 @@
       <c r="AF262" s="13"/>
       <c r="AG262" s="13"/>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A263" s="11">
         <v>256</v>
       </c>
@@ -14739,7 +15099,7 @@
       <c r="AF263" s="13"/>
       <c r="AG263" s="13"/>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A264" s="11">
         <v>257</v>
       </c>
@@ -14784,7 +15144,7 @@
       <c r="AF264" s="13"/>
       <c r="AG264" s="13"/>
     </row>
-    <row r="265" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A265" s="11">
         <v>258</v>
       </c>
@@ -14829,7 +15189,7 @@
       <c r="AF265" s="13"/>
       <c r="AG265" s="13"/>
     </row>
-    <row r="266" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A266" s="11">
         <v>259</v>
       </c>
@@ -14874,7 +15234,7 @@
       <c r="AF266" s="13"/>
       <c r="AG266" s="13"/>
     </row>
-    <row r="267" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A267" s="11">
         <v>260</v>
       </c>
@@ -14919,7 +15279,7 @@
       <c r="AF267" s="13"/>
       <c r="AG267" s="13"/>
     </row>
-    <row r="268" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A268" s="11">
         <v>261</v>
       </c>
@@ -14964,7 +15324,7 @@
       <c r="AF268" s="13"/>
       <c r="AG268" s="13"/>
     </row>
-    <row r="269" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A269" s="11">
         <v>262</v>
       </c>
@@ -15009,7 +15369,7 @@
       <c r="AF269" s="13"/>
       <c r="AG269" s="13"/>
     </row>
-    <row r="270" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A270" s="11">
         <v>263</v>
       </c>
@@ -15054,7 +15414,7 @@
       <c r="AF270" s="13"/>
       <c r="AG270" s="13"/>
     </row>
-    <row r="271" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A271" s="11">
         <v>264</v>
       </c>
@@ -15099,7 +15459,7 @@
       <c r="AF271" s="13"/>
       <c r="AG271" s="13"/>
     </row>
-    <row r="272" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A272" s="11">
         <v>265</v>
       </c>
@@ -15144,7 +15504,7 @@
       <c r="AF272" s="13"/>
       <c r="AG272" s="13"/>
     </row>
-    <row r="273" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A273" s="11">
         <v>266</v>
       </c>
@@ -15189,7 +15549,7 @@
       <c r="AF273" s="13"/>
       <c r="AG273" s="13"/>
     </row>
-    <row r="274" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A274" s="11">
         <v>267</v>
       </c>
@@ -15234,7 +15594,7 @@
       <c r="AF274" s="13"/>
       <c r="AG274" s="13"/>
     </row>
-    <row r="275" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A275" s="11">
         <v>268</v>
       </c>
@@ -15279,7 +15639,7 @@
       <c r="AF275" s="13"/>
       <c r="AG275" s="13"/>
     </row>
-    <row r="276" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A276" s="11">
         <v>269</v>
       </c>
@@ -15324,7 +15684,7 @@
       <c r="AF276" s="13"/>
       <c r="AG276" s="13"/>
     </row>
-    <row r="277" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A277" s="11">
         <v>270</v>
       </c>
@@ -15369,7 +15729,7 @@
       <c r="AF277" s="13"/>
       <c r="AG277" s="13"/>
     </row>
-    <row r="278" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A278" s="11">
         <v>271</v>
       </c>
@@ -15414,7 +15774,7 @@
       <c r="AF278" s="13"/>
       <c r="AG278" s="13"/>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A279" s="11">
         <v>272</v>
       </c>
@@ -15459,7 +15819,7 @@
       <c r="AF279" s="13"/>
       <c r="AG279" s="13"/>
     </row>
-    <row r="280" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A280" s="11">
         <v>273</v>
       </c>
@@ -15504,7 +15864,7 @@
       <c r="AF280" s="13"/>
       <c r="AG280" s="13"/>
     </row>
-    <row r="281" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A281" s="11">
         <v>274</v>
       </c>
@@ -15549,7 +15909,7 @@
       <c r="AF281" s="13"/>
       <c r="AG281" s="13"/>
     </row>
-    <row r="282" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A282" s="11">
         <v>275</v>
       </c>
@@ -15594,7 +15954,7 @@
       <c r="AF282" s="13"/>
       <c r="AG282" s="13"/>
     </row>
-    <row r="283" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A283" s="11">
         <v>276</v>
       </c>
@@ -15639,7 +15999,7 @@
       <c r="AF283" s="13"/>
       <c r="AG283" s="13"/>
     </row>
-    <row r="284" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A284" s="11">
         <v>277</v>
       </c>
@@ -15684,7 +16044,7 @@
       <c r="AF284" s="13"/>
       <c r="AG284" s="13"/>
     </row>
-    <row r="285" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A285" s="11">
         <v>278</v>
       </c>
@@ -15729,7 +16089,7 @@
       <c r="AF285" s="13"/>
       <c r="AG285" s="13"/>
     </row>
-    <row r="286" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A286" s="11">
         <v>279</v>
       </c>
@@ -15774,7 +16134,7 @@
       <c r="AF286" s="13"/>
       <c r="AG286" s="13"/>
     </row>
-    <row r="287" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A287" s="11">
         <v>280</v>
       </c>
@@ -15819,7 +16179,7 @@
       <c r="AF287" s="13"/>
       <c r="AG287" s="13"/>
     </row>
-    <row r="288" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A288" s="11">
         <v>281</v>
       </c>
@@ -15864,7 +16224,7 @@
       <c r="AF288" s="13"/>
       <c r="AG288" s="13"/>
     </row>
-    <row r="289" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A289" s="11">
         <v>282</v>
       </c>
@@ -15909,7 +16269,7 @@
       <c r="AF289" s="13"/>
       <c r="AG289" s="13"/>
     </row>
-    <row r="290" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A290" s="11">
         <v>283</v>
       </c>
@@ -15954,7 +16314,7 @@
       <c r="AF290" s="13"/>
       <c r="AG290" s="13"/>
     </row>
-    <row r="291" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A291" s="11">
         <v>284</v>
       </c>
@@ -15999,7 +16359,7 @@
       <c r="AF291" s="13"/>
       <c r="AG291" s="13"/>
     </row>
-    <row r="292" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A292" s="11">
         <v>285</v>
       </c>
@@ -16044,7 +16404,7 @@
       <c r="AF292" s="13"/>
       <c r="AG292" s="13"/>
     </row>
-    <row r="293" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A293" s="11">
         <v>286</v>
       </c>
@@ -16089,7 +16449,7 @@
       <c r="AF293" s="13"/>
       <c r="AG293" s="13"/>
     </row>
-    <row r="294" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A294" s="11">
         <v>287</v>
       </c>
@@ -16134,7 +16494,7 @@
       <c r="AF294" s="13"/>
       <c r="AG294" s="13"/>
     </row>
-    <row r="295" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A295" s="11">
         <v>288</v>
       </c>
@@ -16179,7 +16539,7 @@
       <c r="AF295" s="13"/>
       <c r="AG295" s="13"/>
     </row>
-    <row r="296" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A296" s="11">
         <v>289</v>
       </c>
@@ -16224,7 +16584,7 @@
       <c r="AF296" s="13"/>
       <c r="AG296" s="13"/>
     </row>
-    <row r="297" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A297" s="11">
         <v>290</v>
       </c>
@@ -16269,7 +16629,7 @@
       <c r="AF297" s="13"/>
       <c r="AG297" s="13"/>
     </row>
-    <row r="298" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A298" s="11">
         <v>291</v>
       </c>
@@ -16314,7 +16674,7 @@
       <c r="AF298" s="13"/>
       <c r="AG298" s="13"/>
     </row>
-    <row r="299" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A299" s="11">
         <v>292</v>
       </c>
@@ -16359,7 +16719,7 @@
       <c r="AF299" s="13"/>
       <c r="AG299" s="13"/>
     </row>
-    <row r="300" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A300" s="11">
         <v>293</v>
       </c>
@@ -16404,7 +16764,7 @@
       <c r="AF300" s="13"/>
       <c r="AG300" s="13"/>
     </row>
-    <row r="301" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A301" s="11">
         <v>294</v>
       </c>
@@ -16449,7 +16809,7 @@
       <c r="AF301" s="13"/>
       <c r="AG301" s="13"/>
     </row>
-    <row r="302" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A302" s="11">
         <v>295</v>
       </c>
@@ -16494,7 +16854,7 @@
       <c r="AF302" s="13"/>
       <c r="AG302" s="13"/>
     </row>
-    <row r="303" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A303" s="11">
         <v>296</v>
       </c>
@@ -16539,7 +16899,7 @@
       <c r="AF303" s="13"/>
       <c r="AG303" s="13"/>
     </row>
-    <row r="304" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A304" s="11">
         <v>297</v>
       </c>
@@ -16584,7 +16944,7 @@
       <c r="AF304" s="13"/>
       <c r="AG304" s="13"/>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A305" s="11">
         <v>298</v>
       </c>
@@ -16629,7 +16989,7 @@
       <c r="AF305" s="13"/>
       <c r="AG305" s="13"/>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A306" s="11">
         <v>299</v>
       </c>
@@ -16674,7 +17034,7 @@
       <c r="AF306" s="13"/>
       <c r="AG306" s="13"/>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A307" s="11">
         <v>300</v>
       </c>
@@ -16719,7 +17079,7 @@
       <c r="AF307" s="13"/>
       <c r="AG307" s="13"/>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A308" s="11">
         <v>301</v>
       </c>
@@ -16764,7 +17124,7 @@
       <c r="AF308" s="13"/>
       <c r="AG308" s="13"/>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A309" s="11">
         <v>302</v>
       </c>
@@ -16809,7 +17169,7 @@
       <c r="AF309" s="13"/>
       <c r="AG309" s="13"/>
     </row>
-    <row r="310" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A310" s="11">
         <v>303</v>
       </c>
@@ -16854,7 +17214,7 @@
       <c r="AF310" s="13"/>
       <c r="AG310" s="13"/>
     </row>
-    <row r="311" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A311" s="11">
         <v>304</v>
       </c>
@@ -16899,7 +17259,7 @@
       <c r="AF311" s="13"/>
       <c r="AG311" s="13"/>
     </row>
-    <row r="312" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A312" s="11">
         <v>305</v>
       </c>
@@ -16944,7 +17304,7 @@
       <c r="AF312" s="13"/>
       <c r="AG312" s="13"/>
     </row>
-    <row r="313" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A313" s="11">
         <v>306</v>
       </c>
@@ -16989,7 +17349,7 @@
       <c r="AF313" s="13"/>
       <c r="AG313" s="13"/>
     </row>
-    <row r="314" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A314" s="11">
         <v>307</v>
       </c>
@@ -17034,7 +17394,7 @@
       <c r="AF314" s="13"/>
       <c r="AG314" s="13"/>
     </row>
-    <row r="315" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A315" s="11">
         <v>308</v>
       </c>
@@ -17079,7 +17439,7 @@
       <c r="AF315" s="13"/>
       <c r="AG315" s="13"/>
     </row>
-    <row r="316" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A316" s="11">
         <v>309</v>
       </c>
@@ -17124,7 +17484,7 @@
       <c r="AF316" s="13"/>
       <c r="AG316" s="13"/>
     </row>
-    <row r="317" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A317" s="11">
         <v>310</v>
       </c>
@@ -17169,7 +17529,7 @@
       <c r="AF317" s="13"/>
       <c r="AG317" s="13"/>
     </row>
-    <row r="318" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A318" s="11">
         <v>311</v>
       </c>
@@ -17214,7 +17574,7 @@
       <c r="AF318" s="13"/>
       <c r="AG318" s="13"/>
     </row>
-    <row r="319" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A319" s="11">
         <v>312</v>
       </c>
@@ -17259,7 +17619,7 @@
       <c r="AF319" s="13"/>
       <c r="AG319" s="13"/>
     </row>
-    <row r="320" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A320" s="11">
         <v>313</v>
       </c>
@@ -17304,7 +17664,7 @@
       <c r="AF320" s="13"/>
       <c r="AG320" s="13"/>
     </row>
-    <row r="321" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A321" s="11">
         <v>314</v>
       </c>
@@ -17349,7 +17709,7 @@
       <c r="AF321" s="13"/>
       <c r="AG321" s="13"/>
     </row>
-    <row r="322" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A322" s="11">
         <v>315</v>
       </c>
@@ -17394,7 +17754,7 @@
       <c r="AF322" s="13"/>
       <c r="AG322" s="13"/>
     </row>
-    <row r="323" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A323" s="11">
         <v>316</v>
       </c>
@@ -17439,7 +17799,7 @@
       <c r="AF323" s="13"/>
       <c r="AG323" s="13"/>
     </row>
-    <row r="324" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A324" s="11">
         <v>317</v>
       </c>
@@ -17484,7 +17844,7 @@
       <c r="AF324" s="13"/>
       <c r="AG324" s="13"/>
     </row>
-    <row r="325" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A325" s="11">
         <v>318</v>
       </c>
@@ -17529,7 +17889,7 @@
       <c r="AF325" s="13"/>
       <c r="AG325" s="13"/>
     </row>
-    <row r="326" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A326" s="11">
         <v>319</v>
       </c>
@@ -17574,7 +17934,7 @@
       <c r="AF326" s="13"/>
       <c r="AG326" s="13"/>
     </row>
-    <row r="327" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A327" s="11">
         <v>320</v>
       </c>
@@ -17619,7 +17979,7 @@
       <c r="AF327" s="13"/>
       <c r="AG327" s="13"/>
     </row>
-    <row r="328" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A328" s="11">
         <v>321</v>
       </c>
@@ -17664,7 +18024,7 @@
       <c r="AF328" s="13"/>
       <c r="AG328" s="13"/>
     </row>
-    <row r="329" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A329" s="11">
         <v>322</v>
       </c>
@@ -17709,7 +18069,7 @@
       <c r="AF329" s="13"/>
       <c r="AG329" s="13"/>
     </row>
-    <row r="330" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A330" s="11">
         <v>323</v>
       </c>
@@ -17754,7 +18114,7 @@
       <c r="AF330" s="13"/>
       <c r="AG330" s="13"/>
     </row>
-    <row r="331" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A331" s="11">
         <v>324</v>
       </c>
@@ -17799,7 +18159,7 @@
       <c r="AF331" s="13"/>
       <c r="AG331" s="13"/>
     </row>
-    <row r="332" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A332" s="11">
         <v>325</v>
       </c>
@@ -17844,7 +18204,7 @@
       <c r="AF332" s="13"/>
       <c r="AG332" s="13"/>
     </row>
-    <row r="333" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A333" s="11">
         <v>326</v>
       </c>
@@ -17889,7 +18249,7 @@
       <c r="AF333" s="13"/>
       <c r="AG333" s="13"/>
     </row>
-    <row r="334" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A334" s="11">
         <v>327</v>
       </c>
@@ -17934,7 +18294,7 @@
       <c r="AF334" s="13"/>
       <c r="AG334" s="13"/>
     </row>
-    <row r="335" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A335" s="11">
         <v>328</v>
       </c>
@@ -17979,7 +18339,7 @@
       <c r="AF335" s="13"/>
       <c r="AG335" s="13"/>
     </row>
-    <row r="336" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A336" s="11">
         <v>329</v>
       </c>
@@ -18024,7 +18384,7 @@
       <c r="AF336" s="13"/>
       <c r="AG336" s="13"/>
     </row>
-    <row r="337" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A337" s="11">
         <v>330</v>
       </c>
@@ -18069,7 +18429,7 @@
       <c r="AF337" s="13"/>
       <c r="AG337" s="13"/>
     </row>
-    <row r="338" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A338" s="11">
         <v>331</v>
       </c>
@@ -18114,7 +18474,7 @@
       <c r="AF338" s="13"/>
       <c r="AG338" s="13"/>
     </row>
-    <row r="339" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A339" s="11">
         <v>332</v>
       </c>
@@ -18159,7 +18519,7 @@
       <c r="AF339" s="13"/>
       <c r="AG339" s="13"/>
     </row>
-    <row r="340" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A340" s="11">
         <v>333</v>
       </c>
@@ -18204,7 +18564,7 @@
       <c r="AF340" s="13"/>
       <c r="AG340" s="13"/>
     </row>
-    <row r="341" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A341" s="11">
         <v>334</v>
       </c>
@@ -18249,7 +18609,7 @@
       <c r="AF341" s="13"/>
       <c r="AG341" s="13"/>
     </row>
-    <row r="342" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A342" s="11">
         <v>335</v>
       </c>
@@ -18294,7 +18654,7 @@
       <c r="AF342" s="13"/>
       <c r="AG342" s="13"/>
     </row>
-    <row r="343" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A343" s="11">
         <v>336</v>
       </c>
@@ -18339,7 +18699,7 @@
       <c r="AF343" s="13"/>
       <c r="AG343" s="13"/>
     </row>
-    <row r="344" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A344" s="11">
         <v>337</v>
       </c>
@@ -18384,7 +18744,7 @@
       <c r="AF344" s="13"/>
       <c r="AG344" s="13"/>
     </row>
-    <row r="345" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A345" s="11">
         <v>338</v>
       </c>
@@ -18429,7 +18789,7 @@
       <c r="AF345" s="13"/>
       <c r="AG345" s="13"/>
     </row>
-    <row r="346" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A346" s="11">
         <v>339</v>
       </c>
@@ -18474,7 +18834,7 @@
       <c r="AF346" s="13"/>
       <c r="AG346" s="13"/>
     </row>
-    <row r="347" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A347" s="11">
         <v>340</v>
       </c>
@@ -18519,7 +18879,7 @@
       <c r="AF347" s="13"/>
       <c r="AG347" s="13"/>
     </row>
-    <row r="348" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A348" s="11">
         <v>341</v>
       </c>
@@ -18564,7 +18924,7 @@
       <c r="AF348" s="13"/>
       <c r="AG348" s="13"/>
     </row>
-    <row r="349" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A349" s="11">
         <v>342</v>
       </c>
@@ -18609,7 +18969,7 @@
       <c r="AF349" s="13"/>
       <c r="AG349" s="13"/>
     </row>
-    <row r="350" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A350" s="11">
         <v>343</v>
       </c>
@@ -18654,7 +19014,7 @@
       <c r="AF350" s="13"/>
       <c r="AG350" s="13"/>
     </row>
-    <row r="351" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A351" s="11">
         <v>344</v>
       </c>
@@ -18699,7 +19059,7 @@
       <c r="AF351" s="13"/>
       <c r="AG351" s="13"/>
     </row>
-    <row r="352" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A352" s="11">
         <v>345</v>
       </c>
@@ -18744,7 +19104,7 @@
       <c r="AF352" s="13"/>
       <c r="AG352" s="13"/>
     </row>
-    <row r="353" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A353" s="11">
         <v>346</v>
       </c>
@@ -18789,7 +19149,7 @@
       <c r="AF353" s="13"/>
       <c r="AG353" s="13"/>
     </row>
-    <row r="354" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A354" s="11">
         <v>347</v>
       </c>
@@ -18834,7 +19194,7 @@
       <c r="AF354" s="13"/>
       <c r="AG354" s="13"/>
     </row>
-    <row r="355" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A355" s="11">
         <v>348</v>
       </c>
@@ -18879,7 +19239,7 @@
       <c r="AF355" s="13"/>
       <c r="AG355" s="13"/>
     </row>
-    <row r="356" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A356" s="11">
         <v>349</v>
       </c>
@@ -18924,7 +19284,7 @@
       <c r="AF356" s="13"/>
       <c r="AG356" s="13"/>
     </row>
-    <row r="357" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A357" s="11">
         <v>350</v>
       </c>
@@ -18969,7 +19329,7 @@
       <c r="AF357" s="13"/>
       <c r="AG357" s="13"/>
     </row>
-    <row r="358" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A358" s="11">
         <v>351</v>
       </c>
@@ -19014,7 +19374,7 @@
       <c r="AF358" s="13"/>
       <c r="AG358" s="13"/>
     </row>
-    <row r="359" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A359" s="11">
         <v>352</v>
       </c>
@@ -19059,7 +19419,7 @@
       <c r="AF359" s="13"/>
       <c r="AG359" s="13"/>
     </row>
-    <row r="360" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A360" s="11">
         <v>353</v>
       </c>
@@ -19104,7 +19464,7 @@
       <c r="AF360" s="13"/>
       <c r="AG360" s="13"/>
     </row>
-    <row r="361" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A361" s="11">
         <v>354</v>
       </c>
@@ -19149,7 +19509,7 @@
       <c r="AF361" s="13"/>
       <c r="AG361" s="13"/>
     </row>
-    <row r="362" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A362" s="11">
         <v>355</v>
       </c>
@@ -19194,7 +19554,7 @@
       <c r="AF362" s="13"/>
       <c r="AG362" s="13"/>
     </row>
-    <row r="363" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A363" s="11">
         <v>356</v>
       </c>
@@ -19239,7 +19599,7 @@
       <c r="AF363" s="13"/>
       <c r="AG363" s="13"/>
     </row>
-    <row r="364" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A364" s="11">
         <v>357</v>
       </c>
@@ -19284,7 +19644,7 @@
       <c r="AF364" s="13"/>
       <c r="AG364" s="13"/>
     </row>
-    <row r="365" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A365" s="11">
         <v>358</v>
       </c>
@@ -19329,7 +19689,7 @@
       <c r="AF365" s="13"/>
       <c r="AG365" s="13"/>
     </row>
-    <row r="366" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A366" s="11">
         <v>359</v>
       </c>
@@ -19374,7 +19734,7 @@
       <c r="AF366" s="13"/>
       <c r="AG366" s="13"/>
     </row>
-    <row r="367" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A367" s="11">
         <v>360</v>
       </c>
@@ -19419,7 +19779,7 @@
       <c r="AF367" s="13"/>
       <c r="AG367" s="13"/>
     </row>
-    <row r="368" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A368" s="11">
         <v>361</v>
       </c>
@@ -19464,7 +19824,7 @@
       <c r="AF368" s="13"/>
       <c r="AG368" s="13"/>
     </row>
-    <row r="369" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A369" s="11">
         <v>362</v>
       </c>
@@ -19509,7 +19869,7 @@
       <c r="AF369" s="13"/>
       <c r="AG369" s="13"/>
     </row>
-    <row r="370" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A370" s="11">
         <v>363</v>
       </c>
@@ -19554,7 +19914,7 @@
       <c r="AF370" s="13"/>
       <c r="AG370" s="13"/>
     </row>
-    <row r="371" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A371" s="11">
         <v>364</v>
       </c>
@@ -19599,7 +19959,7 @@
       <c r="AF371" s="13"/>
       <c r="AG371" s="13"/>
     </row>
-    <row r="372" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A372" s="11">
         <v>365</v>
       </c>
@@ -19644,7 +20004,7 @@
       <c r="AF372" s="13"/>
       <c r="AG372" s="13"/>
     </row>
-    <row r="373" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A373" s="11">
         <v>366</v>
       </c>
@@ -19689,7 +20049,7 @@
       <c r="AF373" s="13"/>
       <c r="AG373" s="13"/>
     </row>
-    <row r="374" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A374" s="11">
         <v>367</v>
       </c>
@@ -19734,7 +20094,7 @@
       <c r="AF374" s="13"/>
       <c r="AG374" s="13"/>
     </row>
-    <row r="375" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A375" s="11">
         <v>368</v>
       </c>
@@ -19779,7 +20139,7 @@
       <c r="AF375" s="13"/>
       <c r="AG375" s="13"/>
     </row>
-    <row r="376" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A376" s="11">
         <v>369</v>
       </c>
@@ -19824,7 +20184,7 @@
       <c r="AF376" s="13"/>
       <c r="AG376" s="13"/>
     </row>
-    <row r="377" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A377" s="11">
         <v>370</v>
       </c>
@@ -19869,7 +20229,7 @@
       <c r="AF377" s="13"/>
       <c r="AG377" s="13"/>
     </row>
-    <row r="378" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A378" s="11">
         <v>371</v>
       </c>
@@ -19914,7 +20274,7 @@
       <c r="AF378" s="13"/>
       <c r="AG378" s="13"/>
     </row>
-    <row r="379" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A379" s="11">
         <v>372</v>
       </c>
@@ -19959,7 +20319,7 @@
       <c r="AF379" s="13"/>
       <c r="AG379" s="13"/>
     </row>
-    <row r="380" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A380" s="11">
         <v>373</v>
       </c>
@@ -20004,7 +20364,7 @@
       <c r="AF380" s="13"/>
       <c r="AG380" s="13"/>
     </row>
-    <row r="381" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A381" s="11">
         <v>374</v>
       </c>
@@ -20049,7 +20409,7 @@
       <c r="AF381" s="13"/>
       <c r="AG381" s="13"/>
     </row>
-    <row r="382" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A382" s="11">
         <v>375</v>
       </c>
@@ -20094,7 +20454,7 @@
       <c r="AF382" s="13"/>
       <c r="AG382" s="13"/>
     </row>
-    <row r="383" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A383" s="11">
         <v>376</v>
       </c>
@@ -20139,7 +20499,7 @@
       <c r="AF383" s="13"/>
       <c r="AG383" s="13"/>
     </row>
-    <row r="384" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A384" s="11">
         <v>377</v>
       </c>
@@ -20184,7 +20544,7 @@
       <c r="AF384" s="13"/>
       <c r="AG384" s="13"/>
     </row>
-    <row r="385" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A385" s="11">
         <v>378</v>
       </c>
@@ -20229,7 +20589,7 @@
       <c r="AF385" s="13"/>
       <c r="AG385" s="13"/>
     </row>
-    <row r="386" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A386" s="11">
         <v>379</v>
       </c>
@@ -20274,7 +20634,7 @@
       <c r="AF386" s="13"/>
       <c r="AG386" s="13"/>
     </row>
-    <row r="387" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A387" s="11">
         <v>380</v>
       </c>
@@ -20319,7 +20679,7 @@
       <c r="AF387" s="13"/>
       <c r="AG387" s="13"/>
     </row>
-    <row r="388" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A388" s="11">
         <v>381</v>
       </c>
@@ -20364,7 +20724,7 @@
       <c r="AF388" s="13"/>
       <c r="AG388" s="13"/>
     </row>
-    <row r="389" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A389" s="11">
         <v>382</v>
       </c>
@@ -20409,7 +20769,7 @@
       <c r="AF389" s="13"/>
       <c r="AG389" s="13"/>
     </row>
-    <row r="390" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A390" s="11">
         <v>383</v>
       </c>
@@ -20454,7 +20814,7 @@
       <c r="AF390" s="13"/>
       <c r="AG390" s="13"/>
     </row>
-    <row r="391" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A391" s="11">
         <v>384</v>
       </c>
@@ -20499,7 +20859,7 @@
       <c r="AF391" s="13"/>
       <c r="AG391" s="13"/>
     </row>
-    <row r="392" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A392" s="11">
         <v>385</v>
       </c>
@@ -20544,7 +20904,7 @@
       <c r="AF392" s="13"/>
       <c r="AG392" s="13"/>
     </row>
-    <row r="393" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A393" s="11">
         <v>386</v>
       </c>
@@ -20589,7 +20949,7 @@
       <c r="AF393" s="13"/>
       <c r="AG393" s="13"/>
     </row>
-    <row r="394" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A394" s="11">
         <v>387</v>
       </c>
@@ -20634,7 +20994,7 @@
       <c r="AF394" s="13"/>
       <c r="AG394" s="13"/>
     </row>
-    <row r="395" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A395" s="11">
         <v>388</v>
       </c>
@@ -20679,7 +21039,7 @@
       <c r="AF395" s="13"/>
       <c r="AG395" s="13"/>
     </row>
-    <row r="396" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A396" s="11">
         <v>389</v>
       </c>
@@ -20724,7 +21084,7 @@
       <c r="AF396" s="13"/>
       <c r="AG396" s="13"/>
     </row>
-    <row r="397" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A397" s="11">
         <v>390</v>
       </c>
@@ -20769,7 +21129,7 @@
       <c r="AF397" s="13"/>
       <c r="AG397" s="13"/>
     </row>
-    <row r="398" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A398" s="11">
         <v>391</v>
       </c>
@@ -20814,7 +21174,7 @@
       <c r="AF398" s="13"/>
       <c r="AG398" s="13"/>
     </row>
-    <row r="399" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A399" s="11">
         <v>392</v>
       </c>
@@ -20859,7 +21219,7 @@
       <c r="AF399" s="13"/>
       <c r="AG399" s="13"/>
     </row>
-    <row r="400" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A400" s="11">
         <v>393</v>
       </c>
@@ -20904,7 +21264,7 @@
       <c r="AF400" s="13"/>
       <c r="AG400" s="13"/>
     </row>
-    <row r="401" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A401" s="11">
         <v>394</v>
       </c>
@@ -20949,7 +21309,7 @@
       <c r="AF401" s="13"/>
       <c r="AG401" s="13"/>
     </row>
-    <row r="402" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A402" s="11">
         <v>395</v>
       </c>
@@ -20994,7 +21354,7 @@
       <c r="AF402" s="13"/>
       <c r="AG402" s="13"/>
     </row>
-    <row r="403" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A403" s="11">
         <v>396</v>
       </c>
@@ -21039,7 +21399,7 @@
       <c r="AF403" s="13"/>
       <c r="AG403" s="13"/>
     </row>
-    <row r="404" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A404" s="11">
         <v>397</v>
       </c>
@@ -21084,7 +21444,7 @@
       <c r="AF404" s="13"/>
       <c r="AG404" s="13"/>
     </row>
-    <row r="405" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A405" s="11">
         <v>398</v>
       </c>
@@ -21129,7 +21489,7 @@
       <c r="AF405" s="13"/>
       <c r="AG405" s="13"/>
     </row>
-    <row r="406" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A406" s="11">
         <v>399</v>
       </c>
@@ -21174,7 +21534,7 @@
       <c r="AF406" s="13"/>
       <c r="AG406" s="13"/>
     </row>
-    <row r="407" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A407" s="11">
         <v>400</v>
       </c>
@@ -21219,7 +21579,7 @@
       <c r="AF407" s="13"/>
       <c r="AG407" s="13"/>
     </row>
-    <row r="408" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A408" s="11">
         <v>401</v>
       </c>
@@ -21264,7 +21624,7 @@
       <c r="AF408" s="13"/>
       <c r="AG408" s="13"/>
     </row>
-    <row r="409" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A409" s="11">
         <v>402</v>
       </c>
@@ -21309,7 +21669,7 @@
       <c r="AF409" s="13"/>
       <c r="AG409" s="13"/>
     </row>
-    <row r="410" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A410" s="11">
         <v>403</v>
       </c>
@@ -21354,7 +21714,7 @@
       <c r="AF410" s="13"/>
       <c r="AG410" s="13"/>
     </row>
-    <row r="411" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A411" s="11">
         <v>404</v>
       </c>
@@ -21399,7 +21759,7 @@
       <c r="AF411" s="13"/>
       <c r="AG411" s="13"/>
     </row>
-    <row r="412" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A412" s="11">
         <v>405</v>
       </c>
@@ -21444,7 +21804,7 @@
       <c r="AF412" s="13"/>
       <c r="AG412" s="13"/>
     </row>
-    <row r="413" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A413" s="11">
         <v>406</v>
       </c>
@@ -21489,7 +21849,7 @@
       <c r="AF413" s="13"/>
       <c r="AG413" s="13"/>
     </row>
-    <row r="414" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A414" s="11">
         <v>407</v>
       </c>
@@ -21534,7 +21894,7 @@
       <c r="AF414" s="13"/>
       <c r="AG414" s="13"/>
     </row>
-    <row r="415" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A415" s="11">
         <v>408</v>
       </c>
@@ -21579,7 +21939,7 @@
       <c r="AF415" s="13"/>
       <c r="AG415" s="13"/>
     </row>
-    <row r="416" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A416" s="11">
         <v>409</v>
       </c>
@@ -21624,7 +21984,7 @@
       <c r="AF416" s="13"/>
       <c r="AG416" s="13"/>
     </row>
-    <row r="417" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A417" s="11">
         <v>410</v>
       </c>
@@ -21669,7 +22029,7 @@
       <c r="AF417" s="13"/>
       <c r="AG417" s="13"/>
     </row>
-    <row r="418" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A418" s="11">
         <v>411</v>
       </c>
@@ -21714,7 +22074,7 @@
       <c r="AF418" s="13"/>
       <c r="AG418" s="13"/>
     </row>
-    <row r="419" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A419" s="11">
         <v>412</v>
       </c>
@@ -21759,7 +22119,7 @@
       <c r="AF419" s="13"/>
       <c r="AG419" s="13"/>
     </row>
-    <row r="420" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A420" s="11">
         <v>413</v>
       </c>
@@ -21804,7 +22164,7 @@
       <c r="AF420" s="13"/>
       <c r="AG420" s="13"/>
     </row>
-    <row r="421" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A421" s="11">
         <v>414</v>
       </c>
@@ -21849,7 +22209,7 @@
       <c r="AF421" s="13"/>
       <c r="AG421" s="13"/>
     </row>
-    <row r="422" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A422" s="11">
         <v>415</v>
       </c>
@@ -21894,7 +22254,7 @@
       <c r="AF422" s="13"/>
       <c r="AG422" s="13"/>
     </row>
-    <row r="423" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A423" s="11">
         <v>416</v>
       </c>
@@ -21939,7 +22299,7 @@
       <c r="AF423" s="13"/>
       <c r="AG423" s="13"/>
     </row>
-    <row r="424" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A424" s="11">
         <v>417</v>
       </c>
@@ -21984,7 +22344,7 @@
       <c r="AF424" s="13"/>
       <c r="AG424" s="13"/>
     </row>
-    <row r="425" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A425" s="11">
         <v>418</v>
       </c>
@@ -22029,7 +22389,7 @@
       <c r="AF425" s="13"/>
       <c r="AG425" s="13"/>
     </row>
-    <row r="426" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A426" s="11">
         <v>419</v>
       </c>
@@ -22074,7 +22434,7 @@
       <c r="AF426" s="13"/>
       <c r="AG426" s="13"/>
     </row>
-    <row r="427" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A427" s="11">
         <v>420</v>
       </c>
@@ -22119,7 +22479,7 @@
       <c r="AF427" s="13"/>
       <c r="AG427" s="13"/>
     </row>
-    <row r="428" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A428" s="11">
         <v>421</v>
       </c>
@@ -22164,7 +22524,7 @@
       <c r="AF428" s="13"/>
       <c r="AG428" s="13"/>
     </row>
-    <row r="429" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A429" s="11">
         <v>422</v>
       </c>
@@ -22209,7 +22569,7 @@
       <c r="AF429" s="13"/>
       <c r="AG429" s="13"/>
     </row>
-    <row r="430" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A430" s="11">
         <v>423</v>
       </c>
@@ -22254,7 +22614,7 @@
       <c r="AF430" s="13"/>
       <c r="AG430" s="13"/>
     </row>
-    <row r="431" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A431" s="11">
         <v>424</v>
       </c>
@@ -22299,7 +22659,7 @@
       <c r="AF431" s="13"/>
       <c r="AG431" s="13"/>
     </row>
-    <row r="432" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A432" s="11">
         <v>425</v>
       </c>
@@ -22344,7 +22704,7 @@
       <c r="AF432" s="13"/>
       <c r="AG432" s="13"/>
     </row>
-    <row r="433" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A433" s="11">
         <v>426</v>
       </c>
@@ -22389,7 +22749,7 @@
       <c r="AF433" s="13"/>
       <c r="AG433" s="13"/>
     </row>
-    <row r="434" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A434" s="11">
         <v>427</v>
       </c>
@@ -22434,7 +22794,7 @@
       <c r="AF434" s="13"/>
       <c r="AG434" s="13"/>
     </row>
-    <row r="435" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A435" s="11">
         <v>428</v>
       </c>
@@ -22479,7 +22839,7 @@
       <c r="AF435" s="13"/>
       <c r="AG435" s="13"/>
     </row>
-    <row r="436" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A436" s="11">
         <v>429</v>
       </c>
@@ -22524,7 +22884,7 @@
       <c r="AF436" s="13"/>
       <c r="AG436" s="13"/>
     </row>
-    <row r="437" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A437" s="11">
         <v>430</v>
       </c>
@@ -22569,7 +22929,7 @@
       <c r="AF437" s="13"/>
       <c r="AG437" s="13"/>
     </row>
-    <row r="438" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A438" s="11">
         <v>431</v>
       </c>
@@ -22614,7 +22974,7 @@
       <c r="AF438" s="13"/>
       <c r="AG438" s="13"/>
     </row>
-    <row r="439" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A439" s="11">
         <v>432</v>
       </c>
@@ -22659,7 +23019,7 @@
       <c r="AF439" s="13"/>
       <c r="AG439" s="13"/>
     </row>
-    <row r="440" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A440" s="11">
         <v>433</v>
       </c>
@@ -22704,7 +23064,7 @@
       <c r="AF440" s="13"/>
       <c r="AG440" s="13"/>
     </row>
-    <row r="441" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A441" s="11">
         <v>434</v>
       </c>
@@ -22749,7 +23109,7 @@
       <c r="AF441" s="13"/>
       <c r="AG441" s="13"/>
     </row>
-    <row r="442" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A442" s="11">
         <v>435</v>
       </c>
@@ -22794,7 +23154,7 @@
       <c r="AF442" s="13"/>
       <c r="AG442" s="13"/>
     </row>
-    <row r="443" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A443" s="11">
         <v>436</v>
       </c>
@@ -22839,7 +23199,7 @@
       <c r="AF443" s="13"/>
       <c r="AG443" s="13"/>
     </row>
-    <row r="444" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A444" s="11">
         <v>437</v>
       </c>
@@ -22884,7 +23244,7 @@
       <c r="AF444" s="13"/>
       <c r="AG444" s="13"/>
     </row>
-    <row r="445" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A445" s="11">
         <v>438</v>
       </c>
@@ -22929,7 +23289,7 @@
       <c r="AF445" s="13"/>
       <c r="AG445" s="13"/>
     </row>
-    <row r="446" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A446" s="11">
         <v>439</v>
       </c>
@@ -22974,7 +23334,7 @@
       <c r="AF446" s="13"/>
       <c r="AG446" s="13"/>
     </row>
-    <row r="447" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A447" s="11">
         <v>440</v>
       </c>
@@ -23019,7 +23379,7 @@
       <c r="AF447" s="13"/>
       <c r="AG447" s="13"/>
     </row>
-    <row r="448" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A448" s="11">
         <v>441</v>
       </c>
@@ -23064,7 +23424,7 @@
       <c r="AF448" s="13"/>
       <c r="AG448" s="13"/>
     </row>
-    <row r="449" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A449" s="11">
         <v>442</v>
       </c>
@@ -23109,7 +23469,7 @@
       <c r="AF449" s="13"/>
       <c r="AG449" s="13"/>
     </row>
-    <row r="450" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A450" s="11">
         <v>443</v>
       </c>
@@ -23154,7 +23514,7 @@
       <c r="AF450" s="13"/>
       <c r="AG450" s="13"/>
     </row>
-    <row r="451" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A451" s="11">
         <v>444</v>
       </c>
@@ -23199,7 +23559,7 @@
       <c r="AF451" s="13"/>
       <c r="AG451" s="13"/>
     </row>
-    <row r="452" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A452" s="11">
         <v>445</v>
       </c>
@@ -23244,7 +23604,7 @@
       <c r="AF452" s="13"/>
       <c r="AG452" s="13"/>
     </row>
-    <row r="453" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A453" s="11">
         <v>446</v>
       </c>
@@ -23289,7 +23649,7 @@
       <c r="AF453" s="13"/>
       <c r="AG453" s="13"/>
     </row>
-    <row r="454" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A454" s="11">
         <v>447</v>
       </c>
@@ -23334,7 +23694,7 @@
       <c r="AF454" s="13"/>
       <c r="AG454" s="13"/>
     </row>
-    <row r="455" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A455" s="11">
         <v>448</v>
       </c>
@@ -23379,7 +23739,7 @@
       <c r="AF455" s="13"/>
       <c r="AG455" s="13"/>
     </row>
-    <row r="456" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A456" s="11">
         <v>449</v>
       </c>
@@ -23424,7 +23784,7 @@
       <c r="AF456" s="13"/>
       <c r="AG456" s="13"/>
     </row>
-    <row r="457" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A457" s="11">
         <v>450</v>
       </c>
@@ -23469,7 +23829,7 @@
       <c r="AF457" s="13"/>
       <c r="AG457" s="13"/>
     </row>
-    <row r="458" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A458" s="11">
         <v>451</v>
       </c>
@@ -23514,7 +23874,7 @@
       <c r="AF458" s="13"/>
       <c r="AG458" s="13"/>
     </row>
-    <row r="459" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A459" s="11">
         <v>452</v>
       </c>
@@ -23559,7 +23919,7 @@
       <c r="AF459" s="13"/>
       <c r="AG459" s="13"/>
     </row>
-    <row r="460" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A460" s="11">
         <v>453</v>
       </c>
@@ -23604,7 +23964,7 @@
       <c r="AF460" s="13"/>
       <c r="AG460" s="13"/>
     </row>
-    <row r="461" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A461" s="11">
         <v>454</v>
       </c>
@@ -23649,7 +24009,7 @@
       <c r="AF461" s="13"/>
       <c r="AG461" s="13"/>
     </row>
-    <row r="462" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A462" s="11">
         <v>455</v>
       </c>
@@ -23694,7 +24054,7 @@
       <c r="AF462" s="13"/>
       <c r="AG462" s="13"/>
     </row>
-    <row r="463" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A463" s="11">
         <v>456</v>
       </c>
@@ -23739,7 +24099,7 @@
       <c r="AF463" s="13"/>
       <c r="AG463" s="13"/>
     </row>
-    <row r="464" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A464" s="11">
         <v>457</v>
       </c>
@@ -23784,7 +24144,7 @@
       <c r="AF464" s="13"/>
       <c r="AG464" s="13"/>
     </row>
-    <row r="465" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A465" s="11">
         <v>458</v>
       </c>
@@ -23829,7 +24189,7 @@
       <c r="AF465" s="13"/>
       <c r="AG465" s="13"/>
     </row>
-    <row r="466" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A466" s="11">
         <v>459</v>
       </c>
@@ -23874,7 +24234,7 @@
       <c r="AF466" s="13"/>
       <c r="AG466" s="13"/>
     </row>
-    <row r="467" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A467" s="11">
         <v>460</v>
       </c>
@@ -23919,7 +24279,7 @@
       <c r="AF467" s="13"/>
       <c r="AG467" s="13"/>
     </row>
-    <row r="468" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A468" s="11">
         <v>461</v>
       </c>
@@ -23964,7 +24324,7 @@
       <c r="AF468" s="13"/>
       <c r="AG468" s="13"/>
     </row>
-    <row r="469" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A469" s="11">
         <v>462</v>
       </c>
@@ -24009,7 +24369,7 @@
       <c r="AF469" s="13"/>
       <c r="AG469" s="13"/>
     </row>
-    <row r="470" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A470" s="11">
         <v>463</v>
       </c>
@@ -24054,7 +24414,7 @@
       <c r="AF470" s="13"/>
       <c r="AG470" s="13"/>
     </row>
-    <row r="471" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A471" s="11">
         <v>464</v>
       </c>
@@ -24099,7 +24459,7 @@
       <c r="AF471" s="13"/>
       <c r="AG471" s="13"/>
     </row>
-    <row r="472" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A472" s="11">
         <v>465</v>
       </c>
@@ -24144,7 +24504,7 @@
       <c r="AF472" s="13"/>
       <c r="AG472" s="13"/>
     </row>
-    <row r="473" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A473" s="11">
         <v>466</v>
       </c>
@@ -24189,7 +24549,7 @@
       <c r="AF473" s="13"/>
       <c r="AG473" s="13"/>
     </row>
-    <row r="474" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A474" s="11">
         <v>467</v>
       </c>
@@ -24234,7 +24594,7 @@
       <c r="AF474" s="13"/>
       <c r="AG474" s="13"/>
     </row>
-    <row r="475" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A475" s="11">
         <v>468</v>
       </c>
@@ -24279,7 +24639,7 @@
       <c r="AF475" s="13"/>
       <c r="AG475" s="13"/>
     </row>
-    <row r="476" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A476" s="11">
         <v>469</v>
       </c>
@@ -24324,7 +24684,7 @@
       <c r="AF476" s="13"/>
       <c r="AG476" s="13"/>
     </row>
-    <row r="477" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A477" s="11">
         <v>470</v>
       </c>
@@ -24369,7 +24729,7 @@
       <c r="AF477" s="13"/>
       <c r="AG477" s="13"/>
     </row>
-    <row r="478" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A478" s="11">
         <v>471</v>
       </c>
@@ -24414,7 +24774,7 @@
       <c r="AF478" s="13"/>
       <c r="AG478" s="13"/>
     </row>
-    <row r="479" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A479" s="11">
         <v>472</v>
       </c>
@@ -24459,7 +24819,7 @@
       <c r="AF479" s="13"/>
       <c r="AG479" s="13"/>
     </row>
-    <row r="480" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A480" s="11">
         <v>473</v>
       </c>
@@ -24504,7 +24864,7 @@
       <c r="AF480" s="13"/>
       <c r="AG480" s="13"/>
     </row>
-    <row r="481" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A481" s="11">
         <v>474</v>
       </c>
@@ -24549,7 +24909,7 @@
       <c r="AF481" s="13"/>
       <c r="AG481" s="13"/>
     </row>
-    <row r="482" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A482" s="11">
         <v>475</v>
       </c>
@@ -24594,7 +24954,7 @@
       <c r="AF482" s="13"/>
       <c r="AG482" s="13"/>
     </row>
-    <row r="483" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A483" s="11">
         <v>476</v>
       </c>
@@ -24639,7 +24999,7 @@
       <c r="AF483" s="13"/>
       <c r="AG483" s="13"/>
     </row>
-    <row r="484" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A484" s="11">
         <v>477</v>
       </c>
@@ -24684,7 +25044,7 @@
       <c r="AF484" s="13"/>
       <c r="AG484" s="13"/>
     </row>
-    <row r="485" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A485" s="11">
         <v>478</v>
       </c>
@@ -24729,7 +25089,7 @@
       <c r="AF485" s="13"/>
       <c r="AG485" s="13"/>
     </row>
-    <row r="486" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A486" s="11">
         <v>479</v>
       </c>
@@ -24774,7 +25134,7 @@
       <c r="AF486" s="13"/>
       <c r="AG486" s="13"/>
     </row>
-    <row r="487" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A487" s="11">
         <v>480</v>
       </c>
@@ -24819,7 +25179,7 @@
       <c r="AF487" s="13"/>
       <c r="AG487" s="13"/>
     </row>
-    <row r="488" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A488" s="11">
         <v>481</v>
       </c>
@@ -24864,7 +25224,7 @@
       <c r="AF488" s="13"/>
       <c r="AG488" s="13"/>
     </row>
-    <row r="489" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A489" s="11">
         <v>482</v>
       </c>
@@ -24909,7 +25269,7 @@
       <c r="AF489" s="13"/>
       <c r="AG489" s="13"/>
     </row>
-    <row r="490" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A490" s="11">
         <v>483</v>
       </c>
@@ -24954,7 +25314,7 @@
       <c r="AF490" s="13"/>
       <c r="AG490" s="13"/>
     </row>
-    <row r="491" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A491" s="11">
         <v>484</v>
       </c>
@@ -24999,7 +25359,7 @@
       <c r="AF491" s="13"/>
       <c r="AG491" s="13"/>
     </row>
-    <row r="492" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A492" s="11">
         <v>485</v>
       </c>
@@ -25044,7 +25404,7 @@
       <c r="AF492" s="13"/>
       <c r="AG492" s="13"/>
     </row>
-    <row r="493" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A493" s="11">
         <v>486</v>
       </c>
@@ -25089,7 +25449,7 @@
       <c r="AF493" s="13"/>
       <c r="AG493" s="13"/>
     </row>
-    <row r="494" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A494" s="11">
         <v>487</v>
       </c>
@@ -25134,7 +25494,7 @@
       <c r="AF494" s="13"/>
       <c r="AG494" s="13"/>
     </row>
-    <row r="495" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A495" s="11">
         <v>488</v>
       </c>
@@ -25179,7 +25539,7 @@
       <c r="AF495" s="13"/>
       <c r="AG495" s="13"/>
     </row>
-    <row r="496" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A496" s="11">
         <v>489</v>
       </c>
@@ -25224,7 +25584,7 @@
       <c r="AF496" s="13"/>
       <c r="AG496" s="13"/>
     </row>
-    <row r="497" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A497" s="11">
         <v>490</v>
       </c>
@@ -25269,7 +25629,7 @@
       <c r="AF497" s="13"/>
       <c r="AG497" s="13"/>
     </row>
-    <row r="498" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A498" s="11">
         <v>491</v>
       </c>
@@ -25314,7 +25674,7 @@
       <c r="AF498" s="13"/>
       <c r="AG498" s="13"/>
     </row>
-    <row r="499" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A499" s="11">
         <v>492</v>
       </c>
@@ -25359,7 +25719,7 @@
       <c r="AF499" s="13"/>
       <c r="AG499" s="13"/>
     </row>
-    <row r="500" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A500" s="11">
         <v>493</v>
       </c>
@@ -25404,7 +25764,7 @@
       <c r="AF500" s="13"/>
       <c r="AG500" s="13"/>
     </row>
-    <row r="501" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A501" s="11">
         <v>494</v>
       </c>
@@ -25449,7 +25809,7 @@
       <c r="AF501" s="13"/>
       <c r="AG501" s="13"/>
     </row>
-    <row r="502" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A502" s="11">
         <v>495</v>
       </c>
@@ -25494,7 +25854,7 @@
       <c r="AF502" s="13"/>
       <c r="AG502" s="13"/>
     </row>
-    <row r="503" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A503" s="11">
         <v>496</v>
       </c>
@@ -25539,7 +25899,7 @@
       <c r="AF503" s="13"/>
       <c r="AG503" s="13"/>
     </row>
-    <row r="504" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A504" s="11">
         <v>497</v>
       </c>
@@ -25584,7 +25944,7 @@
       <c r="AF504" s="13"/>
       <c r="AG504" s="13"/>
     </row>
-    <row r="505" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A505" s="11">
         <v>498</v>
       </c>
@@ -25629,7 +25989,7 @@
       <c r="AF505" s="13"/>
       <c r="AG505" s="13"/>
     </row>
-    <row r="506" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A506" s="11">
         <v>499</v>
       </c>
@@ -25674,7 +26034,7 @@
       <c r="AF506" s="13"/>
       <c r="AG506" s="13"/>
     </row>
-    <row r="507" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A507" s="11">
         <v>500</v>
       </c>
@@ -25719,7 +26079,7 @@
       <c r="AF507" s="13"/>
       <c r="AG507" s="13"/>
     </row>
-    <row r="508" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A508" s="11">
         <v>501</v>
       </c>
@@ -25764,7 +26124,7 @@
       <c r="AF508" s="13"/>
       <c r="AG508" s="13"/>
     </row>
-    <row r="509" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A509" s="11">
         <v>502</v>
       </c>
@@ -25809,7 +26169,7 @@
       <c r="AF509" s="13"/>
       <c r="AG509" s="13"/>
     </row>
-    <row r="510" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A510" s="11">
         <v>503</v>
       </c>
@@ -25854,7 +26214,7 @@
       <c r="AF510" s="13"/>
       <c r="AG510" s="13"/>
     </row>
-    <row r="511" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A511" s="11">
         <v>504</v>
       </c>
@@ -25899,7 +26259,7 @@
       <c r="AF511" s="13"/>
       <c r="AG511" s="13"/>
     </row>
-    <row r="512" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A512" s="11">
         <v>505</v>
       </c>
@@ -25944,7 +26304,7 @@
       <c r="AF512" s="13"/>
       <c r="AG512" s="13"/>
     </row>
-    <row r="513" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A513" s="11">
         <v>506</v>
       </c>
@@ -25989,7 +26349,7 @@
       <c r="AF513" s="13"/>
       <c r="AG513" s="13"/>
     </row>
-    <row r="514" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A514" s="11">
         <v>507</v>
       </c>
@@ -26034,7 +26394,7 @@
       <c r="AF514" s="13"/>
       <c r="AG514" s="13"/>
     </row>
-    <row r="515" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A515" s="11">
         <v>508</v>
       </c>
@@ -26079,7 +26439,7 @@
       <c r="AF515" s="13"/>
       <c r="AG515" s="13"/>
     </row>
-    <row r="516" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A516" s="11">
         <v>509</v>
       </c>
@@ -26124,7 +26484,7 @@
       <c r="AF516" s="13"/>
       <c r="AG516" s="13"/>
     </row>
-    <row r="517" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A517" s="11">
         <v>510</v>
       </c>
@@ -26169,7 +26529,7 @@
       <c r="AF517" s="13"/>
       <c r="AG517" s="13"/>
     </row>
-    <row r="518" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A518" s="11">
         <v>511</v>
       </c>
@@ -26214,7 +26574,7 @@
       <c r="AF518" s="13"/>
       <c r="AG518" s="13"/>
     </row>
-    <row r="519" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A519" s="11">
         <v>512</v>
       </c>
@@ -26259,7 +26619,7 @@
       <c r="AF519" s="13"/>
       <c r="AG519" s="13"/>
     </row>
-    <row r="520" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A520" s="11">
         <v>513</v>
       </c>
@@ -26304,7 +26664,7 @@
       <c r="AF520" s="13"/>
       <c r="AG520" s="13"/>
     </row>
-    <row r="521" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A521" s="11">
         <v>514</v>
       </c>
@@ -26349,7 +26709,7 @@
       <c r="AF521" s="13"/>
       <c r="AG521" s="13"/>
     </row>
-    <row r="522" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A522" s="11">
         <v>515</v>
       </c>
@@ -26394,7 +26754,7 @@
       <c r="AF522" s="13"/>
       <c r="AG522" s="13"/>
     </row>
-    <row r="523" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A523" s="11">
         <v>516</v>
       </c>
@@ -26439,7 +26799,7 @@
       <c r="AF523" s="13"/>
       <c r="AG523" s="13"/>
     </row>
-    <row r="524" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A524" s="11">
         <v>517</v>
       </c>
@@ -26484,7 +26844,7 @@
       <c r="AF524" s="13"/>
       <c r="AG524" s="13"/>
     </row>
-    <row r="525" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A525" s="11">
         <v>518</v>
       </c>
@@ -26529,7 +26889,7 @@
       <c r="AF525" s="13"/>
       <c r="AG525" s="13"/>
     </row>
-    <row r="526" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A526" s="11">
         <v>519</v>
       </c>
@@ -26574,7 +26934,7 @@
       <c r="AF526" s="13"/>
       <c r="AG526" s="13"/>
     </row>
-    <row r="527" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A527" s="11">
         <v>520</v>
       </c>
@@ -26619,7 +26979,7 @@
       <c r="AF527" s="13"/>
       <c r="AG527" s="13"/>
     </row>
-    <row r="528" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A528" s="11">
         <v>521</v>
       </c>
@@ -26664,7 +27024,7 @@
       <c r="AF528" s="13"/>
       <c r="AG528" s="13"/>
     </row>
-    <row r="529" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A529" s="11">
         <v>522</v>
       </c>
@@ -26709,7 +27069,7 @@
       <c r="AF529" s="13"/>
       <c r="AG529" s="13"/>
     </row>
-    <row r="530" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A530" s="11">
         <v>523</v>
       </c>
@@ -26754,7 +27114,7 @@
       <c r="AF530" s="13"/>
       <c r="AG530" s="13"/>
     </row>
-    <row r="531" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A531" s="11">
         <v>524</v>
       </c>
@@ -26799,7 +27159,7 @@
       <c r="AF531" s="13"/>
       <c r="AG531" s="13"/>
     </row>
-    <row r="532" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A532" s="11">
         <v>525</v>
       </c>
@@ -26844,7 +27204,7 @@
       <c r="AF532" s="13"/>
       <c r="AG532" s="13"/>
     </row>
-    <row r="533" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A533" s="11">
         <v>526</v>
       </c>
@@ -26889,7 +27249,7 @@
       <c r="AF533" s="13"/>
       <c r="AG533" s="13"/>
     </row>
-    <row r="534" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A534" s="11">
         <v>527</v>
       </c>
@@ -26934,7 +27294,7 @@
       <c r="AF534" s="13"/>
       <c r="AG534" s="13"/>
     </row>
-    <row r="535" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A535" s="11">
         <v>528</v>
       </c>
@@ -26979,7 +27339,7 @@
       <c r="AF535" s="13"/>
       <c r="AG535" s="13"/>
     </row>
-    <row r="536" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A536" s="11">
         <v>529</v>
       </c>
@@ -27024,7 +27384,7 @@
       <c r="AF536" s="13"/>
       <c r="AG536" s="13"/>
     </row>
-    <row r="537" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A537" s="11">
         <v>530</v>
       </c>
@@ -27069,7 +27429,7 @@
       <c r="AF537" s="13"/>
       <c r="AG537" s="13"/>
     </row>
-    <row r="538" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A538" s="11">
         <v>531</v>
       </c>
@@ -27114,7 +27474,7 @@
       <c r="AF538" s="13"/>
       <c r="AG538" s="13"/>
     </row>
-    <row r="539" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A539" s="11">
         <v>532</v>
       </c>
@@ -27159,7 +27519,7 @@
       <c r="AF539" s="13"/>
       <c r="AG539" s="13"/>
     </row>
-    <row r="540" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A540" s="11">
         <v>533</v>
       </c>
@@ -27204,7 +27564,7 @@
       <c r="AF540" s="13"/>
       <c r="AG540" s="13"/>
     </row>
-    <row r="541" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A541" s="11">
         <v>534</v>
       </c>
@@ -27249,7 +27609,7 @@
       <c r="AF541" s="13"/>
       <c r="AG541" s="13"/>
     </row>
-    <row r="542" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A542" s="11">
         <v>535</v>
       </c>
@@ -27294,7 +27654,7 @@
       <c r="AF542" s="13"/>
       <c r="AG542" s="13"/>
     </row>
-    <row r="543" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A543" s="11">
         <v>536</v>
       </c>
@@ -27339,7 +27699,7 @@
       <c r="AF543" s="13"/>
       <c r="AG543" s="13"/>
     </row>
-    <row r="544" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A544" s="11">
         <v>537</v>
       </c>
@@ -27384,7 +27744,7 @@
       <c r="AF544" s="13"/>
       <c r="AG544" s="13"/>
     </row>
-    <row r="545" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A545" s="11">
         <v>538</v>
       </c>
@@ -27429,7 +27789,7 @@
       <c r="AF545" s="13"/>
       <c r="AG545" s="13"/>
     </row>
-    <row r="546" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A546" s="11">
         <v>539</v>
       </c>
@@ -27474,7 +27834,7 @@
       <c r="AF546" s="13"/>
       <c r="AG546" s="13"/>
     </row>
-    <row r="547" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A547" s="11">
         <v>540</v>
       </c>
@@ -27519,7 +27879,7 @@
       <c r="AF547" s="13"/>
       <c r="AG547" s="13"/>
     </row>
-    <row r="548" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A548" s="11">
         <v>541</v>
       </c>
@@ -27564,7 +27924,7 @@
       <c r="AF548" s="13"/>
       <c r="AG548" s="13"/>
     </row>
-    <row r="549" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A549" s="11">
         <v>542</v>
       </c>
@@ -27609,7 +27969,7 @@
       <c r="AF549" s="13"/>
       <c r="AG549" s="13"/>
     </row>
-    <row r="550" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A550" s="11">
         <v>543</v>
       </c>
@@ -27654,7 +28014,7 @@
       <c r="AF550" s="13"/>
       <c r="AG550" s="13"/>
     </row>
-    <row r="551" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A551" s="11">
         <v>544</v>
       </c>
@@ -27699,7 +28059,7 @@
       <c r="AF551" s="13"/>
       <c r="AG551" s="13"/>
     </row>
-    <row r="552" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A552" s="11">
         <v>545</v>
       </c>
@@ -27744,7 +28104,7 @@
       <c r="AF552" s="13"/>
       <c r="AG552" s="13"/>
     </row>
-    <row r="553" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A553" s="11">
         <v>546</v>
       </c>
@@ -27789,7 +28149,7 @@
       <c r="AF553" s="13"/>
       <c r="AG553" s="13"/>
     </row>
-    <row r="554" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A554" s="11">
         <v>547</v>
       </c>
@@ -27834,7 +28194,7 @@
       <c r="AF554" s="13"/>
       <c r="AG554" s="13"/>
     </row>
-    <row r="555" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A555" s="11">
         <v>548</v>
       </c>
@@ -27879,7 +28239,7 @@
       <c r="AF555" s="13"/>
       <c r="AG555" s="13"/>
     </row>
-    <row r="556" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A556" s="11">
         <v>549</v>
       </c>
@@ -27924,7 +28284,7 @@
       <c r="AF556" s="13"/>
       <c r="AG556" s="13"/>
     </row>
-    <row r="557" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A557" s="11">
         <v>550</v>
       </c>
@@ -27969,7 +28329,7 @@
       <c r="AF557" s="13"/>
       <c r="AG557" s="13"/>
     </row>
-    <row r="558" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A558" s="11">
         <v>551</v>
       </c>
@@ -28014,7 +28374,7 @@
       <c r="AF558" s="13"/>
       <c r="AG558" s="13"/>
     </row>
-    <row r="559" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A559" s="11">
         <v>552</v>
       </c>
@@ -28059,7 +28419,7 @@
       <c r="AF559" s="13"/>
       <c r="AG559" s="13"/>
     </row>
-    <row r="560" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A560" s="11">
         <v>553</v>
       </c>
@@ -28104,7 +28464,7 @@
       <c r="AF560" s="13"/>
       <c r="AG560" s="13"/>
     </row>
-    <row r="561" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A561" s="11">
         <v>554</v>
       </c>
@@ -28149,7 +28509,7 @@
       <c r="AF561" s="13"/>
       <c r="AG561" s="13"/>
     </row>
-    <row r="562" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A562" s="11">
         <v>555</v>
       </c>
@@ -28194,7 +28554,7 @@
       <c r="AF562" s="13"/>
       <c r="AG562" s="13"/>
     </row>
-    <row r="563" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A563" s="11">
         <v>556</v>
       </c>
@@ -28239,7 +28599,7 @@
       <c r="AF563" s="13"/>
       <c r="AG563" s="13"/>
     </row>
-    <row r="564" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A564" s="11">
         <v>557</v>
       </c>
@@ -28284,7 +28644,7 @@
       <c r="AF564" s="13"/>
       <c r="AG564" s="13"/>
     </row>
-    <row r="565" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A565" s="11">
         <v>558</v>
       </c>
@@ -28329,7 +28689,7 @@
       <c r="AF565" s="13"/>
       <c r="AG565" s="13"/>
     </row>
-    <row r="566" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A566" s="11">
         <v>559</v>
       </c>
@@ -28374,7 +28734,7 @@
       <c r="AF566" s="13"/>
       <c r="AG566" s="13"/>
     </row>
-    <row r="567" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A567" s="11">
         <v>560</v>
       </c>
@@ -28421,20 +28781,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="T6:T7"/>
     <mergeCell ref="AF6:AF7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="AG6:AG7"/>
@@ -28451,6 +28797,20 @@
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="AB6:AB7"/>
     <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="T6:T7"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB8:AB567" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -28473,12 +28833,18 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DE5615F0-C9E7-4064-89AD-774F26CFBD30}">
           <x14:formula1>
             <xm:f>Master!$A$2:$A$169</xm:f>
           </x14:formula1>
           <xm:sqref>B8:B567</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EC27346F-D7B2-4C46-A156-2136FC0978D0}">
+          <x14:formula1>
+            <xm:f>Master!$D$2:$D$112</xm:f>
+          </x14:formula1>
+          <xm:sqref>L8:L567</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -28489,16 +28855,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}">
   <dimension ref="B1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="23.81640625" style="32" customWidth="1"/>
-    <col min="7" max="7" width="92.453125" customWidth="1"/>
+    <col min="5" max="6" width="23.85546875" style="32" customWidth="1"/>
+    <col min="7" max="7" width="92.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="51.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1" s="27" t="s">
         <v>386</v>
       </c>
@@ -28506,12 +28872,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="51" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -28520,12 +28886,12 @@
       </c>
       <c r="G2" s="21"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B3" s="51" t="s">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="48" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -28536,14 +28902,14 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28">
         <v>1</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="48"/>
+      <c r="D4" s="52"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -28552,14 +28918,14 @@
       </c>
       <c r="G4" s="21"/>
     </row>
-    <row r="5" spans="2:7" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:7" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="28">
         <v>2</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="50"/>
+      <c r="D5" s="47"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -28567,14 +28933,14 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="28">
         <v>3</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="50"/>
+      <c r="D6" s="47"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -28585,14 +28951,14 @@
         <v>366</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="28">
         <v>4</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="50"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -28603,14 +28969,14 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="80.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" ht="96" x14ac:dyDescent="0.25">
       <c r="B8" s="28">
         <v>5</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="50"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -28621,14 +28987,14 @@
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="28">
         <v>6</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="46" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="50"/>
+      <c r="D9" s="47"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -28639,14 +29005,14 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="57.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="28">
         <v>7</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="46" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="50"/>
+      <c r="D10" s="47"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -28657,14 +29023,14 @@
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28">
         <v>8</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="50"/>
+      <c r="D11" s="47"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -28675,14 +29041,14 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>9</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="46" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="50"/>
+      <c r="D12" s="47"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
@@ -28691,14 +29057,14 @@
       </c>
       <c r="G12" s="31"/>
     </row>
-    <row r="13" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="28">
         <v>10</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="50"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
@@ -28707,14 +29073,14 @@
       </c>
       <c r="G13" s="31"/>
     </row>
-    <row r="14" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28">
         <v>11</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="50"/>
+      <c r="D14" s="47"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
@@ -28723,14 +29089,14 @@
       </c>
       <c r="G14" s="31"/>
     </row>
-    <row r="15" spans="2:7" ht="79" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>12</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="46" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="50"/>
+      <c r="D15" s="47"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -28741,12 +29107,12 @@
         <v>368</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="69" x14ac:dyDescent="0.35">
-      <c r="B16" s="52">
+    <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
+      <c r="B16" s="49">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="50" t="s">
         <v>349</v>
       </c>
       <c r="D16" s="29" t="s">
@@ -28762,9 +29128,9 @@
         <v>369</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="52"/>
-      <c r="C17" s="46"/>
+    <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="29" t="s">
         <v>345</v>
       </c>
@@ -28778,9 +29144,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="57.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="52"/>
-      <c r="C18" s="46"/>
+    <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="29" t="s">
         <v>346</v>
       </c>
@@ -28794,9 +29160,9 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="57.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="52"/>
-      <c r="C19" s="46"/>
+    <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="29" t="s">
         <v>347</v>
       </c>
@@ -28810,9 +29176,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="57.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="52"/>
-      <c r="C20" s="46"/>
+    <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="29" t="s">
         <v>348</v>
       </c>
@@ -28826,9 +29192,9 @@
         <v>372</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="46" x14ac:dyDescent="0.35">
-      <c r="B21" s="52"/>
-      <c r="C21" s="46"/>
+    <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="29" t="s">
         <v>352</v>
       </c>
@@ -28842,14 +29208,14 @@
         <v>374</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="30">
         <v>14</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="46" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="50"/>
+      <c r="D22" s="47"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -28860,15 +29226,15 @@
         <v>383</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="28">
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="50"/>
+      <c r="D23" s="47"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -28879,15 +29245,15 @@
         <v>383</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="46" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="50"/>
+      <c r="D24" s="47"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -28898,15 +29264,15 @@
         <v>383</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="28">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="50"/>
+      <c r="D25" s="47"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -28917,15 +29283,15 @@
         <v>383</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="61" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" ht="60.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="28">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="46" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="50"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -28936,15 +29302,15 @@
         <v>385</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="50"/>
+      <c r="D27" s="47"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -28955,15 +29321,15 @@
         <v>375</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="46" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="50"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -28974,15 +29340,15 @@
         <v>376</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="50"/>
+      <c r="D29" s="47"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -28993,15 +29359,15 @@
         <v>376</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="84.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:7" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="50"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -29012,15 +29378,15 @@
         <v>377</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:7" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="28">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="50"/>
+      <c r="D31" s="47"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -29031,15 +29397,15 @@
         <v>378</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="50"/>
+      <c r="D32" s="47"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -29048,15 +29414,15 @@
       </c>
       <c r="G32" s="20"/>
     </row>
-    <row r="33" spans="2:7" ht="79" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="50"/>
+      <c r="D33" s="47"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -29067,15 +29433,15 @@
         <v>379</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="51.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="50" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="46"/>
+      <c r="D34" s="50"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -29086,15 +29452,15 @@
         <v>380</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:7" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C35" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="46"/>
+      <c r="D35" s="50"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
@@ -29108,20 +29474,6 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29138,6 +29490,20 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -29146,911 +29512,1247 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDAC048-C2F1-4ABA-B2C8-6CB3150A85B7}">
-  <dimension ref="A1:B171"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D171"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="17"/>
+    <col min="1" max="1" width="15.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>322</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D1" s="17" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" s="54" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D3" s="54" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D4" s="54" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D5" s="54" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D6" s="54" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D7" s="54" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D8" s="55" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D9" s="55" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D10" s="54" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D11" s="55" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D12" s="54" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D13" s="54" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D14" s="54" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D15" s="54" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D16" s="54" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D17" s="54" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D18" s="54" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D19" s="55" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D20" s="55" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>48</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D21" s="55" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D22" s="54" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
         <v>50</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D23" s="55" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D24" s="54" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D25" s="55" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D26" s="55" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D27" s="54" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D28" s="54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D29" s="55" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D30" s="55" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D31" s="54" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D32" s="54" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D33" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>72</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D34" s="54" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>74</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D35" s="54" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D36" s="54" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>78</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D37" s="54" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
         <v>80</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D38" s="55" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>82</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D39" s="54" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>82</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D40" s="54" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D41" s="54" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D42" s="54" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D43" s="54" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>89</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D44" s="54" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>89</v>
       </c>
       <c r="B45" s="17" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D45" s="54" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>89</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D46" s="54" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B47" s="17" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D47" s="54" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D48" s="54" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>96</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D49" s="54" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>98</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D50" s="54" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>98</v>
       </c>
       <c r="B51" s="17" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D51" s="54" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>101</v>
       </c>
       <c r="B52" s="17" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D52" s="54" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>101</v>
       </c>
       <c r="B53" s="17" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D53" s="54" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
         <v>104</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D54" s="55" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
         <v>106</v>
       </c>
       <c r="B55" s="17" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D55" s="55" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
         <v>108</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D56" s="55" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>110</v>
       </c>
       <c r="B57" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D57" s="54" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
         <v>112</v>
       </c>
       <c r="B58" s="17" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D58" s="54" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A59" s="17" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D59" s="55" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
         <v>116</v>
       </c>
       <c r="B60" s="17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D60" s="54" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>118</v>
       </c>
       <c r="B61" s="17" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D61" s="54" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
         <v>120</v>
       </c>
       <c r="B62" s="17" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D62" s="54" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B63" s="17" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D63" s="54" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>124</v>
       </c>
       <c r="B64" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D64" s="54" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>126</v>
       </c>
       <c r="B65" s="17" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D65" s="54" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>126</v>
       </c>
       <c r="B66" s="17" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D66" s="54" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A67" s="17" t="s">
         <v>129</v>
       </c>
       <c r="B67" s="17" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D67" s="55" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A68" s="17" t="s">
         <v>131</v>
       </c>
       <c r="B68" s="17" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D68" s="55" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>133</v>
       </c>
       <c r="B69" s="17" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D69" s="54" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A70" s="17" t="s">
         <v>135</v>
       </c>
       <c r="B70" s="17" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D70" s="55" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>137</v>
       </c>
       <c r="B71" s="17" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D71" s="54" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>139</v>
       </c>
       <c r="B72" s="17" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D72" s="54" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>141</v>
       </c>
       <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D73" s="54" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>143</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D74" s="54" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>145</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D75" s="54" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>145</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D76" s="54" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>148</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D77" s="54" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>150</v>
       </c>
       <c r="B78" s="17" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D78" s="54" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
         <v>152</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D79" s="54" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
         <v>153</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D80" s="54" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
         <v>155</v>
       </c>
       <c r="B81" s="17" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D81" s="54" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="s">
         <v>157</v>
       </c>
       <c r="B82" s="17" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D82" s="55" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
         <v>157</v>
       </c>
       <c r="B83" s="17" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D83" s="54" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
         <v>160</v>
       </c>
       <c r="B84" s="17" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D84" s="54" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
         <v>162</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D85" s="54" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A86" s="17" t="s">
         <v>162</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D86" s="55" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
         <v>165</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D87" s="54" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>167</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D88" s="54" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>167</v>
       </c>
       <c r="B89" s="17" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D89" s="54" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>170</v>
       </c>
       <c r="B90" s="17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D90" s="54" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>170</v>
       </c>
       <c r="B91" s="17" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D91" s="54" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>173</v>
       </c>
       <c r="B92" s="17" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D92" s="54" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
         <v>173</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D93" s="54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
         <v>173</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D94" s="54" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
         <v>177</v>
       </c>
       <c r="B95" s="17" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D95" s="54" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A96" s="17" t="s">
         <v>177</v>
       </c>
       <c r="B96" s="17" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D96" s="55" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
         <v>180</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D97" s="54" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
         <v>182</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D98" s="54" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
         <v>182</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D99" s="54" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
         <v>185</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D100" s="54" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
         <v>187</v>
       </c>
       <c r="B101" s="17" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D101" s="54" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
         <v>189</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D102" s="54" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
         <v>191</v>
       </c>
       <c r="B103" s="17" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D103" s="54" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
         <v>193</v>
       </c>
       <c r="B104" s="17" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D104" s="54" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A105" s="17" t="s">
         <v>195</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D105" s="55" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A106" s="17" t="s">
         <v>197</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D106" s="55" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
         <v>197</v>
       </c>
       <c r="B107" s="17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D107" s="54" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
         <v>199</v>
       </c>
       <c r="B108" s="17" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D108" s="31" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
         <v>201</v>
       </c>
       <c r="B109" s="17" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D109" s="56" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
         <v>203</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D110" s="31" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
         <v>205</v>
       </c>
       <c r="B111" s="17" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D111" s="31" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
         <v>205</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D112" s="54" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="17" t="s">
         <v>208</v>
       </c>
@@ -30058,7 +30760,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="17" t="s">
         <v>208</v>
       </c>
@@ -30066,7 +30768,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="17" t="s">
         <v>210</v>
       </c>
@@ -30074,7 +30776,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="17" t="s">
         <v>212</v>
       </c>
@@ -30082,7 +30784,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="17" t="s">
         <v>214</v>
       </c>
@@ -30090,7 +30792,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="17" t="s">
         <v>216</v>
       </c>
@@ -30098,7 +30800,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="17" t="s">
         <v>218</v>
       </c>
@@ -30106,7 +30808,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="17" t="s">
         <v>220</v>
       </c>
@@ -30114,7 +30816,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="17" t="s">
         <v>222</v>
       </c>
@@ -30122,7 +30824,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="17" t="s">
         <v>224</v>
       </c>
@@ -30130,7 +30832,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="17" t="s">
         <v>226</v>
       </c>
@@ -30138,7 +30840,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="17" t="s">
         <v>228</v>
       </c>
@@ -30146,7 +30848,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="17" t="s">
         <v>230</v>
       </c>
@@ -30154,7 +30856,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="17" t="s">
         <v>232</v>
       </c>
@@ -30162,7 +30864,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="17" t="s">
         <v>234</v>
       </c>
@@ -30170,7 +30872,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
         <v>236</v>
       </c>
@@ -30178,7 +30880,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="17" t="s">
         <v>238</v>
       </c>
@@ -30186,7 +30888,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="17" t="s">
         <v>240</v>
       </c>
@@ -30194,7 +30896,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
         <v>242</v>
       </c>
@@ -30202,7 +30904,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
         <v>244</v>
       </c>
@@ -30210,7 +30912,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
         <v>246</v>
       </c>
@@ -30218,7 +30920,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
         <v>248</v>
       </c>
@@ -30226,7 +30928,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
         <v>250</v>
       </c>
@@ -30234,7 +30936,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
         <v>252</v>
       </c>
@@ -30242,7 +30944,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
         <v>254</v>
       </c>
@@ -30250,7 +30952,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
         <v>256</v>
       </c>
@@ -30258,7 +30960,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
         <v>258</v>
       </c>
@@ -30266,7 +30968,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
         <v>260</v>
       </c>
@@ -30274,7 +30976,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
         <v>262</v>
       </c>
@@ -30282,7 +30984,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
         <v>264</v>
       </c>
@@ -30290,7 +30992,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
         <v>266</v>
       </c>
@@ -30298,7 +31000,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
         <v>268</v>
       </c>
@@ -30306,7 +31008,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
         <v>270</v>
       </c>
@@ -30314,7 +31016,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="17" t="s">
         <v>272</v>
       </c>
@@ -30322,7 +31024,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="17" t="s">
         <v>274</v>
       </c>
@@ -30330,7 +31032,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="17" t="s">
         <v>276</v>
       </c>
@@ -30338,7 +31040,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="17" t="s">
         <v>278</v>
       </c>
@@ -30346,7 +31048,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="17" t="s">
         <v>280</v>
       </c>
@@ -30354,7 +31056,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="17" t="s">
         <v>282</v>
       </c>
@@ -30362,7 +31064,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="17" t="s">
         <v>284</v>
       </c>
@@ -30370,7 +31072,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="17" t="s">
         <v>286</v>
       </c>
@@ -30378,7 +31080,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="17" t="s">
         <v>288</v>
       </c>
@@ -30386,7 +31088,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="17" t="s">
         <v>290</v>
       </c>
@@ -30394,7 +31096,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="17" t="s">
         <v>292</v>
       </c>
@@ -30402,7 +31104,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="17" t="s">
         <v>294</v>
       </c>
@@ -30410,7 +31112,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="17" t="s">
         <v>296</v>
       </c>
@@ -30418,7 +31120,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="17" t="s">
         <v>298</v>
       </c>
@@ -30426,7 +31128,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="17" t="s">
         <v>300</v>
       </c>
@@ -30434,7 +31136,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="17" t="s">
         <v>300</v>
       </c>
@@ -30442,7 +31144,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="17" t="s">
         <v>303</v>
       </c>
@@ -30450,7 +31152,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="17" t="s">
         <v>305</v>
       </c>
@@ -30458,7 +31160,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="17" t="s">
         <v>307</v>
       </c>
@@ -30466,7 +31168,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="17" t="s">
         <v>309</v>
       </c>
@@ -30474,7 +31176,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="17" t="s">
         <v>311</v>
       </c>
@@ -30482,7 +31184,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="17" t="s">
         <v>313</v>
       </c>
@@ -30490,7 +31192,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="17" t="s">
         <v>315</v>
       </c>
@@ -30498,7 +31200,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="17" t="s">
         <v>317</v>
       </c>
@@ -30506,12 +31208,12 @@
         <v>318</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B170" s="17" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="17" t="s">
         <v>320</v>
       </c>
@@ -30524,12 +31226,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13254DC6-374D-4986-96B0-F1A090138EDE}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="7" width="15.54296875" style="1" customWidth="1"/>
+    <col min="3" max="7" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -30539,7 +31241,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="53" t="s">
@@ -30553,7 +31255,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -30573,7 +31275,7 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="6"/>
@@ -30583,7 +31285,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>

--- a/wwwroot/template/TemPlateApproverQuote.xlsx
+++ b/wwwroot/template/TemPlateApproverQuote.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D4F6B1-A19A-4BFB-835F-B6141B4F9EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BE796D-1C69-46C5-9651-D86A834B495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
@@ -2760,25 +2760,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2799,6 +2794,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2811,24 +2827,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3302,18 +3302,18 @@
       <c r="AE3" s="9"/>
     </row>
     <row r="4" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="45" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -3376,15 +3376,15 @@
       <c r="M5" s="25">
         <v>12</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="39">
         <f>M5+1</f>
         <v>13</v>
       </c>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="42"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="41"/>
       <c r="T5" s="24">
         <v>14</v>
       </c>
@@ -3442,110 +3442,110 @@
       </c>
     </row>
     <row r="6" spans="1:33" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="37" t="s">
         <v>388</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="37" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="L6" s="37" t="s">
         <v>342</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="N6" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="35" t="s">
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="V6" s="35" t="s">
+      <c r="V6" s="37" t="s">
         <v>350</v>
       </c>
-      <c r="W6" s="35" t="s">
+      <c r="W6" s="37" t="s">
         <v>351</v>
       </c>
-      <c r="X6" s="35" t="s">
+      <c r="X6" s="37" t="s">
         <v>355</v>
       </c>
-      <c r="Y6" s="35" t="s">
+      <c r="Y6" s="37" t="s">
         <v>356</v>
       </c>
-      <c r="Z6" s="35" t="s">
+      <c r="Z6" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="AA6" s="35" t="s">
+      <c r="AA6" s="37" t="s">
         <v>358</v>
       </c>
-      <c r="AB6" s="35" t="s">
+      <c r="AB6" s="37" t="s">
         <v>359</v>
       </c>
-      <c r="AC6" s="35" t="s">
+      <c r="AC6" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="AD6" s="35" t="s">
+      <c r="AD6" s="37" t="s">
         <v>361</v>
       </c>
-      <c r="AE6" s="35" t="s">
+      <c r="AE6" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="AF6" s="39" t="s">
+      <c r="AF6" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="AG6" s="39" t="s">
+      <c r="AG6" s="36" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
       <c r="N7" s="19" t="s">
         <v>344</v>
       </c>
@@ -3564,20 +3564,20 @@
       <c r="S7" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="36"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
@@ -28781,6 +28781,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="T6:T7"/>
     <mergeCell ref="AF6:AF7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="AG6:AG7"/>
@@ -28797,20 +28811,6 @@
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="AB6:AB7"/>
     <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="T6:T7"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB8:AB567" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -28873,11 +28873,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -28887,11 +28887,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -28906,10 +28906,10 @@
       <c r="B4" s="28">
         <v>1</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="52"/>
+      <c r="D4" s="51"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -28922,10 +28922,10 @@
       <c r="B5" s="28">
         <v>2</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="52" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="47"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -28937,10 +28937,10 @@
       <c r="B6" s="28">
         <v>3</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="52" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="47"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -28955,10 +28955,10 @@
       <c r="B7" s="28">
         <v>4</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="52" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="47"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -28973,10 +28973,10 @@
       <c r="B8" s="28">
         <v>5</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="52" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -28991,10 +28991,10 @@
       <c r="B9" s="28">
         <v>6</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="52" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="47"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -29009,10 +29009,10 @@
       <c r="B10" s="28">
         <v>7</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="47"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -29027,10 +29027,10 @@
       <c r="B11" s="28">
         <v>8</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="52" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="47"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -29045,10 +29045,10 @@
       <c r="B12" s="28">
         <v>9</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="52" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="47"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
@@ -29061,10 +29061,10 @@
       <c r="B13" s="28">
         <v>10</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="52" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="47"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
@@ -29077,10 +29077,10 @@
       <c r="B14" s="28">
         <v>11</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="52" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="47"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
@@ -29093,10 +29093,10 @@
       <c r="B15" s="28">
         <v>12</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="52" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="47"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -29108,11 +29108,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="49">
+      <c r="B16" s="55">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>349</v>
       </c>
       <c r="D16" s="29" t="s">
@@ -29129,8 +29129,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="49"/>
       <c r="D17" s="29" t="s">
         <v>345</v>
       </c>
@@ -29145,8 +29145,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="29" t="s">
         <v>346</v>
       </c>
@@ -29161,8 +29161,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="29" t="s">
         <v>347</v>
       </c>
@@ -29177,8 +29177,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="29" t="s">
         <v>348</v>
       </c>
@@ -29193,8 +29193,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="49"/>
       <c r="D21" s="29" t="s">
         <v>352</v>
       </c>
@@ -29212,10 +29212,10 @@
       <c r="B22" s="30">
         <v>14</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="52" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="47"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -29231,10 +29231,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="52" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="47"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -29250,10 +29250,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="52" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="47"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -29269,10 +29269,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="52" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="47"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -29288,10 +29288,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="52" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="47"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -29307,10 +29307,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="52" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="47"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -29326,10 +29326,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="52" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="47"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -29345,10 +29345,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="52" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="47"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -29364,10 +29364,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="52" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="47"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -29383,10 +29383,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="52" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="47"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -29402,10 +29402,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="52" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="47"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -29419,10 +29419,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="52" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="47"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -29438,10 +29438,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="50"/>
+      <c r="D34" s="49"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -29457,10 +29457,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="49" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="50"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
@@ -29474,6 +29474,20 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29490,20 +29504,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -29538,7 +29538,7 @@
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="33" t="s">
         <v>390</v>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="33" t="s">
         <v>391</v>
       </c>
     </row>
@@ -29560,7 +29560,7 @@
       <c r="B4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="33" t="s">
         <v>392</v>
       </c>
     </row>
@@ -29571,7 +29571,7 @@
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="33" t="s">
         <v>393</v>
       </c>
     </row>
@@ -29582,7 +29582,7 @@
       <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="33" t="s">
         <v>394</v>
       </c>
     </row>
@@ -29593,7 +29593,7 @@
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="33" t="s">
         <v>395</v>
       </c>
     </row>
@@ -29604,7 +29604,7 @@
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="34" t="s">
         <v>396</v>
       </c>
     </row>
@@ -29615,7 +29615,7 @@
       <c r="B9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="34" t="s">
         <v>397</v>
       </c>
     </row>
@@ -29626,7 +29626,7 @@
       <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="33" t="s">
         <v>398</v>
       </c>
     </row>
@@ -29637,7 +29637,7 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="34" t="s">
         <v>399</v>
       </c>
     </row>
@@ -29648,7 +29648,7 @@
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="33" t="s">
         <v>400</v>
       </c>
     </row>
@@ -29659,7 +29659,7 @@
       <c r="B13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="33" t="s">
         <v>401</v>
       </c>
     </row>
@@ -29670,7 +29670,7 @@
       <c r="B14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="33" t="s">
         <v>402</v>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       <c r="B15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="33" t="s">
         <v>403</v>
       </c>
     </row>
@@ -29692,7 +29692,7 @@
       <c r="B16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="33" t="s">
         <v>404</v>
       </c>
     </row>
@@ -29703,7 +29703,7 @@
       <c r="B17" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="33" t="s">
         <v>405</v>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       <c r="B18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="33" t="s">
         <v>406</v>
       </c>
     </row>
@@ -29725,7 +29725,7 @@
       <c r="B19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="34" t="s">
         <v>407</v>
       </c>
     </row>
@@ -29736,7 +29736,7 @@
       <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="34" t="s">
         <v>408</v>
       </c>
     </row>
@@ -29747,7 +29747,7 @@
       <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="34" t="s">
         <v>409</v>
       </c>
     </row>
@@ -29758,7 +29758,7 @@
       <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="33" t="s">
         <v>410</v>
       </c>
     </row>
@@ -29769,7 +29769,7 @@
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="34" t="s">
         <v>411</v>
       </c>
     </row>
@@ -29780,7 +29780,7 @@
       <c r="B24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="33" t="s">
         <v>412</v>
       </c>
     </row>
@@ -29791,7 +29791,7 @@
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="34" t="s">
         <v>413</v>
       </c>
     </row>
@@ -29802,7 +29802,7 @@
       <c r="B26" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="34" t="s">
         <v>414</v>
       </c>
     </row>
@@ -29813,7 +29813,7 @@
       <c r="B27" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="33" t="s">
         <v>415</v>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="D28" s="33" t="s">
         <v>416</v>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       <c r="B29" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="34" t="s">
         <v>417</v>
       </c>
     </row>
@@ -29846,7 +29846,7 @@
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="34" t="s">
         <v>418</v>
       </c>
     </row>
@@ -29857,7 +29857,7 @@
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="33" t="s">
         <v>419</v>
       </c>
     </row>
@@ -29868,7 +29868,7 @@
       <c r="B32" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="33" t="s">
         <v>420</v>
       </c>
     </row>
@@ -29879,7 +29879,7 @@
       <c r="B33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="33" t="s">
         <v>421</v>
       </c>
     </row>
@@ -29890,7 +29890,7 @@
       <c r="B34" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="33" t="s">
         <v>422</v>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       <c r="B35" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="33" t="s">
         <v>423</v>
       </c>
     </row>
@@ -29912,7 +29912,7 @@
       <c r="B36" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="33" t="s">
         <v>424</v>
       </c>
     </row>
@@ -29923,7 +29923,7 @@
       <c r="B37" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="33" t="s">
         <v>425</v>
       </c>
     </row>
@@ -29934,7 +29934,7 @@
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="55" t="s">
+      <c r="D38" s="34" t="s">
         <v>426</v>
       </c>
     </row>
@@ -29945,7 +29945,7 @@
       <c r="B39" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="33" t="s">
         <v>427</v>
       </c>
     </row>
@@ -29956,7 +29956,7 @@
       <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="33" t="s">
         <v>428</v>
       </c>
     </row>
@@ -29967,7 +29967,7 @@
       <c r="B41" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="D41" s="33" t="s">
         <v>429</v>
       </c>
     </row>
@@ -29978,7 +29978,7 @@
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="54" t="s">
+      <c r="D42" s="33" t="s">
         <v>430</v>
       </c>
     </row>
@@ -29989,7 +29989,7 @@
       <c r="B43" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="D43" s="33" t="s">
         <v>431</v>
       </c>
     </row>
@@ -30000,7 +30000,7 @@
       <c r="B44" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D44" s="33" t="s">
         <v>432</v>
       </c>
     </row>
@@ -30011,7 +30011,7 @@
       <c r="B45" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="33" t="s">
         <v>433</v>
       </c>
     </row>
@@ -30022,7 +30022,7 @@
       <c r="B46" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="54" t="s">
+      <c r="D46" s="33" t="s">
         <v>434</v>
       </c>
     </row>
@@ -30033,7 +30033,7 @@
       <c r="B47" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="54" t="s">
+      <c r="D47" s="33" t="s">
         <v>435</v>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       <c r="B48" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="D48" s="33" t="s">
         <v>436</v>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       <c r="B49" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="D49" s="33" t="s">
         <v>437</v>
       </c>
     </row>
@@ -30066,7 +30066,7 @@
       <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D50" s="33" t="s">
         <v>438</v>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       <c r="B51" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="54" t="s">
+      <c r="D51" s="33" t="s">
         <v>439</v>
       </c>
     </row>
@@ -30088,7 +30088,7 @@
       <c r="B52" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="54" t="s">
+      <c r="D52" s="33" t="s">
         <v>440</v>
       </c>
     </row>
@@ -30099,7 +30099,7 @@
       <c r="B53" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="54" t="s">
+      <c r="D53" s="33" t="s">
         <v>441</v>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
       <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="55" t="s">
+      <c r="D54" s="34" t="s">
         <v>442</v>
       </c>
     </row>
@@ -30121,7 +30121,7 @@
       <c r="B55" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="34" t="s">
         <v>443</v>
       </c>
     </row>
@@ -30132,7 +30132,7 @@
       <c r="B56" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D56" s="34" t="s">
         <v>444</v>
       </c>
     </row>
@@ -30143,7 +30143,7 @@
       <c r="B57" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="54" t="s">
+      <c r="D57" s="33" t="s">
         <v>445</v>
       </c>
     </row>
@@ -30154,7 +30154,7 @@
       <c r="B58" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="54" t="s">
+      <c r="D58" s="33" t="s">
         <v>446</v>
       </c>
     </row>
@@ -30165,7 +30165,7 @@
       <c r="B59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="55" t="s">
+      <c r="D59" s="34" t="s">
         <v>447</v>
       </c>
     </row>
@@ -30176,7 +30176,7 @@
       <c r="B60" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D60" s="54" t="s">
+      <c r="D60" s="33" t="s">
         <v>448</v>
       </c>
     </row>
@@ -30187,7 +30187,7 @@
       <c r="B61" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="54" t="s">
+      <c r="D61" s="33" t="s">
         <v>449</v>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       <c r="B62" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="54" t="s">
+      <c r="D62" s="33" t="s">
         <v>450</v>
       </c>
     </row>
@@ -30209,7 +30209,7 @@
       <c r="B63" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="54" t="s">
+      <c r="D63" s="33" t="s">
         <v>451</v>
       </c>
     </row>
@@ -30220,7 +30220,7 @@
       <c r="B64" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="54" t="s">
+      <c r="D64" s="33" t="s">
         <v>452</v>
       </c>
     </row>
@@ -30231,7 +30231,7 @@
       <c r="B65" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D65" s="54" t="s">
+      <c r="D65" s="33" t="s">
         <v>453</v>
       </c>
     </row>
@@ -30242,7 +30242,7 @@
       <c r="B66" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="54" t="s">
+      <c r="D66" s="33" t="s">
         <v>454</v>
       </c>
     </row>
@@ -30253,7 +30253,7 @@
       <c r="B67" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="55" t="s">
+      <c r="D67" s="34" t="s">
         <v>455</v>
       </c>
     </row>
@@ -30264,7 +30264,7 @@
       <c r="B68" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="55" t="s">
+      <c r="D68" s="34" t="s">
         <v>456</v>
       </c>
     </row>
@@ -30275,7 +30275,7 @@
       <c r="B69" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="54" t="s">
+      <c r="D69" s="33" t="s">
         <v>457</v>
       </c>
     </row>
@@ -30286,7 +30286,7 @@
       <c r="B70" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="55" t="s">
+      <c r="D70" s="34" t="s">
         <v>458</v>
       </c>
     </row>
@@ -30297,7 +30297,7 @@
       <c r="B71" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D71" s="54" t="s">
+      <c r="D71" s="33" t="s">
         <v>459</v>
       </c>
     </row>
@@ -30308,7 +30308,7 @@
       <c r="B72" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="54" t="s">
+      <c r="D72" s="33" t="s">
         <v>460</v>
       </c>
     </row>
@@ -30319,7 +30319,7 @@
       <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="54" t="s">
+      <c r="D73" s="33" t="s">
         <v>461</v>
       </c>
     </row>
@@ -30330,7 +30330,7 @@
       <c r="B74" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="54" t="s">
+      <c r="D74" s="33" t="s">
         <v>462</v>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       <c r="B75" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="54" t="s">
+      <c r="D75" s="33" t="s">
         <v>463</v>
       </c>
     </row>
@@ -30352,7 +30352,7 @@
       <c r="B76" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="54" t="s">
+      <c r="D76" s="33" t="s">
         <v>464</v>
       </c>
     </row>
@@ -30363,7 +30363,7 @@
       <c r="B77" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D77" s="54" t="s">
+      <c r="D77" s="33" t="s">
         <v>465</v>
       </c>
     </row>
@@ -30374,7 +30374,7 @@
       <c r="B78" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D78" s="54" t="s">
+      <c r="D78" s="33" t="s">
         <v>466</v>
       </c>
     </row>
@@ -30385,7 +30385,7 @@
       <c r="B79" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="54" t="s">
+      <c r="D79" s="33" t="s">
         <v>467</v>
       </c>
     </row>
@@ -30396,7 +30396,7 @@
       <c r="B80" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="54" t="s">
+      <c r="D80" s="33" t="s">
         <v>468</v>
       </c>
     </row>
@@ -30407,7 +30407,7 @@
       <c r="B81" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D81" s="54" t="s">
+      <c r="D81" s="33" t="s">
         <v>469</v>
       </c>
     </row>
@@ -30418,7 +30418,7 @@
       <c r="B82" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D82" s="55" t="s">
+      <c r="D82" s="34" t="s">
         <v>470</v>
       </c>
     </row>
@@ -30429,7 +30429,7 @@
       <c r="B83" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D83" s="54" t="s">
+      <c r="D83" s="33" t="s">
         <v>471</v>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
       <c r="B84" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D84" s="54" t="s">
+      <c r="D84" s="33" t="s">
         <v>472</v>
       </c>
     </row>
@@ -30451,7 +30451,7 @@
       <c r="B85" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="54" t="s">
+      <c r="D85" s="33" t="s">
         <v>473</v>
       </c>
     </row>
@@ -30462,7 +30462,7 @@
       <c r="B86" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="55" t="s">
+      <c r="D86" s="34" t="s">
         <v>474</v>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       <c r="B87" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="54" t="s">
+      <c r="D87" s="33" t="s">
         <v>475</v>
       </c>
     </row>
@@ -30484,7 +30484,7 @@
       <c r="B88" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D88" s="54" t="s">
+      <c r="D88" s="33" t="s">
         <v>476</v>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       <c r="B89" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D89" s="54" t="s">
+      <c r="D89" s="33" t="s">
         <v>477</v>
       </c>
     </row>
@@ -30506,7 +30506,7 @@
       <c r="B90" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="54" t="s">
+      <c r="D90" s="33" t="s">
         <v>478</v>
       </c>
     </row>
@@ -30517,7 +30517,7 @@
       <c r="B91" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="54" t="s">
+      <c r="D91" s="33" t="s">
         <v>479</v>
       </c>
     </row>
@@ -30528,7 +30528,7 @@
       <c r="B92" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="54" t="s">
+      <c r="D92" s="33" t="s">
         <v>480</v>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       <c r="B93" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D93" s="54" t="s">
+      <c r="D93" s="33" t="s">
         <v>481</v>
       </c>
     </row>
@@ -30550,7 +30550,7 @@
       <c r="B94" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D94" s="54" t="s">
+      <c r="D94" s="33" t="s">
         <v>482</v>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
       <c r="B95" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="54" t="s">
+      <c r="D95" s="33" t="s">
         <v>483</v>
       </c>
     </row>
@@ -30572,7 +30572,7 @@
       <c r="B96" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D96" s="55" t="s">
+      <c r="D96" s="34" t="s">
         <v>484</v>
       </c>
     </row>
@@ -30583,7 +30583,7 @@
       <c r="B97" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D97" s="54" t="s">
+      <c r="D97" s="33" t="s">
         <v>485</v>
       </c>
     </row>
@@ -30594,7 +30594,7 @@
       <c r="B98" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="D98" s="54" t="s">
+      <c r="D98" s="33" t="s">
         <v>486</v>
       </c>
     </row>
@@ -30605,7 +30605,7 @@
       <c r="B99" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D99" s="54" t="s">
+      <c r="D99" s="33" t="s">
         <v>487</v>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D100" s="54" t="s">
+      <c r="D100" s="33" t="s">
         <v>488</v>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       <c r="B101" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="54" t="s">
+      <c r="D101" s="33" t="s">
         <v>489</v>
       </c>
     </row>
@@ -30638,7 +30638,7 @@
       <c r="B102" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="54" t="s">
+      <c r="D102" s="33" t="s">
         <v>490</v>
       </c>
     </row>
@@ -30649,7 +30649,7 @@
       <c r="B103" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D103" s="54" t="s">
+      <c r="D103" s="33" t="s">
         <v>491</v>
       </c>
     </row>
@@ -30660,7 +30660,7 @@
       <c r="B104" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D104" s="54" t="s">
+      <c r="D104" s="33" t="s">
         <v>492</v>
       </c>
     </row>
@@ -30671,7 +30671,7 @@
       <c r="B105" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D105" s="55" t="s">
+      <c r="D105" s="34" t="s">
         <v>493</v>
       </c>
     </row>
@@ -30682,7 +30682,7 @@
       <c r="B106" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D106" s="55" t="s">
+      <c r="D106" s="34" t="s">
         <v>494</v>
       </c>
     </row>
@@ -30693,7 +30693,7 @@
       <c r="B107" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="54" t="s">
+      <c r="D107" s="33" t="s">
         <v>495</v>
       </c>
     </row>
@@ -30715,7 +30715,7 @@
       <c r="B109" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D109" s="56" t="s">
+      <c r="D109" s="35" t="s">
         <v>497</v>
       </c>
     </row>
@@ -30748,7 +30748,7 @@
       <c r="B112" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D112" s="54" t="s">
+      <c r="D112" s="33" t="s">
         <v>500</v>
       </c>
     </row>
@@ -31244,12 +31244,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>

--- a/wwwroot/template/TemPlateApproverQuote.xlsx
+++ b/wwwroot/template/TemPlateApproverQuote.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BE796D-1C69-46C5-9651-D86A834B495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6985D257-6262-473B-92A4-3BC69FD33605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
-    <sheet name="フォーム説明" sheetId="7" r:id="rId2"/>
-    <sheet name="Master" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Input form (ex)" sheetId="8" r:id="rId2"/>
+    <sheet name="フォーム説明" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="Master" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">フォーム説明!$B$1:$H$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">フォーム説明!$B$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -666,7 +670,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="522">
   <si>
     <t>No</t>
   </si>
@@ -2436,6 +2440,70 @@
   <si>
     <t>Pallet</t>
   </si>
+  <si>
+    <t>Phải điền</t>
+  </si>
+  <si>
+    <t>Không cần điền</t>
+  </si>
+  <si>
+    <t>Có nhu cầu thì điền</t>
+  </si>
+  <si>
+    <t>Đọc lại điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mã cũ (mã đã có trong file master). </t>
+  </si>
+  <si>
+    <t>Lí do xin báo giá
+Reason for quotation request</t>
+  </si>
+  <si>
+    <t>O00000863</t>
+  </si>
+  <si>
+    <t>Nếu là mã ngoài danh mục có thiết kế: Phải đính kèm</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>O00000864</t>
+  </si>
+  <si>
+    <t>Nếu là mã tiêu chuẩn: Không cần</t>
+  </si>
+  <si>
+    <t>O00000865</t>
+  </si>
+  <si>
+    <t>Nếu là sữar chữa/bảo dưỡng/thi công...: cần copy link format PL12 hoặc PL13</t>
+  </si>
+  <si>
+    <t>2. Mã mới : Chưa mua bao giờ</t>
+  </si>
+  <si>
+    <t>cái/chiếc</t>
+  </si>
+  <si>
+    <t>Up ngoài phần lựa chọn &gt;&gt; báo lỗi ko up được</t>
+  </si>
+  <si>
+    <t>Không được để trống</t>
+  </si>
+  <si>
+    <t>Phải điền, với hàng dịch vụ ghi "-"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hệ thống báo lỗi file nếu PIC cố tình thêm NCC ko có trong MAP tương ứng chủng loại (VD: chủng loại A chỉ có 2 vendor , PIC cố tình add thêm vendor 3 &gt;&gt; báo lỗi ko cho up) </t>
+  </si>
+  <si>
+    <t>phải có trong MAP</t>
+  </si>
+  <si>
+    <t>Điền tay mà điền sai vendor code ko có trong MAP &gt;&gt; báo lỗi ko cho up</t>
+  </si>
 </sst>
 </file>
 
@@ -2444,7 +2512,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2544,8 +2612,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2570,8 +2666,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2666,11 +2786,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2767,13 +2954,31 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2794,27 +2999,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2827,8 +3011,128 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2850,6 +3154,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Form blank"/>
+      <sheetName val="フォーム説明"/>
+      <sheetName val="Master"/>
+      <sheetName val="Sheet4"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3302,18 +3628,18 @@
       <c r="AE3" s="9"/>
     </row>
     <row r="4" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -3376,15 +3702,15 @@
       <c r="M5" s="25">
         <v>12</v>
       </c>
-      <c r="N5" s="39">
+      <c r="N5" s="45">
         <f>M5+1</f>
         <v>13</v>
       </c>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="41"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="47"/>
       <c r="T5" s="24">
         <v>14</v>
       </c>
@@ -3442,110 +3768,110 @@
       </c>
     </row>
     <row r="6" spans="1:33" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="N6" s="48" t="s">
         <v>349</v>
       </c>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="37" t="s">
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="40" t="s">
         <v>353</v>
       </c>
-      <c r="U6" s="37" t="s">
+      <c r="U6" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="V6" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="W6" s="37" t="s">
+      <c r="W6" s="40" t="s">
         <v>351</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="X6" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="Y6" s="37" t="s">
+      <c r="Y6" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="Z6" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="AB6" s="37" t="s">
+      <c r="AB6" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="AC6" s="37" t="s">
+      <c r="AC6" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="AD6" s="37" t="s">
+      <c r="AD6" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="AE6" s="37" t="s">
+      <c r="AE6" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="AF6" s="36" t="s">
+      <c r="AF6" s="44" t="s">
         <v>363</v>
       </c>
-      <c r="AG6" s="36" t="s">
+      <c r="AG6" s="44" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="48"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
       <c r="N7" s="19" t="s">
         <v>344</v>
       </c>
@@ -3564,20 +3890,20 @@
       <c r="S7" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
@@ -28781,20 +29107,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="T6:T7"/>
     <mergeCell ref="AF6:AF7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="AG6:AG7"/>
@@ -28811,6 +29123,20 @@
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="AB6:AB7"/>
     <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="T6:T7"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB8:AB567" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -28853,6 +29179,1076 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F14715-33DD-4AD1-AAA5-A602831337A4}">
+  <dimension ref="A1:AG21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="52.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="59"/>
+      <c r="B1" s="60" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>502</v>
+      </c>
+      <c r="E1" s="63" t="s">
+        <v>503</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="59"/>
+      <c r="E2" s="59"/>
+    </row>
+    <row r="3" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="66">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25">
+        <v>2</v>
+      </c>
+      <c r="C4" s="25">
+        <v>3</v>
+      </c>
+      <c r="D4" s="25">
+        <v>4</v>
+      </c>
+      <c r="E4" s="25">
+        <v>5</v>
+      </c>
+      <c r="F4" s="25">
+        <v>6</v>
+      </c>
+      <c r="G4" s="25">
+        <v>7</v>
+      </c>
+      <c r="H4" s="25">
+        <v>8</v>
+      </c>
+      <c r="I4" s="25">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25">
+        <v>10</v>
+      </c>
+      <c r="K4" s="25">
+        <v>11</v>
+      </c>
+      <c r="L4" s="25">
+        <v>12</v>
+      </c>
+      <c r="M4" s="45">
+        <f>L4+1</f>
+        <v>13</v>
+      </c>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="37">
+        <v>14</v>
+      </c>
+      <c r="T4" s="25">
+        <f>S4+1</f>
+        <v>15</v>
+      </c>
+      <c r="U4" s="25">
+        <f t="shared" ref="U4:AF4" si="0">T4+1</f>
+        <v>16</v>
+      </c>
+      <c r="V4" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W4" s="25">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="X4" s="25">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y4" s="25">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z4" s="25">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AA4" s="25">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB4" s="25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC4" s="25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AD4" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AE4" s="25">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AF4" s="36">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AG4" s="25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="I5" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="J5" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="K5" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="L5" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="M5" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="T5" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="U5" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="V5" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="W5" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="X5" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y5" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z5" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA5" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB5" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="AC5" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="AD5" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE5" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF5" s="70" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG5" s="73" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="74"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="76" t="s">
+        <v>344</v>
+      </c>
+      <c r="N6" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="O6" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="P6" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q6" s="76" t="s">
+        <v>348</v>
+      </c>
+      <c r="R6" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="70"/>
+      <c r="AG6" s="73"/>
+    </row>
+    <row r="7" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="77">
+        <v>1</v>
+      </c>
+      <c r="B7" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C7" s="79" t="e">
+        <f>VLOOKUP(B7,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="78" t="s">
+        <v>507</v>
+      </c>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81" t="str">
+        <f>L7&amp;"có hình dáng dạng "&amp;M7&amp;" chất liệu "&amp;N7&amp;" thành phần hóa chất: "&amp;O7&amp;" có kích thước "&amp;P7&amp;" dùng để "&amp;R7&amp;" cho "&amp;Q7</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I7" s="81"/>
+      <c r="J7" s="78">
+        <v>10</v>
+      </c>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="84" t="s">
+        <v>508</v>
+      </c>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="85" t="s">
+        <v>509</v>
+      </c>
+      <c r="AB7" s="80"/>
+      <c r="AC7" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD7" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE7" s="80"/>
+      <c r="AF7" s="87"/>
+      <c r="AG7" s="80"/>
+    </row>
+    <row r="8" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="77">
+        <v>2</v>
+      </c>
+      <c r="B8" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C8" s="79" t="e">
+        <f>VLOOKUP(B8,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="78" t="s">
+        <v>510</v>
+      </c>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81" t="str">
+        <f t="shared" ref="H8:H9" si="1">L8&amp;"có hình dáng dạng "&amp;M8&amp;" chất liệu "&amp;N8&amp;" thành phần hóa chất: "&amp;O8&amp;" có kích thước "&amp;P8&amp;" dùng để "&amp;R8&amp;" cho "&amp;Q8</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I8" s="81"/>
+      <c r="J8" s="78">
+        <v>10</v>
+      </c>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="84" t="s">
+        <v>511</v>
+      </c>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD8" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="87"/>
+      <c r="AG8" s="80"/>
+    </row>
+    <row r="9" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="77">
+        <v>3</v>
+      </c>
+      <c r="B9" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C9" s="79" t="e">
+        <f>VLOOKUP(B9,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="78" t="s">
+        <v>512</v>
+      </c>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I9" s="81"/>
+      <c r="J9" s="78">
+        <v>10</v>
+      </c>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="84" t="s">
+        <v>513</v>
+      </c>
+      <c r="X9" s="81"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD9" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="87"/>
+      <c r="AG9" s="80"/>
+    </row>
+    <row r="10" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H10" s="62" t="str">
+        <f t="shared" ref="H10:H11" si="2">M10&amp;" "&amp;N10&amp;" "&amp;O10&amp;""&amp;P10&amp;" "&amp;Q10&amp;" "&amp;R10</f>
+        <v xml:space="preserve">    </v>
+      </c>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="AA10" s="89"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="90"/>
+    </row>
+    <row r="11" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H11" s="62" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    </v>
+      </c>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="AA11" s="89"/>
+      <c r="AC11" s="90"/>
+      <c r="AD11" s="90"/>
+    </row>
+    <row r="12" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="65" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="66">
+        <v>1</v>
+      </c>
+      <c r="B13" s="25">
+        <v>2</v>
+      </c>
+      <c r="C13" s="25">
+        <v>3</v>
+      </c>
+      <c r="D13" s="25">
+        <v>4</v>
+      </c>
+      <c r="E13" s="25">
+        <v>5</v>
+      </c>
+      <c r="F13" s="25">
+        <v>6</v>
+      </c>
+      <c r="G13" s="25">
+        <v>7</v>
+      </c>
+      <c r="H13" s="25">
+        <v>8</v>
+      </c>
+      <c r="I13" s="25">
+        <v>9</v>
+      </c>
+      <c r="J13" s="25">
+        <v>10</v>
+      </c>
+      <c r="K13" s="25">
+        <v>11</v>
+      </c>
+      <c r="L13" s="25">
+        <v>12</v>
+      </c>
+      <c r="M13" s="45">
+        <f>L13+1</f>
+        <v>13</v>
+      </c>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="37">
+        <v>14</v>
+      </c>
+      <c r="T13" s="25">
+        <f>S13+1</f>
+        <v>15</v>
+      </c>
+      <c r="U13" s="25">
+        <f t="shared" ref="U13:AF13" si="3">T13+1</f>
+        <v>16</v>
+      </c>
+      <c r="V13" s="25">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="W13" s="25">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="X13" s="25">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="Y13" s="25">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="Z13" s="25">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="AA13" s="25">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="AB13" s="25">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="AC13" s="25">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="AD13" s="25">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="AE13" s="25">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="AF13" s="91">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="AG13" s="25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="J14" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="M14" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="T14" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="U14" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="V14" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="W14" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="X14" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y14" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z14" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA14" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB14" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="AC14" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="AD14" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE14" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF14" s="92" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG14" s="73" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="74"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76" t="s">
+        <v>344</v>
+      </c>
+      <c r="N15" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="O15" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="P15" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q15" s="76" t="s">
+        <v>348</v>
+      </c>
+      <c r="R15" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="S15" s="75"/>
+      <c r="T15" s="75"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="75"/>
+      <c r="W15" s="75"/>
+      <c r="X15" s="75"/>
+      <c r="Y15" s="75"/>
+      <c r="Z15" s="75"/>
+      <c r="AA15" s="75"/>
+      <c r="AB15" s="75"/>
+      <c r="AC15" s="75"/>
+      <c r="AD15" s="75"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="92"/>
+      <c r="AG15" s="73"/>
+    </row>
+    <row r="16" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="77">
+        <v>1</v>
+      </c>
+      <c r="B16" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C16" s="79" t="e">
+        <f>VLOOKUP(B16,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="78"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="81" t="str">
+        <f>L16&amp;"có hình dáng dạng "&amp;M16&amp;" chất liệu "&amp;N16&amp;" thành phần hóa chất: "&amp;O16&amp;" có kích thước "&amp;P16&amp;" dùng để "&amp;R16&amp;" cho "&amp;Q16</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78">
+        <v>10</v>
+      </c>
+      <c r="K16" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="84" t="s">
+        <v>508</v>
+      </c>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="81"/>
+      <c r="AA16" s="85" t="s">
+        <v>509</v>
+      </c>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD16" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE16" s="80"/>
+      <c r="AF16" s="94"/>
+      <c r="AG16" s="80"/>
+    </row>
+    <row r="17" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="77">
+        <v>2</v>
+      </c>
+      <c r="B17" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C17" s="79" t="e">
+        <f>VLOOKUP(B17,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="78"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="81" t="str">
+        <f t="shared" ref="H17:H19" si="4">L17&amp;"có hình dáng dạng "&amp;M17&amp;" chất liệu "&amp;N17&amp;" thành phần hóa chất: "&amp;O17&amp;" có kích thước "&amp;P17&amp;" dùng để "&amp;R17&amp;" cho "&amp;Q17</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78">
+        <v>10</v>
+      </c>
+      <c r="K17" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="84" t="s">
+        <v>511</v>
+      </c>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="80"/>
+      <c r="AC17" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD17" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE17" s="80"/>
+      <c r="AF17" s="94"/>
+      <c r="AG17" s="80"/>
+    </row>
+    <row r="18" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="77">
+        <v>3</v>
+      </c>
+      <c r="B18" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C18" s="79" t="e">
+        <f>VLOOKUP(B18,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="78"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78">
+        <v>10</v>
+      </c>
+      <c r="K18" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="78"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="84" t="s">
+        <v>513</v>
+      </c>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="80"/>
+      <c r="AC18" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD18" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="94"/>
+      <c r="AG18" s="80"/>
+    </row>
+    <row r="19" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="77">
+        <v>3</v>
+      </c>
+      <c r="B19" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C19" s="79" t="e">
+        <f>VLOOKUP(B19,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="78"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78">
+        <v>10</v>
+      </c>
+      <c r="K19" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="84" t="s">
+        <v>513</v>
+      </c>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD19" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE19" s="80"/>
+      <c r="AF19" s="94"/>
+      <c r="AG19" s="94"/>
+    </row>
+    <row r="20" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="95" t="s">
+        <v>516</v>
+      </c>
+      <c r="D20" s="95" t="s">
+        <v>516</v>
+      </c>
+      <c r="K20" s="95" t="s">
+        <v>516</v>
+      </c>
+      <c r="L20" s="95" t="s">
+        <v>517</v>
+      </c>
+      <c r="M20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="N20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="O20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="P20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="R20" s="95" t="s">
+        <v>518</v>
+      </c>
+      <c r="Y20" s="95" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="L21" s="95" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y21" s="95" t="s">
+        <v>521</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:R14"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="M13:R13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA7:AA11 AA16:AA18" xr:uid="{7148D881-3CE6-40B6-9B29-09D7A050C101}">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D11 D16:D18" xr:uid="{FDC3D732-F935-4BDC-8886-6FDA35E5E73C}">
+      <formula1>"A,E,Ngoài danh mục"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE7:AE11 AE16:AE18" xr:uid="{30D041A7-3425-4EC4-A098-9DC8E11BF9A1}">
+      <formula1>" ,O"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S10:S11" xr:uid="{94B4A679-687B-47A3-AC9A-1414E213AFCA}">
+      <formula1>",Need (cần)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T11" xr:uid="{21EA1E4E-98F5-4D4C-AFBF-011F2D0D3EDA}">
+      <formula1>"CO,CQ,CO&amp;CQ"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}">
   <dimension ref="B1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28873,11 +30269,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -28887,11 +30283,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -28906,10 +30302,10 @@
       <c r="B4" s="28">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="51"/>
+      <c r="D4" s="57"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -28922,10 +30318,10 @@
       <c r="B5" s="28">
         <v>2</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="51" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="53"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -28937,10 +30333,10 @@
       <c r="B6" s="28">
         <v>3</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="53"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -28955,10 +30351,10 @@
       <c r="B7" s="28">
         <v>4</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="53"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -28973,10 +30369,10 @@
       <c r="B8" s="28">
         <v>5</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="53"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -28991,10 +30387,10 @@
       <c r="B9" s="28">
         <v>6</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="53"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -29009,10 +30405,10 @@
       <c r="B10" s="28">
         <v>7</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="51" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="53"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -29027,10 +30423,10 @@
       <c r="B11" s="28">
         <v>8</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="53"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -29045,10 +30441,10 @@
       <c r="B12" s="28">
         <v>9</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="53"/>
+      <c r="D12" s="52"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
@@ -29061,10 +30457,10 @@
       <c r="B13" s="28">
         <v>10</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="53"/>
+      <c r="D13" s="52"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
@@ -29077,10 +30473,10 @@
       <c r="B14" s="28">
         <v>11</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="53"/>
+      <c r="D14" s="52"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
@@ -29093,10 +30489,10 @@
       <c r="B15" s="28">
         <v>12</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="53"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -29108,11 +30504,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="55">
+      <c r="B16" s="54">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="55" t="s">
         <v>349</v>
       </c>
       <c r="D16" s="29" t="s">
@@ -29129,8 +30525,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="55"/>
-      <c r="C17" s="49"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="29" t="s">
         <v>345</v>
       </c>
@@ -29145,8 +30541,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="55"/>
-      <c r="C18" s="49"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="29" t="s">
         <v>346</v>
       </c>
@@ -29161,8 +30557,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="55"/>
-      <c r="C19" s="49"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="29" t="s">
         <v>347</v>
       </c>
@@ -29177,8 +30573,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="55"/>
-      <c r="C20" s="49"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="29" t="s">
         <v>348</v>
       </c>
@@ -29193,8 +30589,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="55"/>
-      <c r="C21" s="49"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
       <c r="D21" s="29" t="s">
         <v>352</v>
       </c>
@@ -29212,10 +30608,10 @@
       <c r="B22" s="30">
         <v>14</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="53"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -29231,10 +30627,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="53"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -29250,10 +30646,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="53"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -29269,10 +30665,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="51" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="53"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -29288,10 +30684,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="53"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -29307,10 +30703,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="51" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="53"/>
+      <c r="D27" s="52"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -29326,10 +30722,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="53"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -29345,10 +30741,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="53"/>
+      <c r="D29" s="52"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -29364,10 +30760,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="53"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -29383,10 +30779,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="51" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="53"/>
+      <c r="D31" s="52"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -29402,10 +30798,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="53"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -29419,10 +30815,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="51" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="53"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -29438,10 +30834,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="55" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="49"/>
+      <c r="D34" s="55"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -29457,10 +30853,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="55" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="49"/>
+      <c r="D35" s="55"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
@@ -29474,20 +30870,6 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29504,13 +30886,27 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDAC048-C2F1-4ABA-B2C8-6CB3150A85B7}">
   <dimension ref="A1:D171"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
@@ -31223,7 +32619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13254DC6-374D-4986-96B0-F1A090138EDE}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31244,12 +32640,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>

--- a/wwwroot/template/TemPlateApproverQuote.xlsx
+++ b/wwwroot/template/TemPlateApproverQuote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6985D257-6262-473B-92A4-3BC69FD33605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
@@ -2857,7 +2857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2928,15 +2928,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2946,7 +2937,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2955,72 +2945,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3049,30 +2973,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3122,9 +3022,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3133,6 +3030,96 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3628,18 +3615,18 @@
       <c r="AE3" s="9"/>
     </row>
     <row r="4" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="70" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -3672,206 +3659,206 @@
       <c r="C5" s="22">
         <v>3</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="22">
         <v>4</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="22">
         <v>4</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="22">
         <v>5</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="22">
         <v>6</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="22">
         <v>7</v>
       </c>
-      <c r="I5" s="25">
-        <v>8</v>
-      </c>
-      <c r="J5" s="25">
+      <c r="I5" s="22">
+        <v>8</v>
+      </c>
+      <c r="J5" s="22">
         <v>9</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="22">
         <v>10</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="22">
         <v>11</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="22">
         <v>12</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="64">
         <f>M5+1</f>
         <v>13</v>
       </c>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="47"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="66"/>
       <c r="T5" s="24">
         <v>14</v>
       </c>
-      <c r="U5" s="25">
+      <c r="U5" s="22">
         <f>T5+1</f>
         <v>15</v>
       </c>
-      <c r="V5" s="25">
+      <c r="V5" s="22">
         <f t="shared" ref="V5:AG5" si="0">U5+1</f>
         <v>16</v>
       </c>
-      <c r="W5" s="25">
+      <c r="W5" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="X5" s="25">
+      <c r="X5" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="Y5" s="25">
+      <c r="Y5" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="Z5" s="25">
+      <c r="Z5" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AA5" s="25">
+      <c r="AA5" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AB5" s="25">
+      <c r="AB5" s="22">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AC5" s="25">
+      <c r="AC5" s="22">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="AD5" s="25">
+      <c r="AD5" s="22">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AE5" s="25">
+      <c r="AE5" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AF5" s="25">
+      <c r="AF5" s="22">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AG5" s="25">
+      <c r="AG5" s="22">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:33" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="62" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="62" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="62" t="s">
         <v>388</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="62" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="62" t="s">
         <v>336</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="62" t="s">
         <v>338</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="62" t="s">
         <v>339</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="62" t="s">
         <v>342</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="62" t="s">
         <v>343</v>
       </c>
-      <c r="N6" s="48" t="s">
+      <c r="N6" s="67" t="s">
         <v>349</v>
       </c>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="40" t="s">
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="62" t="s">
         <v>353</v>
       </c>
-      <c r="U6" s="40" t="s">
+      <c r="U6" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="V6" s="40" t="s">
+      <c r="V6" s="62" t="s">
         <v>350</v>
       </c>
-      <c r="W6" s="40" t="s">
+      <c r="W6" s="62" t="s">
         <v>351</v>
       </c>
-      <c r="X6" s="40" t="s">
+      <c r="X6" s="62" t="s">
         <v>355</v>
       </c>
-      <c r="Y6" s="40" t="s">
+      <c r="Y6" s="62" t="s">
         <v>356</v>
       </c>
-      <c r="Z6" s="40" t="s">
+      <c r="Z6" s="62" t="s">
         <v>357</v>
       </c>
-      <c r="AA6" s="40" t="s">
+      <c r="AA6" s="62" t="s">
         <v>358</v>
       </c>
-      <c r="AB6" s="40" t="s">
+      <c r="AB6" s="62" t="s">
         <v>359</v>
       </c>
-      <c r="AC6" s="40" t="s">
+      <c r="AC6" s="62" t="s">
         <v>360</v>
       </c>
-      <c r="AD6" s="40" t="s">
+      <c r="AD6" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="AE6" s="40" t="s">
+      <c r="AE6" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="AF6" s="44" t="s">
+      <c r="AF6" s="61" t="s">
         <v>363</v>
       </c>
-      <c r="AG6" s="44" t="s">
+      <c r="AG6" s="61" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:33" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
       <c r="N7" s="19" t="s">
         <v>344</v>
       </c>
@@ -3890,20 +3877,20 @@
       <c r="S7" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="41"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="44"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="63"/>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="63"/>
+      <c r="AA7" s="63"/>
+      <c r="AB7" s="63"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
@@ -29107,6 +29094,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="T6:T7"/>
     <mergeCell ref="AF6:AF7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="AG6:AG7"/>
@@ -29123,20 +29124,6 @@
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="AB6:AB7"/>
     <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="T6:T7"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB8:AB567" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -29187,1007 +29174,1009 @@
     <col min="8" max="8" width="52.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59"/>
-      <c r="B1" s="60" t="s">
+    <row r="1" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
         <v>501</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="35" t="s">
         <v>502</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="37" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="38" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
-      <c r="E2" s="59"/>
-    </row>
-    <row r="3" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+    <row r="2" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="E2" s="33"/>
+    </row>
+    <row r="3" spans="1:33" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+    <row r="4" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="40">
         <v>1</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="22">
         <v>2</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="22">
         <v>3</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="22">
         <v>4</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="22">
         <v>5</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="22">
         <v>6</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="22">
         <v>7</v>
       </c>
-      <c r="H4" s="25">
-        <v>8</v>
-      </c>
-      <c r="I4" s="25">
+      <c r="H4" s="22">
+        <v>8</v>
+      </c>
+      <c r="I4" s="22">
         <v>9</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="22">
         <v>10</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="22">
         <v>11</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="22">
         <v>12</v>
       </c>
-      <c r="M4" s="45">
+      <c r="M4" s="64">
         <f>L4+1</f>
         <v>13</v>
       </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="37">
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="24">
         <v>14</v>
       </c>
-      <c r="T4" s="25">
+      <c r="T4" s="22">
         <f>S4+1</f>
         <v>15</v>
       </c>
-      <c r="U4" s="25">
+      <c r="U4" s="22">
         <f t="shared" ref="U4:AF4" si="0">T4+1</f>
         <v>16</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="W4" s="25">
+      <c r="W4" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="X4" s="25">
+      <c r="X4" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="Y4" s="25">
+      <c r="Y4" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Z4" s="25">
+      <c r="Z4" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AA4" s="25">
+      <c r="AA4" s="22">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AB4" s="25">
+      <c r="AB4" s="22">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="AC4" s="25">
+      <c r="AC4" s="22">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AD4" s="25">
+      <c r="AD4" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="AE4" s="22">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AF4" s="36">
+      <c r="AF4" s="32">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AG4" s="25">
+      <c r="AG4" s="22">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+    <row r="5" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="76" t="s">
         <v>333</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="76" t="s">
         <v>334</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="76" t="s">
         <v>335</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="76" t="s">
         <v>336</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="76" t="s">
         <v>337</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="76" t="s">
         <v>338</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="76" t="s">
         <v>340</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="76" t="s">
         <v>341</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="76" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="69" t="s">
+      <c r="K5" s="76" t="s">
         <v>342</v>
       </c>
-      <c r="L5" s="69" t="s">
+      <c r="L5" s="76" t="s">
         <v>343</v>
       </c>
-      <c r="M5" s="70" t="s">
+      <c r="M5" s="78" t="s">
         <v>349</v>
       </c>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="69" t="s">
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="76" t="s">
         <v>353</v>
       </c>
-      <c r="T5" s="69" t="s">
+      <c r="T5" s="76" t="s">
         <v>354</v>
       </c>
-      <c r="U5" s="69" t="s">
+      <c r="U5" s="76" t="s">
         <v>350</v>
       </c>
-      <c r="V5" s="69" t="s">
+      <c r="V5" s="76" t="s">
         <v>351</v>
       </c>
-      <c r="W5" s="69" t="s">
+      <c r="W5" s="76" t="s">
         <v>355</v>
       </c>
-      <c r="X5" s="69" t="s">
+      <c r="X5" s="76" t="s">
         <v>356</v>
       </c>
-      <c r="Y5" s="69" t="s">
+      <c r="Y5" s="76" t="s">
         <v>357</v>
       </c>
-      <c r="Z5" s="69" t="s">
+      <c r="Z5" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="AA5" s="69" t="s">
+      <c r="AA5" s="76" t="s">
         <v>359</v>
       </c>
-      <c r="AB5" s="69" t="s">
+      <c r="AB5" s="76" t="s">
         <v>360</v>
       </c>
-      <c r="AC5" s="69" t="s">
+      <c r="AC5" s="76" t="s">
         <v>361</v>
       </c>
-      <c r="AD5" s="69" t="s">
+      <c r="AD5" s="76" t="s">
         <v>362</v>
       </c>
-      <c r="AE5" s="73" t="s">
+      <c r="AE5" s="75" t="s">
         <v>363</v>
       </c>
-      <c r="AF5" s="70" t="s">
+      <c r="AF5" s="78" t="s">
         <v>364</v>
       </c>
-      <c r="AG5" s="73" t="s">
+      <c r="AG5" s="75" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="76" t="s">
+    <row r="6" spans="1:33" s="41" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="82"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="N6" s="76" t="s">
+      <c r="N6" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="O6" s="76" t="s">
+      <c r="O6" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="P6" s="76" t="s">
+      <c r="P6" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="Q6" s="76" t="s">
+      <c r="Q6" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="R6" s="76" t="s">
+      <c r="R6" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75"/>
-      <c r="W6" s="75"/>
-      <c r="X6" s="75"/>
-      <c r="Y6" s="75"/>
-      <c r="Z6" s="75"/>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="75"/>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="73"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="73"/>
-    </row>
-    <row r="7" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="77">
+      <c r="S6" s="77"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
+      <c r="V6" s="77"/>
+      <c r="W6" s="77"/>
+      <c r="X6" s="77"/>
+      <c r="Y6" s="77"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="77"/>
+      <c r="AB6" s="77"/>
+      <c r="AC6" s="77"/>
+      <c r="AD6" s="77"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="78"/>
+      <c r="AG6" s="75"/>
+    </row>
+    <row r="7" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
         <v>1</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="44">
         <v>3110</v>
       </c>
-      <c r="C7" s="79" t="e">
+      <c r="C7" s="45" t="e">
         <f>VLOOKUP(B7,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="78" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81" t="str">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47" t="str">
         <f>L7&amp;"có hình dáng dạng "&amp;M7&amp;" chất liệu "&amp;N7&amp;" thành phần hóa chất: "&amp;O7&amp;" có kích thước "&amp;P7&amp;" dùng để "&amp;R7&amp;" cho "&amp;Q7</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="78">
+      <c r="I7" s="47"/>
+      <c r="J7" s="44">
         <v>10</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="84" t="s">
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="50" t="s">
         <v>508</v>
       </c>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="85" t="s">
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="AB7" s="80"/>
-      <c r="AC7" s="86">
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="52">
         <v>46143</v>
       </c>
-      <c r="AD7" s="86">
+      <c r="AD7" s="52">
         <v>46132</v>
       </c>
-      <c r="AE7" s="80"/>
-      <c r="AF7" s="87"/>
-      <c r="AG7" s="80"/>
-    </row>
-    <row r="8" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="77">
+      <c r="AE7" s="46"/>
+      <c r="AF7" s="53"/>
+      <c r="AG7" s="46"/>
+    </row>
+    <row r="8" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
         <v>2</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="44">
         <v>3110</v>
       </c>
-      <c r="C8" s="79" t="e">
+      <c r="C8" s="45" t="e">
         <f>VLOOKUP(B8,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D8" s="79"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="78" t="s">
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="44" t="s">
         <v>510</v>
       </c>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81" t="str">
+      <c r="G8" s="47"/>
+      <c r="H8" s="47" t="str">
         <f t="shared" ref="H8:H9" si="1">L8&amp;"có hình dáng dạng "&amp;M8&amp;" chất liệu "&amp;N8&amp;" thành phần hóa chất: "&amp;O8&amp;" có kích thước "&amp;P8&amp;" dùng để "&amp;R8&amp;" cho "&amp;Q8</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="78">
+      <c r="I8" s="47"/>
+      <c r="J8" s="44">
         <v>10</v>
       </c>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="84" t="s">
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="86">
+      <c r="X8" s="47"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
+      <c r="AA8" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="46"/>
+      <c r="AC8" s="52">
         <v>46143</v>
       </c>
-      <c r="AD8" s="86">
+      <c r="AD8" s="52">
         <v>46132</v>
       </c>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="87"/>
-      <c r="AG8" s="80"/>
-    </row>
-    <row r="9" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="77">
+      <c r="AE8" s="46"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="46"/>
+    </row>
+    <row r="9" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
         <v>3</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="44">
         <v>3110</v>
       </c>
-      <c r="C9" s="79" t="e">
+      <c r="C9" s="45" t="e">
         <f>VLOOKUP(B9,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="78" t="s">
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="44" t="s">
         <v>512</v>
       </c>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81" t="str">
+      <c r="G9" s="47"/>
+      <c r="H9" s="47" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I9" s="81"/>
-      <c r="J9" s="78">
+      <c r="I9" s="47"/>
+      <c r="J9" s="44">
         <v>10</v>
       </c>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="80"/>
-      <c r="T9" s="80"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="80"/>
-      <c r="W9" s="84" t="s">
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="50" t="s">
         <v>513</v>
       </c>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="80"/>
-      <c r="AC9" s="86">
+      <c r="X9" s="47"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
+      <c r="AA9" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="52">
         <v>46143</v>
       </c>
-      <c r="AD9" s="86">
+      <c r="AD9" s="52">
         <v>46132</v>
       </c>
-      <c r="AE9" s="80"/>
-      <c r="AF9" s="87"/>
-      <c r="AG9" s="80"/>
-    </row>
-    <row r="10" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="H10" s="62" t="str">
+      <c r="AE9" s="46"/>
+      <c r="AF9" s="53"/>
+      <c r="AG9" s="46"/>
+    </row>
+    <row r="10" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H10" s="36" t="str">
         <f t="shared" ref="H10:H11" si="2">M10&amp;" "&amp;N10&amp;" "&amp;O10&amp;""&amp;P10&amp;" "&amp;Q10&amp;" "&amp;R10</f>
         <v xml:space="preserve">    </v>
       </c>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="AA10" s="89"/>
-      <c r="AC10" s="90"/>
-      <c r="AD10" s="90"/>
-    </row>
-    <row r="11" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="H11" s="62" t="str">
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="AA10" s="55"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+    </row>
+    <row r="11" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H11" s="36" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    </v>
       </c>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="AA11" s="89"/>
-      <c r="AC11" s="90"/>
-      <c r="AD11" s="90"/>
-    </row>
-    <row r="12" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="65" t="s">
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+    </row>
+    <row r="12" spans="1:33" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="66">
+    <row r="13" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="40">
         <v>1</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="22">
         <v>2</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="22">
         <v>3</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="22">
         <v>4</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="22">
         <v>5</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="22">
         <v>6</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="22">
         <v>7</v>
       </c>
-      <c r="H13" s="25">
-        <v>8</v>
-      </c>
-      <c r="I13" s="25">
+      <c r="H13" s="22">
+        <v>8</v>
+      </c>
+      <c r="I13" s="22">
         <v>9</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="22">
         <v>10</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="22">
         <v>11</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="22">
         <v>12</v>
       </c>
-      <c r="M13" s="45">
+      <c r="M13" s="64">
         <f>L13+1</f>
         <v>13</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="37">
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="24">
         <v>14</v>
       </c>
-      <c r="T13" s="25">
+      <c r="T13" s="22">
         <f>S13+1</f>
         <v>15</v>
       </c>
-      <c r="U13" s="25">
+      <c r="U13" s="22">
         <f t="shared" ref="U13:AF13" si="3">T13+1</f>
         <v>16</v>
       </c>
-      <c r="V13" s="25">
+      <c r="V13" s="22">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="W13" s="25">
+      <c r="W13" s="22">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X13" s="25">
+      <c r="X13" s="22">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="Y13" s="25">
+      <c r="Y13" s="22">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="Z13" s="25">
+      <c r="Z13" s="22">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="22">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="AB13" s="25">
+      <c r="AB13" s="22">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="AC13" s="25">
+      <c r="AC13" s="22">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="AD13" s="25">
+      <c r="AD13" s="22">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="AE13" s="25">
+      <c r="AE13" s="22">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="AF13" s="91">
+      <c r="AF13" s="57">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="AG13" s="25">
+      <c r="AG13" s="22">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
+    <row r="14" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="76" t="s">
         <v>333</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="76" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="76" t="s">
         <v>335</v>
       </c>
-      <c r="E14" s="69" t="s">
+      <c r="E14" s="76" t="s">
         <v>336</v>
       </c>
-      <c r="F14" s="69" t="s">
+      <c r="F14" s="76" t="s">
         <v>337</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="76" t="s">
         <v>338</v>
       </c>
-      <c r="H14" s="69" t="s">
+      <c r="H14" s="76" t="s">
         <v>340</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="76" t="s">
         <v>341</v>
       </c>
-      <c r="J14" s="69" t="s">
+      <c r="J14" s="76" t="s">
         <v>339</v>
       </c>
-      <c r="K14" s="69" t="s">
+      <c r="K14" s="76" t="s">
         <v>342</v>
       </c>
-      <c r="L14" s="69" t="s">
+      <c r="L14" s="76" t="s">
         <v>343</v>
       </c>
-      <c r="M14" s="70" t="s">
+      <c r="M14" s="78" t="s">
         <v>349</v>
       </c>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="69" t="s">
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="76" t="s">
         <v>353</v>
       </c>
-      <c r="T14" s="69" t="s">
+      <c r="T14" s="76" t="s">
         <v>354</v>
       </c>
-      <c r="U14" s="69" t="s">
+      <c r="U14" s="76" t="s">
         <v>350</v>
       </c>
-      <c r="V14" s="69" t="s">
+      <c r="V14" s="76" t="s">
         <v>351</v>
       </c>
-      <c r="W14" s="69" t="s">
+      <c r="W14" s="76" t="s">
         <v>355</v>
       </c>
-      <c r="X14" s="69" t="s">
+      <c r="X14" s="76" t="s">
         <v>356</v>
       </c>
-      <c r="Y14" s="69" t="s">
+      <c r="Y14" s="76" t="s">
         <v>357</v>
       </c>
-      <c r="Z14" s="69" t="s">
+      <c r="Z14" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="AA14" s="69" t="s">
+      <c r="AA14" s="76" t="s">
         <v>359</v>
       </c>
-      <c r="AB14" s="69" t="s">
+      <c r="AB14" s="76" t="s">
         <v>360</v>
       </c>
-      <c r="AC14" s="69" t="s">
+      <c r="AC14" s="76" t="s">
         <v>361</v>
       </c>
-      <c r="AD14" s="69" t="s">
+      <c r="AD14" s="76" t="s">
         <v>362</v>
       </c>
-      <c r="AE14" s="73" t="s">
+      <c r="AE14" s="75" t="s">
         <v>363</v>
       </c>
-      <c r="AF14" s="92" t="s">
+      <c r="AF14" s="74" t="s">
         <v>364</v>
       </c>
-      <c r="AG14" s="73" t="s">
+      <c r="AG14" s="75" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="74"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="76" t="s">
+    <row r="15" spans="1:33" s="41" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="82"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="N15" s="76" t="s">
+      <c r="N15" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="O15" s="76" t="s">
+      <c r="O15" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="P15" s="76" t="s">
+      <c r="P15" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="Q15" s="76" t="s">
+      <c r="Q15" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="R15" s="76" t="s">
+      <c r="R15" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="75"/>
-      <c r="Y15" s="75"/>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="75"/>
-      <c r="AC15" s="75"/>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="92"/>
-      <c r="AG15" s="73"/>
-    </row>
-    <row r="16" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="77">
+      <c r="S15" s="77"/>
+      <c r="T15" s="77"/>
+      <c r="U15" s="77"/>
+      <c r="V15" s="77"/>
+      <c r="W15" s="77"/>
+      <c r="X15" s="77"/>
+      <c r="Y15" s="77"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="77"/>
+      <c r="AC15" s="77"/>
+      <c r="AD15" s="77"/>
+      <c r="AE15" s="75"/>
+      <c r="AF15" s="74"/>
+      <c r="AG15" s="75"/>
+    </row>
+    <row r="16" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
         <v>1</v>
       </c>
-      <c r="B16" s="78">
+      <c r="B16" s="44">
         <v>3110</v>
       </c>
-      <c r="C16" s="79" t="e">
+      <c r="C16" s="45" t="e">
         <f>VLOOKUP(B16,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D16" s="78"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="81" t="str">
+      <c r="D16" s="44"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="47" t="str">
         <f>L16&amp;"có hình dáng dạng "&amp;M16&amp;" chất liệu "&amp;N16&amp;" thành phần hóa chất: "&amp;O16&amp;" có kích thước "&amp;P16&amp;" dùng để "&amp;R16&amp;" cho "&amp;Q16</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78">
+      <c r="I16" s="44"/>
+      <c r="J16" s="44">
         <v>10</v>
       </c>
-      <c r="K16" s="78" t="s">
+      <c r="K16" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="83"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="83"/>
-      <c r="W16" s="84" t="s">
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="50" t="s">
         <v>508</v>
       </c>
-      <c r="X16" s="80"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="85" t="s">
+      <c r="X16" s="46"/>
+      <c r="Y16" s="47"/>
+      <c r="Z16" s="47"/>
+      <c r="AA16" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="AB16" s="80"/>
-      <c r="AC16" s="86">
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="52">
         <v>46143</v>
       </c>
-      <c r="AD16" s="86">
+      <c r="AD16" s="52">
         <v>46132</v>
       </c>
-      <c r="AE16" s="80"/>
-      <c r="AF16" s="94"/>
-      <c r="AG16" s="80"/>
-    </row>
-    <row r="17" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="77">
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="59"/>
+      <c r="AG16" s="46"/>
+    </row>
+    <row r="17" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="43">
         <v>2</v>
       </c>
-      <c r="B17" s="78">
+      <c r="B17" s="44">
         <v>3110</v>
       </c>
-      <c r="C17" s="79" t="e">
+      <c r="C17" s="45" t="e">
         <f>VLOOKUP(B17,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D17" s="78"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="81" t="str">
+      <c r="D17" s="44"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="47" t="str">
         <f t="shared" ref="H17:H19" si="4">L17&amp;"có hình dáng dạng "&amp;M17&amp;" chất liệu "&amp;N17&amp;" thành phần hóa chất: "&amp;O17&amp;" có kích thước "&amp;P17&amp;" dùng để "&amp;R17&amp;" cho "&amp;Q17</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78">
+      <c r="I17" s="44"/>
+      <c r="J17" s="44">
         <v>10</v>
       </c>
-      <c r="K17" s="78" t="s">
+      <c r="K17" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="80"/>
-      <c r="T17" s="80"/>
-      <c r="U17" s="80"/>
-      <c r="V17" s="80"/>
-      <c r="W17" s="84" t="s">
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="X17" s="80"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB17" s="80"/>
-      <c r="AC17" s="86">
+      <c r="X17" s="46"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="47"/>
+      <c r="AA17" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="52">
         <v>46143</v>
       </c>
-      <c r="AD17" s="86">
+      <c r="AD17" s="52">
         <v>46132</v>
       </c>
-      <c r="AE17" s="80"/>
-      <c r="AF17" s="94"/>
-      <c r="AG17" s="80"/>
-    </row>
-    <row r="18" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="77">
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="59"/>
+      <c r="AG17" s="46"/>
+    </row>
+    <row r="18" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="43">
         <v>3</v>
       </c>
-      <c r="B18" s="78">
+      <c r="B18" s="44">
         <v>3110</v>
       </c>
-      <c r="C18" s="79" t="e">
+      <c r="C18" s="45" t="e">
         <f>VLOOKUP(B18,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="81" t="str">
+      <c r="D18" s="44"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="47" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78">
+      <c r="I18" s="44"/>
+      <c r="J18" s="44">
         <v>10</v>
       </c>
-      <c r="K18" s="78" t="s">
+      <c r="K18" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="84" t="s">
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="50" t="s">
         <v>513</v>
       </c>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB18" s="80"/>
-      <c r="AC18" s="86">
+      <c r="X18" s="46"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="47"/>
+      <c r="AA18" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="52">
         <v>46143</v>
       </c>
-      <c r="AD18" s="86">
+      <c r="AD18" s="52">
         <v>46132</v>
       </c>
-      <c r="AE18" s="80"/>
-      <c r="AF18" s="94"/>
-      <c r="AG18" s="80"/>
-    </row>
-    <row r="19" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="77">
+      <c r="AE18" s="46"/>
+      <c r="AF18" s="59"/>
+      <c r="AG18" s="46"/>
+    </row>
+    <row r="19" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="43">
         <v>3</v>
       </c>
-      <c r="B19" s="78">
+      <c r="B19" s="44">
         <v>3110</v>
       </c>
-      <c r="C19" s="79" t="e">
+      <c r="C19" s="45" t="e">
         <f>VLOOKUP(B19,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="81" t="str">
+      <c r="D19" s="44"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="47" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78">
+      <c r="I19" s="44"/>
+      <c r="J19" s="44">
         <v>10</v>
       </c>
-      <c r="K19" s="78" t="s">
+      <c r="K19" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="84" t="s">
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="50" t="s">
         <v>513</v>
       </c>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB19" s="80"/>
-      <c r="AC19" s="86">
+      <c r="X19" s="46"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="47"/>
+      <c r="AA19" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="46"/>
+      <c r="AC19" s="52">
         <v>46143</v>
       </c>
-      <c r="AD19" s="86">
+      <c r="AD19" s="52">
         <v>46132</v>
       </c>
-      <c r="AE19" s="80"/>
-      <c r="AF19" s="94"/>
-      <c r="AG19" s="94"/>
-    </row>
-    <row r="20" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="95" t="s">
+      <c r="AE19" s="46"/>
+      <c r="AF19" s="59"/>
+      <c r="AG19" s="59"/>
+    </row>
+    <row r="20" spans="1:33" s="60" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="60" t="s">
         <v>516</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="60" t="s">
         <v>516</v>
       </c>
-      <c r="K20" s="95" t="s">
+      <c r="K20" s="60" t="s">
         <v>516</v>
       </c>
-      <c r="L20" s="95" t="s">
+      <c r="L20" s="60" t="s">
         <v>517</v>
       </c>
-      <c r="M20" s="95" t="s">
+      <c r="M20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="N20" s="95" t="s">
+      <c r="N20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="O20" s="95" t="s">
+      <c r="O20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="P20" s="95" t="s">
+      <c r="P20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="Q20" s="95" t="s">
+      <c r="Q20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="R20" s="95" t="s">
+      <c r="R20" s="60" t="s">
         <v>518</v>
       </c>
-      <c r="Y20" s="95" t="s">
+      <c r="Y20" s="60" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
-      <c r="L21" s="95" t="s">
+    <row r="21" spans="1:33" s="60" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="L21" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="Y21" s="95" t="s">
+      <c r="Y21" s="60" t="s">
         <v>521</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:R14"/>
-    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="M13:R13"/>
     <mergeCell ref="A14:A15"/>
@@ -30204,28 +30193,26 @@
     <mergeCell ref="AD5:AD6"/>
     <mergeCell ref="AE5:AE6"/>
     <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:R5"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:R14"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA7:AA11 AA16:AA18" xr:uid="{7148D881-3CE6-40B6-9B29-09D7A050C101}">
@@ -30256,24 +30243,24 @@
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="23.85546875" style="32" customWidth="1"/>
+    <col min="5" max="6" width="23.85546875" customWidth="1"/>
     <col min="7" max="7" width="92.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="19" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -30283,11 +30270,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -30299,13 +30286,13 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="28">
+      <c r="B4" s="25">
         <v>1</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="57"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -30315,13 +30302,13 @@
       <c r="G4" s="21"/>
     </row>
     <row r="5" spans="2:7" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="28">
+      <c r="B5" s="25">
         <v>2</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="86" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="87"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -30330,13 +30317,13 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="28">
+      <c r="B6" s="25">
         <v>3</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="86" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="52"/>
+      <c r="D6" s="87"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -30348,13 +30335,13 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28">
+      <c r="B7" s="25">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="86" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="52"/>
+      <c r="D7" s="87"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -30366,13 +30353,13 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="96" x14ac:dyDescent="0.25">
-      <c r="B8" s="28">
+      <c r="B8" s="25">
         <v>5</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="86" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="87"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -30384,13 +30371,13 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="28">
+      <c r="B9" s="25">
         <v>6</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="86" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="87"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -30402,13 +30389,13 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="28">
+      <c r="B10" s="25">
         <v>7</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="86" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="87"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -30420,13 +30407,13 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28">
-        <v>8</v>
-      </c>
-      <c r="C11" s="51" t="s">
+      <c r="B11" s="25">
+        <v>8</v>
+      </c>
+      <c r="C11" s="86" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="87"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -30438,61 +30425,61 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="28">
+      <c r="B12" s="25">
         <v>9</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="86" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="52"/>
+      <c r="D12" s="87"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G12" s="31"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="28">
+      <c r="B13" s="25">
         <v>10</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="86" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="52"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="28">
+      <c r="B14" s="25">
         <v>11</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="86" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="52"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G14" s="31"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="28">
+      <c r="B15" s="25">
         <v>12</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="86" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="52"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -30504,14 +30491,14 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="54">
+      <c r="B16" s="89">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="83" t="s">
         <v>349</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="26" t="s">
         <v>344</v>
       </c>
       <c r="E16" s="20" t="s">
@@ -30525,9 +30512,9 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="29" t="s">
+      <c r="B17" s="89"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="26" t="s">
         <v>345</v>
       </c>
       <c r="E17" s="20" t="s">
@@ -30541,9 +30528,9 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="29" t="s">
+      <c r="B18" s="89"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="26" t="s">
         <v>346</v>
       </c>
       <c r="E18" s="20" t="s">
@@ -30557,9 +30544,9 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="29" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="26" t="s">
         <v>347</v>
       </c>
       <c r="E19" s="20" t="s">
@@ -30573,9 +30560,9 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="29" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="26" t="s">
         <v>348</v>
       </c>
       <c r="E20" s="20" t="s">
@@ -30589,9 +30576,9 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="54"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="29" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="26" t="s">
         <v>352</v>
       </c>
       <c r="E21" s="20" t="s">
@@ -30605,13 +30592,13 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="30">
+      <c r="B22" s="27">
         <v>14</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="86" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="87"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -30623,14 +30610,14 @@
       </c>
     </row>
     <row r="23" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28">
+      <c r="B23" s="25">
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="86" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="52"/>
+      <c r="D23" s="87"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -30642,14 +30629,14 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="28">
+      <c r="B24" s="25">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="86" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="52"/>
+      <c r="D24" s="87"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -30661,14 +30648,14 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="28">
+      <c r="B25" s="25">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="86" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="52"/>
+      <c r="D25" s="87"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -30680,14 +30667,14 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="60.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="28">
+      <c r="B26" s="25">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="86" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="52"/>
+      <c r="D26" s="87"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -30699,14 +30686,14 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="28">
+      <c r="B27" s="25">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="86" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="52"/>
+      <c r="D27" s="87"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -30718,14 +30705,14 @@
       </c>
     </row>
     <row r="28" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="28">
+      <c r="B28" s="25">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="86" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="52"/>
+      <c r="D28" s="87"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -30737,14 +30724,14 @@
       </c>
     </row>
     <row r="29" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="28">
+      <c r="B29" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="86" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="52"/>
+      <c r="D29" s="87"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -30756,14 +30743,14 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="28">
+      <c r="B30" s="25">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="86" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="87"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -30775,14 +30762,14 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="28">
+      <c r="B31" s="25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="86" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="52"/>
+      <c r="D31" s="87"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -30794,14 +30781,14 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="28">
+      <c r="B32" s="25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="86" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="52"/>
+      <c r="D32" s="87"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -30811,14 +30798,14 @@
       <c r="G32" s="20"/>
     </row>
     <row r="33" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="28">
+      <c r="B33" s="25">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="86" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="52"/>
+      <c r="D33" s="87"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -30830,14 +30817,14 @@
       </c>
     </row>
     <row r="34" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="28">
+      <c r="B34" s="25">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="83" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="55"/>
+      <c r="D34" s="83"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -30849,27 +30836,41 @@
       </c>
     </row>
     <row r="35" spans="2:7" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="28">
+      <c r="B35" s="25">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="83" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="55"/>
+      <c r="D35" s="83"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="21" t="s">
         <v>381</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -30886,20 +30887,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -30934,7 +30921,7 @@
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="29" t="s">
         <v>390</v>
       </c>
     </row>
@@ -30945,7 +30932,7 @@
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="29" t="s">
         <v>391</v>
       </c>
     </row>
@@ -30956,7 +30943,7 @@
       <c r="B4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="29" t="s">
         <v>392</v>
       </c>
     </row>
@@ -30967,7 +30954,7 @@
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="29" t="s">
         <v>393</v>
       </c>
     </row>
@@ -30978,7 +30965,7 @@
       <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="29" t="s">
         <v>394</v>
       </c>
     </row>
@@ -30989,7 +30976,7 @@
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="29" t="s">
         <v>395</v>
       </c>
     </row>
@@ -31000,7 +30987,7 @@
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="30" t="s">
         <v>396</v>
       </c>
     </row>
@@ -31011,7 +30998,7 @@
       <c r="B9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="30" t="s">
         <v>397</v>
       </c>
     </row>
@@ -31022,7 +31009,7 @@
       <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="29" t="s">
         <v>398</v>
       </c>
     </row>
@@ -31033,7 +31020,7 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="30" t="s">
         <v>399</v>
       </c>
     </row>
@@ -31044,7 +31031,7 @@
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="29" t="s">
         <v>400</v>
       </c>
     </row>
@@ -31055,7 +31042,7 @@
       <c r="B13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="29" t="s">
         <v>401</v>
       </c>
     </row>
@@ -31066,7 +31053,7 @@
       <c r="B14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="29" t="s">
         <v>402</v>
       </c>
     </row>
@@ -31077,7 +31064,7 @@
       <c r="B15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="29" t="s">
         <v>403</v>
       </c>
     </row>
@@ -31088,7 +31075,7 @@
       <c r="B16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="29" t="s">
         <v>404</v>
       </c>
     </row>
@@ -31099,7 +31086,7 @@
       <c r="B17" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="29" t="s">
         <v>405</v>
       </c>
     </row>
@@ -31110,7 +31097,7 @@
       <c r="B18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="29" t="s">
         <v>406</v>
       </c>
     </row>
@@ -31121,7 +31108,7 @@
       <c r="B19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="30" t="s">
         <v>407</v>
       </c>
     </row>
@@ -31132,7 +31119,7 @@
       <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="30" t="s">
         <v>408</v>
       </c>
     </row>
@@ -31143,7 +31130,7 @@
       <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="30" t="s">
         <v>409</v>
       </c>
     </row>
@@ -31154,7 +31141,7 @@
       <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="29" t="s">
         <v>410</v>
       </c>
     </row>
@@ -31165,7 +31152,7 @@
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="30" t="s">
         <v>411</v>
       </c>
     </row>
@@ -31176,7 +31163,7 @@
       <c r="B24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="29" t="s">
         <v>412</v>
       </c>
     </row>
@@ -31187,7 +31174,7 @@
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="30" t="s">
         <v>413</v>
       </c>
     </row>
@@ -31198,7 +31185,7 @@
       <c r="B26" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="30" t="s">
         <v>414</v>
       </c>
     </row>
@@ -31209,7 +31196,7 @@
       <c r="B27" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="29" t="s">
         <v>415</v>
       </c>
     </row>
@@ -31220,7 +31207,7 @@
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="29" t="s">
         <v>416</v>
       </c>
     </row>
@@ -31231,7 +31218,7 @@
       <c r="B29" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="30" t="s">
         <v>417</v>
       </c>
     </row>
@@ -31242,7 +31229,7 @@
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="30" t="s">
         <v>418</v>
       </c>
     </row>
@@ -31253,7 +31240,7 @@
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="29" t="s">
         <v>419</v>
       </c>
     </row>
@@ -31264,7 +31251,7 @@
       <c r="B32" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="29" t="s">
         <v>420</v>
       </c>
     </row>
@@ -31275,7 +31262,7 @@
       <c r="B33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="29" t="s">
         <v>421</v>
       </c>
     </row>
@@ -31286,7 +31273,7 @@
       <c r="B34" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="29" t="s">
         <v>422</v>
       </c>
     </row>
@@ -31297,7 +31284,7 @@
       <c r="B35" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="29" t="s">
         <v>423</v>
       </c>
     </row>
@@ -31308,7 +31295,7 @@
       <c r="B36" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="D36" s="29" t="s">
         <v>424</v>
       </c>
     </row>
@@ -31319,7 +31306,7 @@
       <c r="B37" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="33" t="s">
+      <c r="D37" s="29" t="s">
         <v>425</v>
       </c>
     </row>
@@ -31330,7 +31317,7 @@
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="30" t="s">
         <v>426</v>
       </c>
     </row>
@@ -31341,7 +31328,7 @@
       <c r="B39" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="33" t="s">
+      <c r="D39" s="29" t="s">
         <v>427</v>
       </c>
     </row>
@@ -31352,7 +31339,7 @@
       <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="29" t="s">
         <v>428</v>
       </c>
     </row>
@@ -31363,7 +31350,7 @@
       <c r="B41" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="29" t="s">
         <v>429</v>
       </c>
     </row>
@@ -31374,7 +31361,7 @@
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="D42" s="29" t="s">
         <v>430</v>
       </c>
     </row>
@@ -31385,7 +31372,7 @@
       <c r="B43" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="29" t="s">
         <v>431</v>
       </c>
     </row>
@@ -31396,7 +31383,7 @@
       <c r="B44" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="33" t="s">
+      <c r="D44" s="29" t="s">
         <v>432</v>
       </c>
     </row>
@@ -31407,7 +31394,7 @@
       <c r="B45" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="33" t="s">
+      <c r="D45" s="29" t="s">
         <v>433</v>
       </c>
     </row>
@@ -31418,7 +31405,7 @@
       <c r="B46" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="29" t="s">
         <v>434</v>
       </c>
     </row>
@@ -31429,7 +31416,7 @@
       <c r="B47" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="33" t="s">
+      <c r="D47" s="29" t="s">
         <v>435</v>
       </c>
     </row>
@@ -31440,7 +31427,7 @@
       <c r="B48" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="33" t="s">
+      <c r="D48" s="29" t="s">
         <v>436</v>
       </c>
     </row>
@@ -31451,7 +31438,7 @@
       <c r="B49" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="33" t="s">
+      <c r="D49" s="29" t="s">
         <v>437</v>
       </c>
     </row>
@@ -31462,7 +31449,7 @@
       <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="33" t="s">
+      <c r="D50" s="29" t="s">
         <v>438</v>
       </c>
     </row>
@@ -31473,7 +31460,7 @@
       <c r="B51" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="33" t="s">
+      <c r="D51" s="29" t="s">
         <v>439</v>
       </c>
     </row>
@@ -31484,7 +31471,7 @@
       <c r="B52" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="33" t="s">
+      <c r="D52" s="29" t="s">
         <v>440</v>
       </c>
     </row>
@@ -31495,7 +31482,7 @@
       <c r="B53" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="29" t="s">
         <v>441</v>
       </c>
     </row>
@@ -31506,7 +31493,7 @@
       <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="30" t="s">
         <v>442</v>
       </c>
     </row>
@@ -31517,7 +31504,7 @@
       <c r="B55" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="30" t="s">
         <v>443</v>
       </c>
     </row>
@@ -31528,7 +31515,7 @@
       <c r="B56" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="34" t="s">
+      <c r="D56" s="30" t="s">
         <v>444</v>
       </c>
     </row>
@@ -31539,7 +31526,7 @@
       <c r="B57" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="33" t="s">
+      <c r="D57" s="29" t="s">
         <v>445</v>
       </c>
     </row>
@@ -31550,7 +31537,7 @@
       <c r="B58" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="33" t="s">
+      <c r="D58" s="29" t="s">
         <v>446</v>
       </c>
     </row>
@@ -31561,7 +31548,7 @@
       <c r="B59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="30" t="s">
         <v>447</v>
       </c>
     </row>
@@ -31572,7 +31559,7 @@
       <c r="B60" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D60" s="33" t="s">
+      <c r="D60" s="29" t="s">
         <v>448</v>
       </c>
     </row>
@@ -31583,7 +31570,7 @@
       <c r="B61" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="33" t="s">
+      <c r="D61" s="29" t="s">
         <v>449</v>
       </c>
     </row>
@@ -31594,7 +31581,7 @@
       <c r="B62" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="33" t="s">
+      <c r="D62" s="29" t="s">
         <v>450</v>
       </c>
     </row>
@@ -31605,7 +31592,7 @@
       <c r="B63" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="33" t="s">
+      <c r="D63" s="29" t="s">
         <v>451</v>
       </c>
     </row>
@@ -31616,7 +31603,7 @@
       <c r="B64" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="29" t="s">
         <v>452</v>
       </c>
     </row>
@@ -31627,7 +31614,7 @@
       <c r="B65" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D65" s="33" t="s">
+      <c r="D65" s="29" t="s">
         <v>453</v>
       </c>
     </row>
@@ -31638,7 +31625,7 @@
       <c r="B66" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="33" t="s">
+      <c r="D66" s="29" t="s">
         <v>454</v>
       </c>
     </row>
@@ -31649,7 +31636,7 @@
       <c r="B67" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="30" t="s">
         <v>455</v>
       </c>
     </row>
@@ -31660,7 +31647,7 @@
       <c r="B68" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="34" t="s">
+      <c r="D68" s="30" t="s">
         <v>456</v>
       </c>
     </row>
@@ -31671,7 +31658,7 @@
       <c r="B69" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="33" t="s">
+      <c r="D69" s="29" t="s">
         <v>457</v>
       </c>
     </row>
@@ -31682,7 +31669,7 @@
       <c r="B70" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="34" t="s">
+      <c r="D70" s="30" t="s">
         <v>458</v>
       </c>
     </row>
@@ -31693,7 +31680,7 @@
       <c r="B71" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D71" s="33" t="s">
+      <c r="D71" s="29" t="s">
         <v>459</v>
       </c>
     </row>
@@ -31704,7 +31691,7 @@
       <c r="B72" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="D72" s="29" t="s">
         <v>460</v>
       </c>
     </row>
@@ -31715,7 +31702,7 @@
       <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="33" t="s">
+      <c r="D73" s="29" t="s">
         <v>461</v>
       </c>
     </row>
@@ -31726,7 +31713,7 @@
       <c r="B74" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="33" t="s">
+      <c r="D74" s="29" t="s">
         <v>462</v>
       </c>
     </row>
@@ -31737,7 +31724,7 @@
       <c r="B75" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="29" t="s">
         <v>463</v>
       </c>
     </row>
@@ -31748,7 +31735,7 @@
       <c r="B76" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D76" s="29" t="s">
         <v>464</v>
       </c>
     </row>
@@ -31759,7 +31746,7 @@
       <c r="B77" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D77" s="29" t="s">
         <v>465</v>
       </c>
     </row>
@@ -31770,7 +31757,7 @@
       <c r="B78" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D78" s="29" t="s">
         <v>466</v>
       </c>
     </row>
@@ -31781,7 +31768,7 @@
       <c r="B79" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="33" t="s">
+      <c r="D79" s="29" t="s">
         <v>467</v>
       </c>
     </row>
@@ -31792,7 +31779,7 @@
       <c r="B80" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="33" t="s">
+      <c r="D80" s="29" t="s">
         <v>468</v>
       </c>
     </row>
@@ -31803,7 +31790,7 @@
       <c r="B81" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D81" s="33" t="s">
+      <c r="D81" s="29" t="s">
         <v>469</v>
       </c>
     </row>
@@ -31814,7 +31801,7 @@
       <c r="B82" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D82" s="34" t="s">
+      <c r="D82" s="30" t="s">
         <v>470</v>
       </c>
     </row>
@@ -31825,7 +31812,7 @@
       <c r="B83" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D83" s="33" t="s">
+      <c r="D83" s="29" t="s">
         <v>471</v>
       </c>
     </row>
@@ -31836,7 +31823,7 @@
       <c r="B84" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D84" s="33" t="s">
+      <c r="D84" s="29" t="s">
         <v>472</v>
       </c>
     </row>
@@ -31847,7 +31834,7 @@
       <c r="B85" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="33" t="s">
+      <c r="D85" s="29" t="s">
         <v>473</v>
       </c>
     </row>
@@ -31858,7 +31845,7 @@
       <c r="B86" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="34" t="s">
+      <c r="D86" s="30" t="s">
         <v>474</v>
       </c>
     </row>
@@ -31869,7 +31856,7 @@
       <c r="B87" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="29" t="s">
         <v>475</v>
       </c>
     </row>
@@ -31880,7 +31867,7 @@
       <c r="B88" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D88" s="33" t="s">
+      <c r="D88" s="29" t="s">
         <v>476</v>
       </c>
     </row>
@@ -31891,7 +31878,7 @@
       <c r="B89" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D89" s="33" t="s">
+      <c r="D89" s="29" t="s">
         <v>477</v>
       </c>
     </row>
@@ -31902,7 +31889,7 @@
       <c r="B90" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D90" s="29" t="s">
         <v>478</v>
       </c>
     </row>
@@ -31913,7 +31900,7 @@
       <c r="B91" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="33" t="s">
+      <c r="D91" s="29" t="s">
         <v>479</v>
       </c>
     </row>
@@ -31924,7 +31911,7 @@
       <c r="B92" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="33" t="s">
+      <c r="D92" s="29" t="s">
         <v>480</v>
       </c>
     </row>
@@ -31935,7 +31922,7 @@
       <c r="B93" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="29" t="s">
         <v>481</v>
       </c>
     </row>
@@ -31946,7 +31933,7 @@
       <c r="B94" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D94" s="33" t="s">
+      <c r="D94" s="29" t="s">
         <v>482</v>
       </c>
     </row>
@@ -31957,7 +31944,7 @@
       <c r="B95" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="D95" s="29" t="s">
         <v>483</v>
       </c>
     </row>
@@ -31968,7 +31955,7 @@
       <c r="B96" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D96" s="34" t="s">
+      <c r="D96" s="30" t="s">
         <v>484</v>
       </c>
     </row>
@@ -31979,7 +31966,7 @@
       <c r="B97" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D97" s="29" t="s">
         <v>485</v>
       </c>
     </row>
@@ -31990,7 +31977,7 @@
       <c r="B98" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="29" t="s">
         <v>486</v>
       </c>
     </row>
@@ -32001,7 +31988,7 @@
       <c r="B99" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D99" s="33" t="s">
+      <c r="D99" s="29" t="s">
         <v>487</v>
       </c>
     </row>
@@ -32012,7 +31999,7 @@
       <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D100" s="29" t="s">
         <v>488</v>
       </c>
     </row>
@@ -32023,7 +32010,7 @@
       <c r="B101" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="33" t="s">
+      <c r="D101" s="29" t="s">
         <v>489</v>
       </c>
     </row>
@@ -32034,7 +32021,7 @@
       <c r="B102" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="D102" s="29" t="s">
         <v>490</v>
       </c>
     </row>
@@ -32045,7 +32032,7 @@
       <c r="B103" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="D103" s="29" t="s">
         <v>491</v>
       </c>
     </row>
@@ -32056,7 +32043,7 @@
       <c r="B104" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="D104" s="29" t="s">
         <v>492</v>
       </c>
     </row>
@@ -32067,7 +32054,7 @@
       <c r="B105" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D105" s="34" t="s">
+      <c r="D105" s="30" t="s">
         <v>493</v>
       </c>
     </row>
@@ -32078,7 +32065,7 @@
       <c r="B106" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D106" s="34" t="s">
+      <c r="D106" s="30" t="s">
         <v>494</v>
       </c>
     </row>
@@ -32089,7 +32076,7 @@
       <c r="B107" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D107" s="29" t="s">
         <v>495</v>
       </c>
     </row>
@@ -32100,7 +32087,7 @@
       <c r="B108" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D108" s="31" t="s">
+      <c r="D108" s="28" t="s">
         <v>496</v>
       </c>
     </row>
@@ -32111,7 +32098,7 @@
       <c r="B109" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D109" s="35" t="s">
+      <c r="D109" s="31" t="s">
         <v>497</v>
       </c>
     </row>
@@ -32122,7 +32109,7 @@
       <c r="B110" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D110" s="31" t="s">
+      <c r="D110" s="28" t="s">
         <v>498</v>
       </c>
     </row>
@@ -32133,7 +32120,7 @@
       <c r="B111" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D111" s="31" t="s">
+      <c r="D111" s="28" t="s">
         <v>499</v>
       </c>
     </row>
@@ -32144,7 +32131,7 @@
       <c r="B112" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D112" s="29" t="s">
         <v>500</v>
       </c>
     </row>
@@ -32640,12 +32627,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
